--- a/outputs/validation_frame_nodal_loads.xlsx
+++ b/outputs/validation_frame_nodal_loads.xlsx
@@ -643,25 +643,25 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.008506800363843648</v>
+        <v>-0.008506800363761516</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3200869679146143</v>
+        <v>-0.3200869679146637</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.001454028388443931</v>
+        <v>-0.001454028388444138</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1813005936457907</v>
+        <v>0.1813005936458008</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008825836814519907</v>
+        <v>0.0008825836814662386</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.950848033461115e-14</v>
+        <v>-9.285603354946163e-15</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3202032899265028</v>
+        <v>0.3202032899265501</v>
       </c>
     </row>
     <row r="7">
@@ -678,25 +678,25 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.008506800363530128</v>
+        <v>-0.008506800363690507</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3199836416745343</v>
+        <v>-0.3199836416745839</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0001215664955624709</v>
+        <v>-0.000121566495562611</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0320562762172913</v>
+        <v>0.03205627621730149</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008825836815066833</v>
+        <v>0.0008825836814785056</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.953174045802473e-14</v>
+        <v>-9.295205578831507e-15</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3200967218984515</v>
+        <v>0.3200967218985052</v>
       </c>
     </row>
     <row r="8">
@@ -713,25 +713,25 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.008617658990236473</v>
+        <v>-0.008617658990396852</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.319983641674853</v>
+        <v>-0.3199836416746615</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001454028388443984</v>
+        <v>0.001454028388444068</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03205627621734609</v>
+        <v>0.03205627621731389</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.006590736799513456</v>
+        <v>-0.006590736799541642</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.95222817975377e-14</v>
+        <v>-9.296542609148836e-15</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3201029665350309</v>
+        <v>0.3201029665348439</v>
       </c>
     </row>
     <row r="9">
@@ -748,25 +748,25 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.008617658990549991</v>
+        <v>-0.008617658990467861</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3200869679149329</v>
+        <v>-0.3200869679147415</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001215664955624186</v>
+        <v>0.0001215664955626805</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1813005936458454</v>
+        <v>0.1813005936458132</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.006590736799568158</v>
+        <v>-0.006590736799553908</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.952324315212423e-14</v>
+        <v>-9.303613152494448e-15</v>
       </c>
       <c r="K9" t="n">
-        <v>0.320202976022812</v>
+        <v>0.3202029760226185</v>
       </c>
     </row>
     <row r="10">
@@ -783,25 +783,25 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.07036120329910434</v>
+        <v>-0.07036120329889795</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6912454096229569</v>
+        <v>-0.6912454096231312</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.002332846674624704</v>
+        <v>-0.002332846674625141</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0004776631797100466</v>
+        <v>0.0004776631797337471</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0355348953589887</v>
+        <v>-0.03553489535897476</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.010899116652667e-13</v>
+        <v>-2.254982535921031e-14</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6948210974258875</v>
+        <v>0.69482109742604</v>
       </c>
     </row>
     <row r="11">
@@ -818,25 +818,25 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.07036120329830216</v>
+        <v>-0.07036120329871685</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6908036589435386</v>
+        <v>-0.6908036589437132</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0007903423542390336</v>
+        <v>-0.000790342354239219</v>
       </c>
       <c r="H11" t="n">
-        <v>0.03349161994969708</v>
+        <v>0.0334916199497208</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.03553489535892964</v>
+        <v>-0.03553489535896087</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.010500600582059e-13</v>
+        <v>-2.253216035953992e-14</v>
       </c>
       <c r="K11" t="n">
-        <v>0.694378152579992</v>
+        <v>0.6943781525802077</v>
       </c>
     </row>
     <row r="12">
@@ -853,25 +853,25 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.06987906847835977</v>
+        <v>-0.06987906847877449</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6908036589443535</v>
+        <v>-0.6908036589438927</v>
       </c>
       <c r="G12" t="n">
-        <v>0.00233284667462481</v>
+        <v>0.002332846674625</v>
       </c>
       <c r="H12" t="n">
-        <v>0.03349161994976197</v>
+        <v>0.03349161994973283</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0002044443358872198</v>
+        <v>0.0002044443358560187</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.010917419802469e-13</v>
+        <v>-2.255910051777855e-14</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6943329328181957</v>
+        <v>0.6943329328177792</v>
       </c>
     </row>
     <row r="13">
@@ -888,25 +888,25 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.06987906847916199</v>
+        <v>-0.06987906847895559</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6912454096237716</v>
+        <v>-0.6912454096233109</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0007903423542389292</v>
+        <v>0.000790342354239359</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0004776631797749287</v>
+        <v>0.0004776631797457648</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0002044443358281631</v>
+        <v>0.0002044443358421079</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.010136040492752e-13</v>
+        <v>-2.255697836653975e-14</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6947689725214332</v>
+        <v>0.6947689725209542</v>
       </c>
     </row>
     <row r="14">
@@ -923,25 +923,25 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4537190030256291</v>
+        <v>-0.4537190030253384</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7504936950263797</v>
+        <v>-0.7504936950267934</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.003032168184686173</v>
+        <v>-0.003032168184686789</v>
       </c>
       <c r="H14" t="n">
-        <v>0.006590736799522585</v>
+        <v>0.006590736799546265</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.02907849070414583</v>
+        <v>-0.0290784907041432</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.611412101213256e-13</v>
+        <v>-3.586128221406856e-14</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8769896886650491</v>
+        <v>0.8769896886652527</v>
       </c>
     </row>
     <row r="15">
@@ -958,25 +958,25 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4537190030243844</v>
+        <v>-0.4537190030250376</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7505876822821378</v>
+        <v>-0.7505876822825513</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.001456573300679839</v>
+        <v>-0.00145657330068003</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0008825836814975517</v>
+        <v>-0.0008825836814738829</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.02907849070410424</v>
+        <v>-0.0290784907041274</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.611526070967156e-13</v>
+        <v>-3.586244829761654e-14</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8770660887897178</v>
+        <v>0.8770660887904096</v>
       </c>
     </row>
     <row r="16">
@@ -993,25 +993,25 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4537911944455522</v>
+        <v>-0.4537911944462054</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7505876822834716</v>
+        <v>-0.7505876822828246</v>
       </c>
       <c r="G16" t="n">
-        <v>0.003032168184686301</v>
+        <v>0.003032168184686586</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0008825836814504936</v>
+        <v>-0.0008825836814639399</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1913477001706949</v>
+        <v>-0.1913477001707182</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.611381091097773e-13</v>
+        <v>-3.584592144909157e-14</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8771074683275105</v>
+        <v>0.8771074683272948</v>
       </c>
     </row>
     <row r="17">
@@ -1028,25 +1028,25 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.453791194446797</v>
+        <v>-0.4537911944465061</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7504936950277137</v>
+        <v>-0.7504936950270665</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001456573300679713</v>
+        <v>0.001456573300680231</v>
       </c>
       <c r="H17" t="n">
-        <v>0.006590736799569702</v>
+        <v>0.006590736799556234</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1913477001707365</v>
+        <v>-0.1913477001707339</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.612105836505838e-13</v>
+        <v>-3.591934838764536e-14</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8770230077025242</v>
+        <v>0.87702300770182</v>
       </c>
     </row>
     <row r="18">
@@ -1063,25 +1063,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.845791139355267</v>
+        <v>-0.8457911393550082</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7611520690270692</v>
+        <v>-0.7611520690276043</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.003139734310674162</v>
+        <v>-0.003139734310674845</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0006683120527781236</v>
+        <v>-0.0006683120527693941</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.05000005721099737</v>
+        <v>-0.05000005721100176</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.899677898334275e-13</v>
+        <v>-4.797347225031697e-14</v>
       </c>
       <c r="K18" t="n">
-        <v>1.137859825078472</v>
+        <v>1.137859825078638</v>
       </c>
     </row>
     <row r="19">
@@ -1098,25 +1098,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8457911393537922</v>
+        <v>-0.8457911393545802</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7611372713163034</v>
+        <v>-0.7611372713168385</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.001559049602196257</v>
+        <v>-0.001559049602196457</v>
       </c>
       <c r="H19" t="n">
-        <v>0.002029479946406675</v>
+        <v>0.00202947994641545</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.05000005721098015</v>
+        <v>-0.05000005721099056</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.900821841067412e-13</v>
+        <v>-4.795316946883113e-14</v>
       </c>
       <c r="K19" t="n">
-        <v>1.137846662706305</v>
+        <v>1.137846662707249</v>
       </c>
     </row>
     <row r="20">
@@ -1133,25 +1133,25 @@
         <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8461134431639535</v>
+        <v>-0.8461134431647414</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7611372713178689</v>
+        <v>-0.7611372713171778</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003139734310674283</v>
+        <v>0.003139734310674613</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00202947994642285</v>
+        <v>0.002029479946420887</v>
       </c>
       <c r="I20" t="n">
-        <v>0.008961453069781296</v>
+        <v>0.008961453069770897</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.900022251312968e-13</v>
+        <v>-4.795187645833391e-14</v>
       </c>
       <c r="K20" t="n">
-        <v>1.138089523026864</v>
+        <v>1.138089523026987</v>
       </c>
     </row>
     <row r="21">
@@ -1168,25 +1168,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8461134431654285</v>
+        <v>-0.8461134431651695</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7611520690286349</v>
+        <v>-0.7611520690279437</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001559049602196137</v>
+        <v>0.001559049602196688</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0006683120527619788</v>
+        <v>-0.0006683120527639328</v>
       </c>
       <c r="I21" t="n">
-        <v>0.008961453069764045</v>
+        <v>0.008961453069759602</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.900474795736123e-13</v>
+        <v>-4.795728302061472e-14</v>
       </c>
       <c r="K21" t="n">
-        <v>1.138096156538405</v>
+        <v>1.138096156537751</v>
       </c>
     </row>
   </sheetData>
@@ -1245,16 +1245,16 @@
         <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>1.138096156538405</v>
+        <v>1.138096156537751</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.8461134431654285</v>
+        <v>-0.8461134431651695</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7611520690286349</v>
+        <v>-0.7611520690279437</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001559049602196137</v>
+        <v>0.001559049602196688</v>
       </c>
     </row>
     <row r="3">
@@ -1267,16 +1267,16 @@
         <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.8461134431654285</v>
+        <v>-0.8461134431651695</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.8461134431654285</v>
+        <v>-0.8461134431651695</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7611520690286349</v>
+        <v>-0.7611520690279437</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001559049602196137</v>
+        <v>0.001559049602196688</v>
       </c>
     </row>
     <row r="4">
@@ -1289,16 +1289,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.7611520690286349</v>
+        <v>-0.7611520690279437</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8461134431654285</v>
+        <v>-0.8461134431651695</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7611520690286349</v>
+        <v>-0.7611520690279437</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001559049602196137</v>
+        <v>0.001559049602196688</v>
       </c>
     </row>
     <row r="5">
@@ -1308,19 +1308,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003139734310674283</v>
+        <v>-0.003139734310674845</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8461134431639535</v>
+        <v>-0.8457911393550082</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7611372713178689</v>
+        <v>-0.7611520690276043</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003139734310674283</v>
+        <v>-0.003139734310674845</v>
       </c>
     </row>
   </sheetData>
@@ -1379,22 +1379,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.751456014022573</v>
+        <v>2.751456014012857</v>
       </c>
       <c r="C2" t="n">
-        <v>-55.20765387894689</v>
+        <v>-55.20765387894221</v>
       </c>
       <c r="D2" t="n">
-        <v>229.7364853741411</v>
+        <v>229.7364853741738</v>
       </c>
       <c r="E2" t="n">
-        <v>31.46052233895557</v>
+        <v>31.46052233893406</v>
       </c>
       <c r="F2" t="n">
-        <v>7.601256117793246</v>
+        <v>7.601256117753555</v>
       </c>
       <c r="G2" t="n">
-        <v>1.124472132600471e-13</v>
+        <v>2.642825570253907e-14</v>
       </c>
     </row>
     <row r="3">
@@ -1402,22 +1402,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2.75145601398571</v>
+        <v>2.751456014004419</v>
       </c>
       <c r="C3" t="n">
-        <v>55.2076538789229</v>
+        <v>55.2076538789276</v>
       </c>
       <c r="D3" t="n">
-        <v>19.2075062988704</v>
+        <v>19.20750629889254</v>
       </c>
       <c r="E3" t="n">
-        <v>-189.3446060375642</v>
+        <v>-189.3446060375859</v>
       </c>
       <c r="F3" t="n">
-        <v>7.601256117642186</v>
+        <v>7.601256117719164</v>
       </c>
       <c r="G3" t="n">
-        <v>1.125134151497627e-13</v>
+        <v>2.645558510898198e-14</v>
       </c>
     </row>
     <row r="4">
@@ -1425,22 +1425,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>-2.751456014048294</v>
+        <v>-2.751456014029591</v>
       </c>
       <c r="C4" t="n">
-        <v>55.20765387896097</v>
+        <v>55.20765387893758</v>
       </c>
       <c r="D4" t="n">
-        <v>-229.7364853741495</v>
+        <v>-229.7364853741628</v>
       </c>
       <c r="E4" t="n">
-        <v>-189.344606037719</v>
+        <v>-189.344606037625</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.377222810504925</v>
+        <v>-3.37722281042796</v>
       </c>
       <c r="G4" t="n">
-        <v>1.124864943468381e-13</v>
+        <v>2.645939050296207e-14</v>
       </c>
     </row>
     <row r="5">
@@ -1448,22 +1448,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-2.751456014011439</v>
+        <v>-2.751456014021153</v>
       </c>
       <c r="C5" t="n">
-        <v>-55.20765387890883</v>
+        <v>-55.20765387893223</v>
       </c>
       <c r="D5" t="n">
-        <v>-19.20750629886214</v>
+        <v>-19.20750629890353</v>
       </c>
       <c r="E5" t="n">
-        <v>31.4605223388009</v>
+        <v>31.46052233889492</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.377222810353881</v>
+        <v>-3.377222810393567</v>
       </c>
       <c r="G5" t="n">
-        <v>1.12489230509892e-13</v>
+        <v>2.647951435709958e-14</v>
       </c>
     </row>
   </sheetData>
@@ -1606,52 +1606,52 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.001454028388443931</v>
+        <v>-0.001454028388444138</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0002423380647406551</v>
+        <v>-0.0002423380647406897</v>
       </c>
       <c r="H2" t="n">
-        <v>-229.736485374141</v>
+        <v>-229.7364853741738</v>
       </c>
       <c r="I2" t="n">
-        <v>-48467.61294813102</v>
+        <v>-48467.61294813793</v>
       </c>
       <c r="J2" t="n">
-        <v>229.7364853741411</v>
+        <v>229.7364853741738</v>
       </c>
       <c r="K2" t="n">
-        <v>-55.20765387894689</v>
+        <v>-55.20765387894221</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.751456014022573</v>
+        <v>-2.751456014012857</v>
       </c>
       <c r="M2" t="n">
-        <v>1.124472132600471e-13</v>
+        <v>2.642825570253907e-14</v>
       </c>
       <c r="N2" t="n">
-        <v>7.601256117793246</v>
+        <v>7.601256117753555</v>
       </c>
       <c r="O2" t="n">
-        <v>-31.46052233895557</v>
+        <v>-31.46052233893405</v>
       </c>
       <c r="P2" t="n">
-        <v>-229.7364853741411</v>
+        <v>-229.7364853741738</v>
       </c>
       <c r="Q2" t="n">
-        <v>55.20765387894689</v>
+        <v>55.20765387894221</v>
       </c>
       <c r="R2" t="n">
-        <v>2.751456014022573</v>
+        <v>2.751456014012857</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.124472132600471e-13</v>
+        <v>-2.642825570253907e-14</v>
       </c>
       <c r="T2" t="n">
-        <v>8.907479966342192</v>
+        <v>8.907479966323589</v>
       </c>
       <c r="U2" t="n">
-        <v>-299.7854009347257</v>
+        <v>-299.7854009347192</v>
       </c>
     </row>
     <row r="3">
@@ -1673,52 +1673,52 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0001215664955624709</v>
+        <v>-0.000121566495562611</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.026108259374515e-05</v>
+        <v>-2.02610825937685e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>-19.2075062988704</v>
+        <v>-19.20750629889253</v>
       </c>
       <c r="I3" t="n">
-        <v>-4052.216518749029</v>
+        <v>-4052.216518753698</v>
       </c>
       <c r="J3" t="n">
-        <v>19.2075062988704</v>
+        <v>19.20750629889254</v>
       </c>
       <c r="K3" t="n">
-        <v>55.2076538789229</v>
+        <v>55.2076538789276</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.75145601398571</v>
+        <v>-2.751456014004419</v>
       </c>
       <c r="M3" t="n">
-        <v>1.125134151497627e-13</v>
+        <v>2.645558510898198e-14</v>
       </c>
       <c r="N3" t="n">
-        <v>7.601256117642186</v>
+        <v>7.601256117719164</v>
       </c>
       <c r="O3" t="n">
-        <v>189.3446060375642</v>
+        <v>189.3446060375859</v>
       </c>
       <c r="P3" t="n">
-        <v>-19.2075062988704</v>
+        <v>-19.20750629889254</v>
       </c>
       <c r="Q3" t="n">
-        <v>-55.2076538789229</v>
+        <v>-55.2076538789276</v>
       </c>
       <c r="R3" t="n">
-        <v>2.75145601398571</v>
+        <v>2.751456014004419</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.125134151497627e-13</v>
+        <v>-2.645558510898198e-14</v>
       </c>
       <c r="T3" t="n">
-        <v>8.907479966272078</v>
+        <v>8.907479966307353</v>
       </c>
       <c r="U3" t="n">
-        <v>141.9013172359731</v>
+        <v>141.9013172359797</v>
       </c>
     </row>
     <row r="4">
@@ -1740,52 +1740,52 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001454028388443984</v>
+        <v>0.001454028388444068</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000242338064740664</v>
+        <v>0.0002423380647406781</v>
       </c>
       <c r="H4" t="n">
-        <v>229.7364853741495</v>
+        <v>229.7364853741628</v>
       </c>
       <c r="I4" t="n">
-        <v>48467.6129481328</v>
+        <v>48467.61294813561</v>
       </c>
       <c r="J4" t="n">
-        <v>-229.7364853741495</v>
+        <v>-229.7364853741628</v>
       </c>
       <c r="K4" t="n">
-        <v>55.20765387896097</v>
+        <v>55.20765387893758</v>
       </c>
       <c r="L4" t="n">
-        <v>2.751456014048294</v>
+        <v>2.751456014029591</v>
       </c>
       <c r="M4" t="n">
-        <v>1.124864943468381e-13</v>
+        <v>2.645939050296207e-14</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.377222810504925</v>
+        <v>-3.377222810427959</v>
       </c>
       <c r="O4" t="n">
-        <v>189.344606037719</v>
+        <v>189.344606037625</v>
       </c>
       <c r="P4" t="n">
-        <v>229.7364853741495</v>
+        <v>229.7364853741628</v>
       </c>
       <c r="Q4" t="n">
-        <v>-55.20765387896097</v>
+        <v>-55.20765387893758</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.751456014048294</v>
+        <v>-2.751456014029591</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.124864943468381e-13</v>
+        <v>-2.645939050296207e-14</v>
       </c>
       <c r="T4" t="n">
-        <v>-13.13151327378484</v>
+        <v>-13.13151327374959</v>
       </c>
       <c r="U4" t="n">
-        <v>141.9013172360468</v>
+        <v>141.9013172360004</v>
       </c>
     </row>
     <row r="5">
@@ -1807,52 +1807,52 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001215664955624186</v>
+        <v>0.0001215664955626805</v>
       </c>
       <c r="G5" t="n">
-        <v>2.026108259373643e-05</v>
+        <v>2.026108259378009e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>19.20750629886214</v>
+        <v>19.20750629890352</v>
       </c>
       <c r="I5" t="n">
-        <v>4052.216518747287</v>
+        <v>4052.216518756018</v>
       </c>
       <c r="J5" t="n">
-        <v>-19.20750629886214</v>
+        <v>-19.20750629890353</v>
       </c>
       <c r="K5" t="n">
-        <v>-55.20765387890883</v>
+        <v>-55.20765387893223</v>
       </c>
       <c r="L5" t="n">
-        <v>2.751456014011439</v>
+        <v>2.751456014021153</v>
       </c>
       <c r="M5" t="n">
-        <v>1.12489230509892e-13</v>
+        <v>2.647951435709958e-14</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.377222810353881</v>
+        <v>-3.377222810393566</v>
       </c>
       <c r="O5" t="n">
-        <v>-31.4605223388009</v>
+        <v>-31.4605223388949</v>
       </c>
       <c r="P5" t="n">
-        <v>19.20750629886214</v>
+        <v>19.20750629890353</v>
       </c>
       <c r="Q5" t="n">
-        <v>55.20765387890883</v>
+        <v>55.20765387893223</v>
       </c>
       <c r="R5" t="n">
-        <v>-2.751456014011439</v>
+        <v>-2.751456014021153</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.12489230509892e-13</v>
+        <v>-2.647951435709958e-14</v>
       </c>
       <c r="T5" t="n">
-        <v>-13.13151327371476</v>
+        <v>-13.13151327373335</v>
       </c>
       <c r="U5" t="n">
-        <v>-299.7854009346521</v>
+        <v>-299.7854009346985</v>
       </c>
     </row>
     <row r="6">
@@ -1874,52 +1874,52 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0008788182861807735</v>
+        <v>-0.0008788182861810029</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0001464697143634622</v>
+        <v>-0.0001464697143635005</v>
       </c>
       <c r="H6" t="n">
-        <v>-138.8532892165622</v>
+        <v>-138.8532892165985</v>
       </c>
       <c r="I6" t="n">
-        <v>-29293.94287269245</v>
+        <v>-29293.9428727001</v>
       </c>
       <c r="J6" t="n">
-        <v>138.8532892165622</v>
+        <v>138.8532892165985</v>
       </c>
       <c r="K6" t="n">
-        <v>-42.9634944294793</v>
+        <v>-42.9634944294736</v>
       </c>
       <c r="L6" t="n">
-        <v>10.38529125067953</v>
+        <v>10.38529125068932</v>
       </c>
       <c r="M6" t="n">
-        <v>1.752702276334041e-13</v>
+        <v>3.775201647367488e-14</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.206939262112485</v>
+        <v>-4.206939262141617</v>
       </c>
       <c r="O6" t="n">
-        <v>-262.6994518333376</v>
+        <v>-262.6994518333104</v>
       </c>
       <c r="P6" t="n">
-        <v>-138.8532892165622</v>
+        <v>-138.8532892165985</v>
       </c>
       <c r="Q6" t="n">
-        <v>42.9634944294793</v>
+        <v>42.9634944294736</v>
       </c>
       <c r="R6" t="n">
-        <v>-10.38529125067953</v>
+        <v>-10.38529125068932</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.752702276334041e-13</v>
+        <v>-3.775201647367488e-14</v>
       </c>
       <c r="T6" t="n">
-        <v>-58.10480824196471</v>
+        <v>-58.10480824199429</v>
       </c>
       <c r="U6" t="n">
-        <v>4.918485256461651</v>
+        <v>4.918485256468898</v>
       </c>
     </row>
     <row r="7">
@@ -1941,52 +1941,52 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0006687758586765627</v>
+        <v>-0.000668775858676608</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0001114626431127605</v>
+        <v>-0.000111462643112768</v>
       </c>
       <c r="H7" t="n">
-        <v>-105.6665856708969</v>
+        <v>-105.6665856709041</v>
       </c>
       <c r="I7" t="n">
-        <v>-22292.52862255209</v>
+        <v>-22292.5286225536</v>
       </c>
       <c r="J7" t="n">
-        <v>105.6665856708969</v>
+        <v>105.6665856709041</v>
       </c>
       <c r="K7" t="n">
-        <v>42.96349442944967</v>
+        <v>42.96349442945541</v>
       </c>
       <c r="L7" t="n">
-        <v>10.38529125071589</v>
+        <v>10.38529125069712</v>
       </c>
       <c r="M7" t="n">
-        <v>1.750906019389773e-13</v>
+        <v>3.767440976047779e-14</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.206939262224786</v>
+        <v>-4.206939262166223</v>
       </c>
       <c r="O7" t="n">
-        <v>129.9526376503293</v>
+        <v>129.9526376503565</v>
       </c>
       <c r="P7" t="n">
-        <v>-105.6665856708969</v>
+        <v>-105.6665856709041</v>
       </c>
       <c r="Q7" t="n">
-        <v>-42.96349442944967</v>
+        <v>-42.96349442945541</v>
       </c>
       <c r="R7" t="n">
-        <v>-10.38529125071589</v>
+        <v>-10.38529125069712</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.750906019389773e-13</v>
+        <v>-3.767440976047779e-14</v>
       </c>
       <c r="T7" t="n">
-        <v>-58.10480824207055</v>
+        <v>-58.10480824201649</v>
       </c>
       <c r="U7" t="n">
-        <v>127.8283289263687</v>
+        <v>127.8283289263759</v>
       </c>
     </row>
     <row r="8">
@@ -2008,52 +2008,52 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008788182861808262</v>
+        <v>0.000878818286180932</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000146469714363471</v>
+        <v>0.0001464697143634887</v>
       </c>
       <c r="H8" t="n">
-        <v>138.8532892165705</v>
+        <v>138.8532892165873</v>
       </c>
       <c r="I8" t="n">
-        <v>29293.94287269421</v>
+        <v>29293.94287269773</v>
       </c>
       <c r="J8" t="n">
-        <v>-138.8532892165705</v>
+        <v>-138.8532892165873</v>
       </c>
       <c r="K8" t="n">
-        <v>42.96349442948349</v>
+        <v>42.96349442946246</v>
       </c>
       <c r="L8" t="n">
-        <v>-10.38529125065367</v>
+        <v>-10.38529125067246</v>
       </c>
       <c r="M8" t="n">
-        <v>1.752361559046339e-13</v>
+        <v>3.774728020148455e-14</v>
       </c>
       <c r="N8" t="n">
-        <v>26.12743971176449</v>
+        <v>26.12743971182311</v>
       </c>
       <c r="O8" t="n">
-        <v>129.9526376504382</v>
+        <v>129.9526376503774</v>
       </c>
       <c r="P8" t="n">
-        <v>138.8532892165705</v>
+        <v>138.8532892165873</v>
       </c>
       <c r="Q8" t="n">
-        <v>-42.96349442948349</v>
+        <v>-42.96349442946246</v>
       </c>
       <c r="R8" t="n">
-        <v>10.38529125065367</v>
+        <v>10.38529125067246</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.752361559046339e-13</v>
+        <v>-3.774728020148455e-14</v>
       </c>
       <c r="T8" t="n">
-        <v>36.18430779215749</v>
+        <v>36.18430779221164</v>
       </c>
       <c r="U8" t="n">
-        <v>127.8283289264627</v>
+        <v>127.8283289263974</v>
       </c>
     </row>
     <row r="9">
@@ -2075,52 +2075,52 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0006687758586765106</v>
+        <v>0.0006687758586766784</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001114626431127518</v>
+        <v>0.0001114626431127797</v>
       </c>
       <c r="H9" t="n">
-        <v>105.6665856708887</v>
+        <v>105.6665856709152</v>
       </c>
       <c r="I9" t="n">
-        <v>22292.52862255035</v>
+        <v>22292.52862255594</v>
       </c>
       <c r="J9" t="n">
-        <v>-105.6665856708887</v>
+        <v>-105.6665856709152</v>
       </c>
       <c r="K9" t="n">
-        <v>-42.96349442944549</v>
+        <v>-42.96349442946655</v>
       </c>
       <c r="L9" t="n">
-        <v>-10.38529125069003</v>
+        <v>-10.38529125068024</v>
       </c>
       <c r="M9" t="n">
-        <v>1.750110271688143e-13</v>
+        <v>3.772111637843662e-14</v>
       </c>
       <c r="N9" t="n">
-        <v>26.12743971187681</v>
+        <v>26.12743971184766</v>
       </c>
       <c r="O9" t="n">
-        <v>-262.6994518332286</v>
+        <v>-262.6994518332895</v>
       </c>
       <c r="P9" t="n">
-        <v>105.6665856708887</v>
+        <v>105.6665856709152</v>
       </c>
       <c r="Q9" t="n">
-        <v>42.96349442944549</v>
+        <v>42.96349442946655</v>
       </c>
       <c r="R9" t="n">
-        <v>10.38529125069003</v>
+        <v>10.38529125068024</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.750110271688143e-13</v>
+        <v>-3.772111637843662e-14</v>
       </c>
       <c r="T9" t="n">
-        <v>36.18430779226336</v>
+        <v>36.18430779223377</v>
       </c>
       <c r="U9" t="n">
-        <v>4.918485256555641</v>
+        <v>4.918485256490328</v>
       </c>
     </row>
     <row r="10">
@@ -2142,52 +2142,52 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0006993215100614693</v>
+        <v>-0.000699321510061648</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0001165535850102449</v>
+        <v>-0.0001165535850102747</v>
       </c>
       <c r="H10" t="n">
-        <v>-110.4927985897122</v>
+        <v>-110.4927985897404</v>
       </c>
       <c r="I10" t="n">
-        <v>-23310.71700204898</v>
+        <v>-23310.71700205493</v>
       </c>
       <c r="J10" t="n">
-        <v>110.4927985897122</v>
+        <v>110.4927985897404</v>
       </c>
       <c r="K10" t="n">
-        <v>9.383961081545465</v>
+        <v>9.38396108156951</v>
       </c>
       <c r="L10" t="n">
-        <v>-46.7476849124899</v>
+        <v>-46.74768491248135</v>
       </c>
       <c r="M10" t="n">
-        <v>1.709152340672448e-13</v>
+        <v>3.788645412536577e-14</v>
       </c>
       <c r="N10" t="n">
-        <v>135.4653152928859</v>
+        <v>135.4653152928687</v>
       </c>
       <c r="O10" t="n">
-        <v>32.6755577232978</v>
+        <v>32.67555772336971</v>
       </c>
       <c r="P10" t="n">
-        <v>-110.4927985897122</v>
+        <v>-110.4927985897404</v>
       </c>
       <c r="Q10" t="n">
-        <v>-9.383961081545465</v>
+        <v>-9.38396108156951</v>
       </c>
       <c r="R10" t="n">
-        <v>46.7476849124899</v>
+        <v>46.74768491248135</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.709152340672448e-13</v>
+        <v>-3.788645412536577e-14</v>
       </c>
       <c r="T10" t="n">
-        <v>145.0207941820534</v>
+        <v>145.0207941820194</v>
       </c>
       <c r="U10" t="n">
-        <v>23.6282087659751</v>
+        <v>23.62820876604724</v>
       </c>
     </row>
     <row r="11">
@@ -2209,52 +2209,52 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0006662309464408056</v>
+        <v>-0.000666230946440811</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0001110384910734676</v>
+        <v>-0.0001110384910734685</v>
       </c>
       <c r="H11" t="n">
-        <v>-105.2644895376473</v>
+        <v>-105.2644895376481</v>
       </c>
       <c r="I11" t="n">
-        <v>-22207.69821469352</v>
+        <v>-22207.6982146937</v>
       </c>
       <c r="J11" t="n">
-        <v>105.2644895376473</v>
+        <v>105.2644895376481</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.383961081613165</v>
+        <v>-9.38396108158932</v>
       </c>
       <c r="L11" t="n">
-        <v>-46.74768491245524</v>
+        <v>-46.74768491247382</v>
       </c>
       <c r="M11" t="n">
-        <v>1.710610954172968e-13</v>
+        <v>3.7940050285295e-14</v>
       </c>
       <c r="N11" t="n">
-        <v>135.4653152927949</v>
+        <v>135.4653152928447</v>
       </c>
       <c r="O11" t="n">
-        <v>-53.58879393192353</v>
+        <v>-53.58879393185191</v>
       </c>
       <c r="P11" t="n">
-        <v>-105.2644895376473</v>
+        <v>-105.2644895376481</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.383961081613165</v>
+        <v>9.38396108158932</v>
       </c>
       <c r="R11" t="n">
-        <v>46.74768491245524</v>
+        <v>46.74768491247382</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.710610954172968e-13</v>
+        <v>-3.7940050285295e-14</v>
       </c>
       <c r="T11" t="n">
-        <v>145.0207941819365</v>
+        <v>145.0207941819982</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.714972557755459</v>
+        <v>-2.714972557683836</v>
       </c>
     </row>
     <row r="12">
@@ -2276,52 +2276,52 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>0.000699321510061491</v>
+        <v>0.000699321510061586</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0001165535850102485</v>
+        <v>0.0001165535850102643</v>
       </c>
       <c r="H12" t="n">
-        <v>110.4927985897156</v>
+        <v>110.4927985897306</v>
       </c>
       <c r="I12" t="n">
-        <v>23310.7170020497</v>
+        <v>23310.71700205286</v>
       </c>
       <c r="J12" t="n">
-        <v>-110.4927985897156</v>
+        <v>-110.4927985897306</v>
       </c>
       <c r="K12" t="n">
-        <v>-9.383961081568032</v>
+        <v>-9.38396108158247</v>
       </c>
       <c r="L12" t="n">
-        <v>46.7476849125169</v>
+        <v>46.74768491249836</v>
       </c>
       <c r="M12" t="n">
-        <v>1.709011987532788e-13</v>
+        <v>3.7816336496814e-14</v>
       </c>
       <c r="N12" t="n">
-        <v>1.505532197320065</v>
+        <v>1.505532197369803</v>
       </c>
       <c r="O12" t="n">
-        <v>-53.58879393180126</v>
+        <v>-53.58879393183292</v>
       </c>
       <c r="P12" t="n">
-        <v>110.4927985897156</v>
+        <v>110.4927985897306</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.383961081568032</v>
+        <v>9.38396108158247</v>
       </c>
       <c r="R12" t="n">
-        <v>-46.7476849125169</v>
+        <v>-46.74768491249836</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.709011987532788e-13</v>
+        <v>-3.7816336496814e-14</v>
       </c>
       <c r="T12" t="n">
-        <v>-281.9916416724216</v>
+        <v>-281.99164167236</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.714972557606814</v>
+        <v>-2.714972557661781</v>
       </c>
     </row>
     <row r="13">
@@ -2343,52 +2343,52 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0006662309464407836</v>
+        <v>0.0006662309464408723</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0001110384910734639</v>
+        <v>0.0001110384910734787</v>
       </c>
       <c r="H13" t="n">
-        <v>105.2644895376438</v>
+        <v>105.2644895376578</v>
       </c>
       <c r="I13" t="n">
-        <v>22207.69821469278</v>
+        <v>22207.69821469574</v>
       </c>
       <c r="J13" t="n">
-        <v>-105.2644895376438</v>
+        <v>-105.2644895376578</v>
       </c>
       <c r="K13" t="n">
-        <v>9.383961081590712</v>
+        <v>9.383961081576246</v>
       </c>
       <c r="L13" t="n">
-        <v>46.74768491248219</v>
+        <v>46.74768491249078</v>
       </c>
       <c r="M13" t="n">
-        <v>1.713298650191092e-13</v>
+        <v>3.803136082930058e-14</v>
       </c>
       <c r="N13" t="n">
-        <v>1.505532197411242</v>
+        <v>1.505532197393904</v>
       </c>
       <c r="O13" t="n">
-        <v>32.6755577234203</v>
+        <v>32.67555772338847</v>
       </c>
       <c r="P13" t="n">
-        <v>105.2644895376438</v>
+        <v>105.2644895376578</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.383961081590712</v>
+        <v>-9.383961081576246</v>
       </c>
       <c r="R13" t="n">
-        <v>-46.74768491248219</v>
+        <v>-46.74768491249078</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.713298650191092e-13</v>
+        <v>-3.803136082930058e-14</v>
       </c>
       <c r="T13" t="n">
-        <v>-281.9916416723045</v>
+        <v>-281.9916416723386</v>
       </c>
       <c r="U13" t="n">
-        <v>23.62820876612409</v>
+        <v>23.62820876606884</v>
       </c>
     </row>
     <row r="14">
@@ -2410,52 +2410,52 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0001075661259879882</v>
+        <v>-0.0001075661259880563</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.79276876646647e-05</v>
+        <v>-1.792768766467605e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>-16.99544790610213</v>
+        <v>-16.99544790611289</v>
       </c>
       <c r="I14" t="n">
-        <v>-3585.537532932939</v>
+        <v>-3585.537532935209</v>
       </c>
       <c r="J14" t="n">
-        <v>16.99544790610213</v>
+        <v>16.99544790611293</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.753528725754137</v>
+        <v>-1.753528725748197</v>
       </c>
       <c r="L14" t="n">
-        <v>-38.19300150410469</v>
+        <v>-38.19300150411129</v>
       </c>
       <c r="M14" t="n">
-        <v>8.204488071905921e-14</v>
+        <v>3.44731562570147e-14</v>
       </c>
       <c r="N14" t="n">
-        <v>130.0609637273842</v>
+        <v>130.0609637274092</v>
       </c>
       <c r="O14" t="n">
-        <v>-10.63228232796507</v>
+        <v>-10.63228232795814</v>
       </c>
       <c r="P14" t="n">
-        <v>-16.99544790610213</v>
+        <v>-16.99544790611293</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.753528725754137</v>
+        <v>1.753528725748197</v>
       </c>
       <c r="R14" t="n">
-        <v>38.19300150410469</v>
+        <v>38.19300150411129</v>
       </c>
       <c r="S14" t="n">
-        <v>-8.204488071905921e-14</v>
+        <v>-3.44731562570147e-14</v>
       </c>
       <c r="T14" t="n">
-        <v>99.09704529724391</v>
+        <v>99.09704529725843</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1111099734400796</v>
+        <v>0.111109973468956</v>
       </c>
     </row>
     <row r="15">
@@ -2477,52 +2477,52 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0001024763015164182</v>
+        <v>-0.0001024763015164266</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.707938358606969e-05</v>
+        <v>-1.70793835860711e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>-16.19125563959407</v>
+        <v>-16.19125563959541</v>
       </c>
       <c r="I15" t="n">
-        <v>-3415.876717213939</v>
+        <v>-3415.876717214221</v>
       </c>
       <c r="J15" t="n">
-        <v>16.19125563959406</v>
+        <v>16.19125563959543</v>
       </c>
       <c r="K15" t="n">
-        <v>1.753528725728103</v>
+        <v>1.753528725734071</v>
       </c>
       <c r="L15" t="n">
-        <v>-38.19300150409149</v>
+        <v>-38.19300150409987</v>
       </c>
       <c r="M15" t="n">
-        <v>8.233802687468803e-14</v>
+        <v>3.441205256422615e-14</v>
       </c>
       <c r="N15" t="n">
-        <v>130.0609637273625</v>
+        <v>130.0609637273784</v>
       </c>
       <c r="O15" t="n">
-        <v>7.415513261833325</v>
+        <v>7.415513261840374</v>
       </c>
       <c r="P15" t="n">
-        <v>-16.19125563959406</v>
+        <v>-16.19125563959543</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.753528725728103</v>
+        <v>-1.753528725734071</v>
       </c>
       <c r="R15" t="n">
-        <v>38.19300150409149</v>
+        <v>38.19300150409987</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.233802687468803e-14</v>
+        <v>-3.441205256422615e-14</v>
       </c>
       <c r="T15" t="n">
-        <v>99.09704529718621</v>
+        <v>99.0970452972208</v>
       </c>
       <c r="U15" t="n">
-        <v>3.10565909253512</v>
+        <v>3.10565909256411</v>
       </c>
     </row>
     <row r="16">
@@ -2544,52 +2544,52 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0001075661259879821</v>
+        <v>0.0001075661259880263</v>
       </c>
       <c r="G16" t="n">
-        <v>1.792768766466369e-05</v>
+        <v>1.792768766467106e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>16.99544790610117</v>
+        <v>16.99544790610816</v>
       </c>
       <c r="I16" t="n">
-        <v>3585.537532932737</v>
+        <v>3585.537532934211</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.99544790610116</v>
+        <v>-16.99544790610815</v>
       </c>
       <c r="K16" t="n">
-        <v>1.753528725738448</v>
+        <v>1.75352872573896</v>
       </c>
       <c r="L16" t="n">
-        <v>38.19300150413709</v>
+        <v>38.19300150412879</v>
       </c>
       <c r="M16" t="n">
-        <v>8.215171483047837e-14</v>
+        <v>3.445541041092048e-14</v>
       </c>
       <c r="N16" t="n">
-        <v>-262.8077779103638</v>
+        <v>-262.8077779103483</v>
       </c>
       <c r="O16" t="n">
-        <v>7.415513261841625</v>
+        <v>7.415513261851743</v>
       </c>
       <c r="P16" t="n">
-        <v>16.99544790610116</v>
+        <v>16.99544790610815</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.753528725738448</v>
+        <v>-1.75352872573896</v>
       </c>
       <c r="R16" t="n">
-        <v>-38.19300150413709</v>
+        <v>-38.19300150412879</v>
       </c>
       <c r="S16" t="n">
-        <v>-8.215171483047837e-14</v>
+        <v>-3.445541041092048e-14</v>
       </c>
       <c r="T16" t="n">
-        <v>33.64976888554114</v>
+        <v>33.64976888557555</v>
       </c>
       <c r="U16" t="n">
-        <v>3.105659092589121</v>
+        <v>3.105659092582187</v>
       </c>
     </row>
     <row r="17">
@@ -2611,52 +2611,52 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0001024763015164238</v>
+        <v>0.000102476301516457</v>
       </c>
       <c r="G17" t="n">
-        <v>1.707938358607064e-05</v>
+        <v>1.707938358607617e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>16.19125563959496</v>
+        <v>16.1912556396002</v>
       </c>
       <c r="I17" t="n">
-        <v>3415.876717214127</v>
+        <v>3415.876717215232</v>
       </c>
       <c r="J17" t="n">
-        <v>-16.19125563959497</v>
+        <v>-16.1912556396002</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.75352872574382</v>
+        <v>-1.75352872574328</v>
       </c>
       <c r="L17" t="n">
-        <v>38.19300150412386</v>
+        <v>38.19300150411733</v>
       </c>
       <c r="M17" t="n">
-        <v>8.207424224246545e-14</v>
+        <v>3.426181395537433e-14</v>
       </c>
       <c r="N17" t="n">
-        <v>-262.8077779103419</v>
+        <v>-262.8077779103172</v>
       </c>
       <c r="O17" t="n">
-        <v>-10.63228232795689</v>
+        <v>-10.63228232794665</v>
       </c>
       <c r="P17" t="n">
-        <v>16.19125563959497</v>
+        <v>16.1912556396002</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.75352872574382</v>
+        <v>1.75352872574328</v>
       </c>
       <c r="R17" t="n">
-        <v>-38.19300150412386</v>
+        <v>-38.19300150411733</v>
       </c>
       <c r="S17" t="n">
-        <v>-8.207424224246545e-14</v>
+        <v>-3.426181395537433e-14</v>
       </c>
       <c r="T17" t="n">
-        <v>33.64976888559887</v>
+        <v>33.64976888561318</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1111099734938534</v>
+        <v>0.1111099734872596</v>
       </c>
     </row>
     <row r="18">
@@ -2678,52 +2678,52 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0001033262400799706</v>
+        <v>0.0001033262400798596</v>
       </c>
       <c r="G18" t="n">
-        <v>1.291578000999632e-05</v>
+        <v>1.291578000998245e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>12.24415944947652</v>
+        <v>12.24415944946336</v>
       </c>
       <c r="I18" t="n">
-        <v>2583.156001999265</v>
+        <v>2583.15600199649</v>
       </c>
       <c r="J18" t="n">
-        <v>-12.24415944947395</v>
+        <v>-12.24415944946668</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.747801985947262e-13</v>
+        <v>-3.448352714485736e-13</v>
       </c>
       <c r="L18" t="n">
-        <v>88.6711377647799</v>
+        <v>88.67113776478836</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.167475404545426e-13</v>
+        <v>-2.618521718900091e-14</v>
       </c>
       <c r="N18" t="n">
-        <v>-437.5151472319367</v>
+        <v>-437.5151472319706</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.086242207293253e-12</v>
+        <v>-1.374012015276094e-12</v>
       </c>
       <c r="P18" t="n">
-        <v>12.24415944947395</v>
+        <v>12.24415944946668</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.747801985947262e-13</v>
+        <v>3.448352714485736e-13</v>
       </c>
       <c r="R18" t="n">
-        <v>-88.6711377647799</v>
+        <v>-88.67113776478836</v>
       </c>
       <c r="S18" t="n">
-        <v>1.167475404545426e-13</v>
+        <v>2.618521718900091e-14</v>
       </c>
       <c r="T18" t="n">
-        <v>-271.8539548863024</v>
+        <v>-271.8539548863363</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.111999381464557e-12</v>
+        <v>-1.384670156312495e-12</v>
       </c>
     </row>
     <row r="19">
@@ -2760,37 +2760,37 @@
         <v>13.13674726470185</v>
       </c>
       <c r="K19" t="n">
-        <v>2.629008122312371e-13</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="L19" t="n">
-        <v>2.212058392753398</v>
+        <v>2.212058392776836</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.169619956442602e-13</v>
+        <v>-2.646494134950217e-14</v>
       </c>
       <c r="N19" t="n">
-        <v>-4.700540704047413</v>
+        <v>-4.70054070414116</v>
       </c>
       <c r="O19" t="n">
-        <v>1.023181539494544e-12</v>
+        <v>1.392663762089796e-12</v>
       </c>
       <c r="P19" t="n">
         <v>-13.13674726470185</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.629008122312371e-13</v>
+        <v>-3.410605131648481e-13</v>
       </c>
       <c r="R19" t="n">
-        <v>-2.212058392753398</v>
+        <v>-2.212058392776836</v>
       </c>
       <c r="S19" t="n">
-        <v>1.169619956442602e-13</v>
+        <v>2.646494134950217e-14</v>
       </c>
       <c r="T19" t="n">
-        <v>-12.99592643797977</v>
+        <v>-12.99592643807352</v>
       </c>
       <c r="U19" t="n">
-        <v>1.051603248924948e-12</v>
+        <v>1.392663762089796e-12</v>
       </c>
     </row>
     <row r="20">
@@ -2812,52 +2812,52 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0001033262400798596</v>
+        <v>0.0001033262400799706</v>
       </c>
       <c r="G20" t="n">
-        <v>1.291578000998245e-05</v>
+        <v>1.291578000999632e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>12.24415944946336</v>
+        <v>12.24415944947652</v>
       </c>
       <c r="I20" t="n">
-        <v>2583.15600199649</v>
+        <v>2583.156001999265</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.24415944946668</v>
+        <v>-12.24415944947395</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.771116669464391e-13</v>
+        <v>-3.529398995283373e-13</v>
       </c>
       <c r="L20" t="n">
-        <v>-88.67113776482549</v>
+        <v>-88.67113776479871</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.167677066149508e-13</v>
+        <v>-2.618391614639393e-14</v>
       </c>
       <c r="N20" t="n">
-        <v>271.8539548864848</v>
+        <v>271.8539548863777</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.108002578575906e-12</v>
+        <v>-1.407318706014848e-12</v>
       </c>
       <c r="P20" t="n">
-        <v>12.24415944946668</v>
+        <v>12.24415944947395</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.771116669464391e-13</v>
+        <v>3.529398995283373e-13</v>
       </c>
       <c r="R20" t="n">
-        <v>88.67113776482549</v>
+        <v>88.67113776479871</v>
       </c>
       <c r="S20" t="n">
-        <v>1.167677066149508e-13</v>
+        <v>2.618391614639393e-14</v>
       </c>
       <c r="T20" t="n">
-        <v>437.515147232119</v>
+        <v>437.515147232012</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.109334846205456e-12</v>
+        <v>-1.415756401002e-12</v>
       </c>
     </row>
     <row r="21">
@@ -2879,52 +2879,52 @@
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0001108586267063432</v>
+        <v>-0.0001108586267063449</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.38573283382929e-05</v>
+        <v>-1.385732833829312e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>-13.13674726470167</v>
+        <v>-13.13674726470188</v>
       </c>
       <c r="I21" t="n">
-        <v>-2771.46566765858</v>
+        <v>-2771.465667658624</v>
       </c>
       <c r="J21" t="n">
-        <v>13.13674726470174</v>
+        <v>13.13674726470185</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.557953848736361e-13</v>
+        <v>-3.552713678800501e-13</v>
       </c>
       <c r="L21" t="n">
-        <v>2.212058392798944</v>
+        <v>2.212058392787033</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.168509733417977e-13</v>
+        <v>-2.653433028854124e-14</v>
       </c>
       <c r="N21" t="n">
-        <v>-12.99592643816196</v>
+        <v>-12.99592643811431</v>
       </c>
       <c r="O21" t="n">
-        <v>-9.947598300641403e-13</v>
+        <v>-1.392663762089796e-12</v>
       </c>
       <c r="P21" t="n">
-        <v>-13.13674726470174</v>
+        <v>-13.13674726470185</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.557953848736361e-13</v>
+        <v>3.552713678800501e-13</v>
       </c>
       <c r="R21" t="n">
-        <v>-2.212058392798944</v>
+        <v>-2.212058392787033</v>
       </c>
       <c r="S21" t="n">
-        <v>1.168509733417977e-13</v>
+        <v>2.653433028854124e-14</v>
       </c>
       <c r="T21" t="n">
-        <v>-4.700540704229594</v>
+        <v>-4.70054070418195</v>
       </c>
       <c r="U21" t="n">
-        <v>-9.947598300641403e-13</v>
+        <v>-1.449507180950604e-12</v>
       </c>
     </row>
     <row r="22">
@@ -2946,52 +2946,52 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0004417506794183179</v>
+        <v>0.0004417506794179848</v>
       </c>
       <c r="G22" t="n">
-        <v>5.521883492728974e-05</v>
+        <v>5.521883492724811e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>52.34745551107067</v>
+        <v>52.34745551103121</v>
       </c>
       <c r="I22" t="n">
-        <v>11043.76698545795</v>
+        <v>11043.76698544962</v>
       </c>
       <c r="J22" t="n">
-        <v>-52.34745551107335</v>
+        <v>-52.34745551102969</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.643574579356937e-13</v>
+        <v>7.904787935331115e-14</v>
       </c>
       <c r="L22" t="n">
-        <v>13.97919724677558</v>
+        <v>13.97919724679529</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.260797022339943e-13</v>
+        <v>-2.964295475749168e-14</v>
       </c>
       <c r="N22" t="n">
-        <v>-37.59404297975952</v>
+        <v>-37.59404297983836</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.682298827494378e-12</v>
+        <v>3.055333763768431e-13</v>
       </c>
       <c r="P22" t="n">
-        <v>52.34745551107335</v>
+        <v>52.34745551102969</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.643574579356937e-13</v>
+        <v>-7.904787935331115e-14</v>
       </c>
       <c r="R22" t="n">
-        <v>-13.97919724677558</v>
+        <v>-13.97919724679529</v>
       </c>
       <c r="S22" t="n">
-        <v>1.260797022339943e-13</v>
+        <v>2.964295475749168e-14</v>
       </c>
       <c r="T22" t="n">
-        <v>-74.23953499444512</v>
+        <v>-74.23953499452399</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.636113549669972e-12</v>
+        <v>3.268496584496461e-13</v>
       </c>
     </row>
     <row r="23">
@@ -3013,52 +3013,52 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0004821348199423869</v>
+        <v>0.0004821348199423592</v>
       </c>
       <c r="G23" t="n">
-        <v>6.026685249279837e-05</v>
+        <v>6.02668524927949e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>57.13297616317285</v>
+        <v>57.13297616316957</v>
       </c>
       <c r="I23" t="n">
-        <v>12053.37049855967</v>
+        <v>12053.37049855898</v>
       </c>
       <c r="J23" t="n">
-        <v>-57.13297616317323</v>
+        <v>-57.13297616316959</v>
       </c>
       <c r="K23" t="n">
-        <v>6.679101716144942e-13</v>
+        <v>-8.526512829121202e-14</v>
       </c>
       <c r="L23" t="n">
-        <v>14.38129338002526</v>
+        <v>14.38129338005121</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.385142001097961e-13</v>
+        <v>-2.568778523226456e-14</v>
       </c>
       <c r="N23" t="n">
-        <v>-77.36050705072442</v>
+        <v>-77.36050705082822</v>
       </c>
       <c r="O23" t="n">
-        <v>2.728484105318785e-12</v>
+        <v>-3.410605131648481e-13</v>
       </c>
       <c r="P23" t="n">
-        <v>57.13297616317323</v>
+        <v>57.13297616316959</v>
       </c>
       <c r="Q23" t="n">
-        <v>-6.679101716144942e-13</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="R23" t="n">
-        <v>-14.38129338002526</v>
+        <v>-14.38129338005121</v>
       </c>
       <c r="S23" t="n">
-        <v>1.385142001097961e-13</v>
+        <v>2.568778523226456e-14</v>
       </c>
       <c r="T23" t="n">
-        <v>-37.68983998947769</v>
+        <v>-37.68983998958147</v>
       </c>
       <c r="U23" t="n">
-        <v>2.671640686457977e-12</v>
+        <v>-3.410605131648481e-13</v>
       </c>
     </row>
     <row r="24">
@@ -3080,52 +3080,52 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0004417506794180959</v>
+        <v>0.0004417506794182069</v>
       </c>
       <c r="G24" t="n">
-        <v>5.521883492726198e-05</v>
+        <v>5.521883492727586e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>52.34745551104436</v>
+        <v>52.34745551105752</v>
       </c>
       <c r="I24" t="n">
-        <v>11043.7669854524</v>
+        <v>11043.76698545517</v>
       </c>
       <c r="J24" t="n">
-        <v>-52.34745551104425</v>
+        <v>-52.3474555110588</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.45705711121991e-13</v>
+        <v>6.661338147750939e-14</v>
       </c>
       <c r="L24" t="n">
-        <v>-13.97919724682958</v>
+        <v>-13.97919724680534</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.260634392014071e-13</v>
+        <v>-2.969423752025024e-14</v>
       </c>
       <c r="N24" t="n">
-        <v>74.23953499466113</v>
+        <v>74.23953499456417</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.62545540863357e-12</v>
+        <v>2.593480985524366e-13</v>
       </c>
       <c r="P24" t="n">
-        <v>52.34745551104425</v>
+        <v>52.3474555110588</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.45705711121991e-13</v>
+        <v>-6.661338147750939e-14</v>
       </c>
       <c r="R24" t="n">
-        <v>13.97919724682958</v>
+        <v>13.97919724680534</v>
       </c>
       <c r="S24" t="n">
-        <v>1.260634392014071e-13</v>
+        <v>2.969423752025024e-14</v>
       </c>
       <c r="T24" t="n">
-        <v>37.5940429799755</v>
+        <v>37.59404297987852</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.540190280342358e-12</v>
+        <v>2.664535259100376e-13</v>
       </c>
     </row>
     <row r="25">
@@ -3147,52 +3147,52 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0004821348199423453</v>
+        <v>0.0004821348199423592</v>
       </c>
       <c r="G25" t="n">
-        <v>6.026685249279316e-05</v>
+        <v>6.02668524927949e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>57.13297616316792</v>
+        <v>57.13297616316957</v>
       </c>
       <c r="I25" t="n">
-        <v>12053.37049855863</v>
+        <v>12053.37049855898</v>
       </c>
       <c r="J25" t="n">
-        <v>-57.13297616316777</v>
+        <v>-57.13297616316959</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.394884621840902e-13</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="L25" t="n">
-        <v>14.38129338007445</v>
+        <v>14.38129338006276</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.384983707580778e-13</v>
+        <v>-2.565309076274502e-14</v>
       </c>
       <c r="N25" t="n">
-        <v>-37.68983998967445</v>
+        <v>-37.68983998962765</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.614797267597169e-12</v>
+        <v>2.842170943040401e-13</v>
       </c>
       <c r="P25" t="n">
-        <v>57.13297616316777</v>
+        <v>57.13297616316959</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.394884621840902e-13</v>
+        <v>-8.526512829121202e-14</v>
       </c>
       <c r="R25" t="n">
-        <v>-14.38129338007445</v>
+        <v>-14.38129338006276</v>
       </c>
       <c r="S25" t="n">
-        <v>1.384983707580778e-13</v>
+        <v>2.565309076274502e-14</v>
       </c>
       <c r="T25" t="n">
-        <v>-77.36050705092119</v>
+        <v>-77.36050705087436</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.501110429875553e-12</v>
+        <v>2.842170943040401e-13</v>
       </c>
     </row>
     <row r="26">
@@ -3214,52 +3214,52 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-9.398725575804345e-05</v>
+        <v>-9.398725575793243e-05</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.174840696975543e-05</v>
+        <v>-1.174840696974155e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>-11.13748980732815</v>
+        <v>-11.13748980731499</v>
       </c>
       <c r="I26" t="n">
-        <v>-2349.681393951086</v>
+        <v>-2349.68139394831</v>
       </c>
       <c r="J26" t="n">
         <v>11.13748980732635</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.632738637155853e-12</v>
+        <v>1.435296326235402e-12</v>
       </c>
       <c r="L26" t="n">
-        <v>2.212058392761011</v>
+        <v>2.212058392780676</v>
       </c>
       <c r="M26" t="n">
-        <v>-8.879008639439689e-14</v>
+        <v>-3.371608547908522e-14</v>
       </c>
       <c r="N26" t="n">
-        <v>-12.99592643801022</v>
+        <v>-12.99592643808889</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.853095454862341e-11</v>
+        <v>5.74118530494161e-12</v>
       </c>
       <c r="P26" t="n">
         <v>-11.13748980732635</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.632738637155853e-12</v>
+        <v>-1.435296326235402e-12</v>
       </c>
       <c r="R26" t="n">
-        <v>-2.212058392761011</v>
+        <v>-2.212058392780676</v>
       </c>
       <c r="S26" t="n">
-        <v>8.879008639439689e-14</v>
+        <v>3.371608547908522e-14</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.700540704077868</v>
+        <v>-4.700540704156521</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.853095454862341e-11</v>
+        <v>5.74118530494161e-12</v>
       </c>
     </row>
     <row r="27">
@@ -3296,37 +3296,37 @@
         <v>8.554683408379788</v>
       </c>
       <c r="K27" t="n">
-        <v>4.661160346586257e-12</v>
+        <v>-1.4210854715202e-12</v>
       </c>
       <c r="L27" t="n">
-        <v>91.28529229081425</v>
+        <v>91.28529229083352</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.00450897599913e-13</v>
+        <v>-2.122434172857623e-14</v>
       </c>
       <c r="N27" t="n">
-        <v>-275.0817579092991</v>
+        <v>-275.0817579093762</v>
       </c>
       <c r="O27" t="n">
-        <v>1.858779796748422e-11</v>
+        <v>-5.74118530494161e-12</v>
       </c>
       <c r="P27" t="n">
         <v>-8.554683408379788</v>
       </c>
       <c r="Q27" t="n">
-        <v>-4.661160346586257e-12</v>
+        <v>1.4210854715202e-12</v>
       </c>
       <c r="R27" t="n">
-        <v>-91.28529229081425</v>
+        <v>-91.28529229083352</v>
       </c>
       <c r="S27" t="n">
-        <v>1.00450897599913e-13</v>
+        <v>2.122434172857623e-14</v>
       </c>
       <c r="T27" t="n">
-        <v>-455.2005804172148</v>
+        <v>-455.2005804172919</v>
       </c>
       <c r="U27" t="n">
-        <v>1.864464138634503e-11</v>
+        <v>-5.684341886080801e-12</v>
       </c>
     </row>
     <row r="28">
@@ -3348,52 +3348,52 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>-9.398725575793243e-05</v>
+        <v>-9.398725575804345e-05</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.174840696974155e-05</v>
+        <v>-1.174840696975543e-05</v>
       </c>
       <c r="H28" t="n">
-        <v>-11.13748980731499</v>
+        <v>-11.13748980732815</v>
       </c>
       <c r="I28" t="n">
-        <v>-2349.68139394831</v>
+        <v>-2349.681393951086</v>
       </c>
       <c r="J28" t="n">
         <v>11.13748980732635</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.646949491871055e-12</v>
+        <v>1.4210854715202e-12</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.212058392800185</v>
+        <v>-2.212058392789006</v>
       </c>
       <c r="M28" t="n">
-        <v>-8.876233081878127e-14</v>
+        <v>-3.352873534367973e-14</v>
       </c>
       <c r="N28" t="n">
-        <v>4.70054070423453</v>
+        <v>4.700540704189827</v>
       </c>
       <c r="O28" t="n">
-        <v>-1.853095454862341e-11</v>
+        <v>5.712763595511205e-12</v>
       </c>
       <c r="P28" t="n">
         <v>-11.13748980732635</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.646949491871055e-12</v>
+        <v>-1.4210854715202e-12</v>
       </c>
       <c r="R28" t="n">
-        <v>2.212058392800185</v>
+        <v>2.212058392789006</v>
       </c>
       <c r="S28" t="n">
-        <v>8.876233081878127e-14</v>
+        <v>3.352873534367973e-14</v>
       </c>
       <c r="T28" t="n">
-        <v>12.99592643816695</v>
+        <v>12.99592643812222</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.861621967691462e-11</v>
+        <v>5.627498467219993e-12</v>
       </c>
     </row>
     <row r="29">
@@ -3415,52 +3415,52 @@
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>-7.219142116787758e-05</v>
+        <v>-7.219142116776656e-05</v>
       </c>
       <c r="G29" t="n">
-        <v>-9.023927645984697e-06</v>
+        <v>-9.02392764597082e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>-8.554683408393494</v>
+        <v>-8.554683408380336</v>
       </c>
       <c r="I29" t="n">
-        <v>-1804.785529196939</v>
+        <v>-1804.785529194164</v>
       </c>
       <c r="J29" t="n">
-        <v>8.554683408394339</v>
+        <v>8.554683408379788</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.632738637155853e-12</v>
+        <v>1.449507180950604e-12</v>
       </c>
       <c r="L29" t="n">
-        <v>91.28529229084891</v>
+        <v>91.2852922908466</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.005775324136593e-13</v>
+        <v>-2.127811815633152e-14</v>
       </c>
       <c r="N29" t="n">
-        <v>-455.2005804173534</v>
+        <v>-455.2005804173441</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.84741111297626e-11</v>
+        <v>5.854872142663226e-12</v>
       </c>
       <c r="P29" t="n">
-        <v>-8.554683408394339</v>
+        <v>-8.554683408379788</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.632738637155853e-12</v>
+        <v>-1.449507180950604e-12</v>
       </c>
       <c r="R29" t="n">
-        <v>-91.28529229084891</v>
+        <v>-91.2852922908466</v>
       </c>
       <c r="S29" t="n">
-        <v>1.005775324136593e-13</v>
+        <v>2.127811815633152e-14</v>
       </c>
       <c r="T29" t="n">
-        <v>-275.0817579094377</v>
+        <v>-275.0817579094285</v>
       </c>
       <c r="U29" t="n">
-        <v>-1.858779796748422e-11</v>
+        <v>5.798028723802418e-12</v>
       </c>
     </row>
     <row r="30">
@@ -3494,40 +3494,40 @@
         <v>369.9427691461476</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.753528725748765</v>
+        <v>-1.753528725763317</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.732214620162267e-12</v>
+        <v>4.604316927725449e-12</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4020961332469026</v>
+        <v>0.4020961332541386</v>
       </c>
       <c r="M30" t="n">
-        <v>-3.67622599029005e-14</v>
+        <v>-2.389755060505649e-14</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.1111099734400467</v>
+        <v>-0.1111099734689656</v>
       </c>
       <c r="O30" t="n">
-        <v>-1.887201506178826e-11</v>
+        <v>1.84172677109018e-11</v>
       </c>
       <c r="P30" t="n">
-        <v>1.753528725748765</v>
+        <v>1.753528725763317</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.732214620162267e-12</v>
+        <v>-4.604316927725449e-12</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.4020961332469026</v>
+        <v>-0.4020961332541386</v>
       </c>
       <c r="S30" t="n">
-        <v>3.67622599029005e-14</v>
+        <v>2.389755060505649e-14</v>
       </c>
       <c r="T30" t="n">
-        <v>-3.105659092535173</v>
+        <v>-3.105659092564143</v>
       </c>
       <c r="U30" t="n">
-        <v>-1.904254531837068e-11</v>
+        <v>1.84172677109018e-11</v>
       </c>
     </row>
     <row r="31">
@@ -3549,52 +3549,52 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0003223038101612952</v>
+        <v>-0.0003223038101611841</v>
       </c>
       <c r="G31" t="n">
-        <v>-4.02879762701619e-05</v>
+        <v>-4.028797627014802e-05</v>
       </c>
       <c r="H31" t="n">
-        <v>-38.19300150411348</v>
+        <v>-38.19300150410032</v>
       </c>
       <c r="I31" t="n">
-        <v>-8057.595254032378</v>
+        <v>-8057.595254029604</v>
       </c>
       <c r="J31" t="n">
-        <v>38.19300150411436</v>
+        <v>38.19300150409981</v>
       </c>
       <c r="K31" t="n">
-        <v>4.703792910731863e-12</v>
+        <v>-4.632738637155853e-12</v>
       </c>
       <c r="L31" t="n">
-        <v>16.59335177284094</v>
+        <v>16.59335177284954</v>
       </c>
       <c r="M31" t="n">
-        <v>-3.452880342758036e-14</v>
+        <v>-1.160616741602283e-14</v>
       </c>
       <c r="N31" t="n">
-        <v>-99.09704529718634</v>
+        <v>-99.09704529722077</v>
       </c>
       <c r="O31" t="n">
-        <v>1.875832822406664e-11</v>
+        <v>-1.84741111297626e-11</v>
       </c>
       <c r="P31" t="n">
-        <v>-38.19300150411436</v>
+        <v>-38.19300150409981</v>
       </c>
       <c r="Q31" t="n">
-        <v>-4.703792910731863e-12</v>
+        <v>4.632738637155853e-12</v>
       </c>
       <c r="R31" t="n">
-        <v>-16.59335177284094</v>
+        <v>-16.59335177284954</v>
       </c>
       <c r="S31" t="n">
-        <v>3.452880342758036e-14</v>
+        <v>1.160616741602283e-14</v>
       </c>
       <c r="T31" t="n">
-        <v>-33.64976888554113</v>
+        <v>-33.64976888557555</v>
       </c>
       <c r="U31" t="n">
-        <v>1.887201506178826e-11</v>
+        <v>-1.84741111297626e-11</v>
       </c>
     </row>
     <row r="32">
@@ -3631,37 +3631,37 @@
         <v>-1.753528725763317</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.718003765447065e-12</v>
+        <v>4.604316927725449e-12</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.4020961332603305</v>
+        <v>-0.4020961332587234</v>
       </c>
       <c r="M32" t="n">
-        <v>-3.682470994803566e-14</v>
+        <v>-2.410918686912566e-14</v>
       </c>
       <c r="N32" t="n">
-        <v>3.105659092588902</v>
+        <v>3.105659092582468</v>
       </c>
       <c r="O32" t="n">
-        <v>-1.881517164292745e-11</v>
+        <v>1.84741111297626e-11</v>
       </c>
       <c r="P32" t="n">
         <v>1.753528725763317</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.718003765447065e-12</v>
+        <v>-4.604316927725449e-12</v>
       </c>
       <c r="R32" t="n">
-        <v>0.4020961332603305</v>
+        <v>0.4020961332587234</v>
       </c>
       <c r="S32" t="n">
-        <v>3.682470994803566e-14</v>
+        <v>2.410918686912566e-14</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1111099734937417</v>
+        <v>0.1111099734873178</v>
       </c>
       <c r="U32" t="n">
-        <v>-1.887201506178826e-11</v>
+        <v>1.84741111297626e-11</v>
       </c>
     </row>
     <row r="33">
@@ -3683,52 +3683,52 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.0003223038101615172</v>
+        <v>-0.0003223038101612952</v>
       </c>
       <c r="G33" t="n">
-        <v>-4.028797627018965e-05</v>
+        <v>-4.02879762701619e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>-38.19300150413979</v>
+        <v>-38.19300150411348</v>
       </c>
       <c r="I33" t="n">
-        <v>-8057.595254037929</v>
+        <v>-8057.595254032378</v>
       </c>
       <c r="J33" t="n">
-        <v>38.19300150414347</v>
+        <v>38.19300150411436</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.746425474877469e-12</v>
+        <v>4.618527782440651e-12</v>
       </c>
       <c r="L33" t="n">
-        <v>16.59335177285531</v>
+        <v>16.59335177285886</v>
       </c>
       <c r="M33" t="n">
-        <v>-3.446266709505874e-14</v>
+        <v>-1.165777543943314e-14</v>
       </c>
       <c r="N33" t="n">
-        <v>-33.64976888559865</v>
+        <v>-33.64976888561286</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.892885848064907e-11</v>
+        <v>1.84741111297626e-11</v>
       </c>
       <c r="P33" t="n">
-        <v>-38.19300150414347</v>
+        <v>-38.19300150411436</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.746425474877469e-12</v>
+        <v>-4.618527782440651e-12</v>
       </c>
       <c r="R33" t="n">
-        <v>-16.59335177285531</v>
+        <v>-16.59335177285886</v>
       </c>
       <c r="S33" t="n">
-        <v>3.446266709505874e-14</v>
+        <v>1.165777543943314e-14</v>
       </c>
       <c r="T33" t="n">
-        <v>-99.09704529724382</v>
+        <v>-99.09704529725796</v>
       </c>
       <c r="U33" t="n">
-        <v>-1.904254531837068e-11</v>
+        <v>1.84741111297626e-11</v>
       </c>
     </row>
   </sheetData>
@@ -3991,16 +3991,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.001454028388443931</v>
+        <v>-0.001454028388444138</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0002423380647406551</v>
+        <v>-0.0002423380647406897</v>
       </c>
       <c r="H2" t="n">
-        <v>-229.736485374141</v>
+        <v>-229.7364853741738</v>
       </c>
       <c r="I2" t="n">
-        <v>-48467.61294813102</v>
+        <v>-48467.61294813793</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -4021,22 +4021,22 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.008506800363843648</v>
+        <v>-0.008506800363761516</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.3200869679146143</v>
+        <v>-0.3200869679146637</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.001454028388443931</v>
+        <v>-0.001454028388444138</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1813005936457907</v>
+        <v>0.1813005936458008</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008825836814519907</v>
+        <v>0.0008825836814662386</v>
       </c>
       <c r="U2" t="n">
-        <v>-3.950848033461115e-14</v>
+        <v>-9.285603354946163e-15</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -4057,58 +4057,58 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.001454028388443931</v>
+        <v>-0.001454028388444138</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.3200869679146143</v>
+        <v>-0.3200869679146637</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.008506800363843648</v>
+        <v>0.008506800363761516</v>
       </c>
       <c r="AE2" t="n">
-        <v>-3.950848033461115e-14</v>
+        <v>-9.285603354946163e-15</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0008825836814519907</v>
+        <v>0.0008825836814662386</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.1813005936457907</v>
+        <v>-0.1813005936458008</v>
       </c>
       <c r="AH2" t="n">
-        <v>229.7364853741411</v>
+        <v>229.7364853741738</v>
       </c>
       <c r="AI2" t="n">
-        <v>-55.20765387894689</v>
+        <v>-55.20765387894221</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-2.751456014022573</v>
+        <v>-2.751456014012857</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.124472132600471e-13</v>
+        <v>2.642825570253907e-14</v>
       </c>
       <c r="AL2" t="n">
-        <v>7.601256117793246</v>
+        <v>7.601256117753555</v>
       </c>
       <c r="AM2" t="n">
-        <v>-31.46052233895557</v>
+        <v>-31.46052233893405</v>
       </c>
       <c r="AN2" t="n">
-        <v>-229.7364853741411</v>
+        <v>-229.7364853741738</v>
       </c>
       <c r="AO2" t="n">
-        <v>55.20765387894689</v>
+        <v>55.20765387894221</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.751456014022573</v>
+        <v>2.751456014012857</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.124472132600471e-13</v>
+        <v>-2.642825570253907e-14</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.907479966342192</v>
+        <v>8.907479966323589</v>
       </c>
       <c r="AS2" t="n">
-        <v>-299.7854009347257</v>
+        <v>-299.7854009347192</v>
       </c>
     </row>
     <row r="3">
@@ -4130,16 +4130,16 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0001215664955624709</v>
+        <v>-0.000121566495562611</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.026108259374515e-05</v>
+        <v>-2.02610825937685e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>-19.2075062988704</v>
+        <v>-19.20750629889253</v>
       </c>
       <c r="I3" t="n">
-        <v>-4052.216518749029</v>
+        <v>-4052.216518753698</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -4160,22 +4160,22 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.008506800363530128</v>
+        <v>-0.008506800363690507</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3199836416745343</v>
+        <v>-0.3199836416745839</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0001215664955624709</v>
+        <v>-0.000121566495562611</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0320562762172913</v>
+        <v>0.03205627621730149</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008825836815066833</v>
+        <v>0.0008825836814785056</v>
       </c>
       <c r="U3" t="n">
-        <v>-3.953174045802473e-14</v>
+        <v>-9.295205578831507e-15</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -4196,58 +4196,58 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.0001215664955624709</v>
+        <v>-0.000121566495562611</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.3199836416745343</v>
+        <v>-0.3199836416745839</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.008506800363530128</v>
+        <v>0.008506800363690507</v>
       </c>
       <c r="AE3" t="n">
-        <v>-3.953174045802473e-14</v>
+        <v>-9.295205578831507e-15</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0008825836815066833</v>
+        <v>0.0008825836814785056</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.0320562762172913</v>
+        <v>-0.03205627621730149</v>
       </c>
       <c r="AH3" t="n">
-        <v>19.2075062988704</v>
+        <v>19.20750629889254</v>
       </c>
       <c r="AI3" t="n">
-        <v>55.2076538789229</v>
+        <v>55.2076538789276</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-2.75145601398571</v>
+        <v>-2.751456014004419</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.125134151497627e-13</v>
+        <v>2.645558510898198e-14</v>
       </c>
       <c r="AL3" t="n">
-        <v>7.601256117642186</v>
+        <v>7.601256117719164</v>
       </c>
       <c r="AM3" t="n">
-        <v>189.3446060375642</v>
+        <v>189.3446060375859</v>
       </c>
       <c r="AN3" t="n">
-        <v>-19.2075062988704</v>
+        <v>-19.20750629889254</v>
       </c>
       <c r="AO3" t="n">
-        <v>-55.2076538789229</v>
+        <v>-55.2076538789276</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.75145601398571</v>
+        <v>2.751456014004419</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-1.125134151497627e-13</v>
+        <v>-2.645558510898198e-14</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.907479966272078</v>
+        <v>8.907479966307353</v>
       </c>
       <c r="AS3" t="n">
-        <v>141.9013172359731</v>
+        <v>141.9013172359797</v>
       </c>
     </row>
     <row r="4">
@@ -4269,16 +4269,16 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001454028388443984</v>
+        <v>0.001454028388444068</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000242338064740664</v>
+        <v>0.0002423380647406781</v>
       </c>
       <c r="H4" t="n">
-        <v>229.7364853741495</v>
+        <v>229.7364853741628</v>
       </c>
       <c r="I4" t="n">
-        <v>48467.6129481328</v>
+        <v>48467.61294813561</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.008617658990236473</v>
+        <v>-0.008617658990396852</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.319983641674853</v>
+        <v>-0.3199836416746615</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001454028388443984</v>
+        <v>0.001454028388444068</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03205627621734609</v>
+        <v>0.03205627621731389</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.006590736799513456</v>
+        <v>-0.006590736799541642</v>
       </c>
       <c r="U4" t="n">
-        <v>-3.95222817975377e-14</v>
+        <v>-9.296542609148836e-15</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -4335,58 +4335,58 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001454028388443984</v>
+        <v>0.001454028388444068</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.319983641674853</v>
+        <v>-0.3199836416746615</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.008617658990236473</v>
+        <v>0.008617658990396852</v>
       </c>
       <c r="AE4" t="n">
-        <v>-3.95222817975377e-14</v>
+        <v>-9.296542609148836e-15</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.006590736799513456</v>
+        <v>-0.006590736799541642</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.03205627621734609</v>
+        <v>-0.03205627621731389</v>
       </c>
       <c r="AH4" t="n">
-        <v>-229.7364853741495</v>
+        <v>-229.7364853741628</v>
       </c>
       <c r="AI4" t="n">
-        <v>55.20765387896097</v>
+        <v>55.20765387893758</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.751456014048294</v>
+        <v>2.751456014029591</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.124864943468381e-13</v>
+        <v>2.645939050296207e-14</v>
       </c>
       <c r="AL4" t="n">
-        <v>-3.377222810504925</v>
+        <v>-3.377222810427959</v>
       </c>
       <c r="AM4" t="n">
-        <v>189.344606037719</v>
+        <v>189.344606037625</v>
       </c>
       <c r="AN4" t="n">
-        <v>229.7364853741495</v>
+        <v>229.7364853741628</v>
       </c>
       <c r="AO4" t="n">
-        <v>-55.20765387896097</v>
+        <v>-55.20765387893758</v>
       </c>
       <c r="AP4" t="n">
-        <v>-2.751456014048294</v>
+        <v>-2.751456014029591</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.124864943468381e-13</v>
+        <v>-2.645939050296207e-14</v>
       </c>
       <c r="AR4" t="n">
-        <v>-13.13151327378484</v>
+        <v>-13.13151327374959</v>
       </c>
       <c r="AS4" t="n">
-        <v>141.9013172360468</v>
+        <v>141.9013172360004</v>
       </c>
     </row>
     <row r="5">
@@ -4408,16 +4408,16 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001215664955624186</v>
+        <v>0.0001215664955626805</v>
       </c>
       <c r="G5" t="n">
-        <v>2.026108259373643e-05</v>
+        <v>2.026108259378009e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>19.20750629886214</v>
+        <v>19.20750629890352</v>
       </c>
       <c r="I5" t="n">
-        <v>4052.216518747287</v>
+        <v>4052.216518756018</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -4438,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.008617658990549991</v>
+        <v>-0.008617658990467861</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3200869679149329</v>
+        <v>-0.3200869679147415</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001215664955624186</v>
+        <v>0.0001215664955626805</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1813005936458454</v>
+        <v>0.1813005936458132</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.006590736799568158</v>
+        <v>-0.006590736799553908</v>
       </c>
       <c r="U5" t="n">
-        <v>-3.952324315212423e-14</v>
+        <v>-9.303613152494448e-15</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -4474,58 +4474,58 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001215664955624186</v>
+        <v>0.0001215664955626805</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.3200869679149329</v>
+        <v>-0.3200869679147415</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.008617658990549991</v>
+        <v>0.008617658990467861</v>
       </c>
       <c r="AE5" t="n">
-        <v>-3.952324315212423e-14</v>
+        <v>-9.303613152494448e-15</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.006590736799568158</v>
+        <v>-0.006590736799553908</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.1813005936458454</v>
+        <v>-0.1813005936458132</v>
       </c>
       <c r="AH5" t="n">
-        <v>-19.20750629886214</v>
+        <v>-19.20750629890353</v>
       </c>
       <c r="AI5" t="n">
-        <v>-55.20765387890883</v>
+        <v>-55.20765387893223</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.751456014011439</v>
+        <v>2.751456014021153</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.12489230509892e-13</v>
+        <v>2.647951435709958e-14</v>
       </c>
       <c r="AL5" t="n">
-        <v>-3.377222810353881</v>
+        <v>-3.377222810393566</v>
       </c>
       <c r="AM5" t="n">
-        <v>-31.4605223388009</v>
+        <v>-31.4605223388949</v>
       </c>
       <c r="AN5" t="n">
-        <v>19.20750629886214</v>
+        <v>19.20750629890353</v>
       </c>
       <c r="AO5" t="n">
-        <v>55.20765387890883</v>
+        <v>55.20765387893223</v>
       </c>
       <c r="AP5" t="n">
-        <v>-2.751456014011439</v>
+        <v>-2.751456014021153</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.12489230509892e-13</v>
+        <v>-2.647951435709958e-14</v>
       </c>
       <c r="AR5" t="n">
-        <v>-13.13151327371476</v>
+        <v>-13.13151327373335</v>
       </c>
       <c r="AS5" t="n">
-        <v>-299.7854009346521</v>
+        <v>-299.7854009346985</v>
       </c>
     </row>
     <row r="6">
@@ -4547,124 +4547,124 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0008788182861807735</v>
+        <v>-0.0008788182861810029</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0001464697143634622</v>
+        <v>-0.0001464697143635005</v>
       </c>
       <c r="H6" t="n">
-        <v>-138.8532892165622</v>
+        <v>-138.8532892165985</v>
       </c>
       <c r="I6" t="n">
-        <v>-29293.94287269245</v>
+        <v>-29293.9428727001</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.008506800363843648</v>
+        <v>-0.008506800363761516</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3200869679146143</v>
+        <v>-0.3200869679146637</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.001454028388443931</v>
+        <v>-0.001454028388444138</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1813005936457907</v>
+        <v>0.1813005936458008</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0008825836814519907</v>
+        <v>0.0008825836814662386</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.950848033461115e-14</v>
+        <v>-9.285603354946163e-15</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.07036120329910434</v>
+        <v>-0.07036120329889795</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.6912454096229569</v>
+        <v>-0.6912454096231312</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.002332846674624704</v>
+        <v>-0.002332846674625141</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0004776631797100466</v>
+        <v>0.0004776631797337471</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0355348953589887</v>
+        <v>-0.03553489535897476</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.010899116652667e-13</v>
+        <v>-2.254982535921031e-14</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.001454028388443931</v>
+        <v>-0.001454028388444138</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3200869679146143</v>
+        <v>-0.3200869679146637</v>
       </c>
       <c r="X6" t="n">
-        <v>0.008506800363843648</v>
+        <v>0.008506800363761516</v>
       </c>
       <c r="Y6" t="n">
-        <v>-3.950848033461115e-14</v>
+        <v>-9.285603354946163e-15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0008825836814519907</v>
+        <v>0.0008825836814662386</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.1813005936457907</v>
+        <v>-0.1813005936458008</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.002332846674624704</v>
+        <v>-0.002332846674625141</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.6912454096229569</v>
+        <v>-0.6912454096231312</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.07036120329910434</v>
+        <v>0.07036120329889795</v>
       </c>
       <c r="AE6" t="n">
-        <v>-1.010899116652667e-13</v>
+        <v>-2.254982535921031e-14</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.0355348953589887</v>
+        <v>-0.03553489535897476</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0004776631797100466</v>
+        <v>-0.0004776631797337471</v>
       </c>
       <c r="AH6" t="n">
-        <v>138.8532892165622</v>
+        <v>138.8532892165985</v>
       </c>
       <c r="AI6" t="n">
-        <v>-42.9634944294793</v>
+        <v>-42.9634944294736</v>
       </c>
       <c r="AJ6" t="n">
-        <v>10.38529125067953</v>
+        <v>10.38529125068932</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.752702276334041e-13</v>
+        <v>3.775201647367488e-14</v>
       </c>
       <c r="AL6" t="n">
-        <v>-4.206939262112485</v>
+        <v>-4.206939262141617</v>
       </c>
       <c r="AM6" t="n">
-        <v>-262.6994518333376</v>
+        <v>-262.6994518333104</v>
       </c>
       <c r="AN6" t="n">
-        <v>-138.8532892165622</v>
+        <v>-138.8532892165985</v>
       </c>
       <c r="AO6" t="n">
-        <v>42.9634944294793</v>
+        <v>42.9634944294736</v>
       </c>
       <c r="AP6" t="n">
-        <v>-10.38529125067953</v>
+        <v>-10.38529125068932</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.752702276334041e-13</v>
+        <v>-3.775201647367488e-14</v>
       </c>
       <c r="AR6" t="n">
-        <v>-58.10480824196471</v>
+        <v>-58.10480824199429</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.918485256461651</v>
+        <v>4.918485256468898</v>
       </c>
     </row>
     <row r="7">
@@ -4686,124 +4686,124 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0006687758586765627</v>
+        <v>-0.000668775858676608</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0001114626431127605</v>
+        <v>-0.000111462643112768</v>
       </c>
       <c r="H7" t="n">
-        <v>-105.6665856708969</v>
+        <v>-105.6665856709041</v>
       </c>
       <c r="I7" t="n">
-        <v>-22292.52862255209</v>
+        <v>-22292.5286225536</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.008506800363530128</v>
+        <v>-0.008506800363690507</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3199836416745343</v>
+        <v>-0.3199836416745839</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0001215664955624709</v>
+        <v>-0.000121566495562611</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0320562762172913</v>
+        <v>0.03205627621730149</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0008825836815066833</v>
+        <v>0.0008825836814785056</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.953174045802473e-14</v>
+        <v>-9.295205578831507e-15</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.07036120329830216</v>
+        <v>-0.07036120329871685</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.6908036589435386</v>
+        <v>-0.6908036589437132</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.0007903423542390336</v>
+        <v>-0.000790342354239219</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03349161994969708</v>
+        <v>0.0334916199497208</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.03553489535892964</v>
+        <v>-0.03553489535896087</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.010500600582059e-13</v>
+        <v>-2.253216035953992e-14</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0001215664955624709</v>
+        <v>-0.000121566495562611</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3199836416745343</v>
+        <v>-0.3199836416745839</v>
       </c>
       <c r="X7" t="n">
-        <v>0.008506800363530128</v>
+        <v>0.008506800363690507</v>
       </c>
       <c r="Y7" t="n">
-        <v>-3.953174045802473e-14</v>
+        <v>-9.295205578831507e-15</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008825836815066833</v>
+        <v>0.0008825836814785056</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.0320562762172913</v>
+        <v>-0.03205627621730149</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.0007903423542390336</v>
+        <v>-0.000790342354239219</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.6908036589435386</v>
+        <v>-0.6908036589437132</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.07036120329830216</v>
+        <v>0.07036120329871685</v>
       </c>
       <c r="AE7" t="n">
-        <v>-1.010500600582059e-13</v>
+        <v>-2.253216035953992e-14</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.03553489535892964</v>
+        <v>-0.03553489535896087</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.03349161994969708</v>
+        <v>-0.0334916199497208</v>
       </c>
       <c r="AH7" t="n">
-        <v>105.6665856708969</v>
+        <v>105.6665856709041</v>
       </c>
       <c r="AI7" t="n">
-        <v>42.96349442944967</v>
+        <v>42.96349442945541</v>
       </c>
       <c r="AJ7" t="n">
-        <v>10.38529125071589</v>
+        <v>10.38529125069712</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.750906019389773e-13</v>
+        <v>3.767440976047779e-14</v>
       </c>
       <c r="AL7" t="n">
-        <v>-4.206939262224786</v>
+        <v>-4.206939262166223</v>
       </c>
       <c r="AM7" t="n">
-        <v>129.9526376503293</v>
+        <v>129.9526376503565</v>
       </c>
       <c r="AN7" t="n">
-        <v>-105.6665856708969</v>
+        <v>-105.6665856709041</v>
       </c>
       <c r="AO7" t="n">
-        <v>-42.96349442944967</v>
+        <v>-42.96349442945541</v>
       </c>
       <c r="AP7" t="n">
-        <v>-10.38529125071589</v>
+        <v>-10.38529125069712</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.750906019389773e-13</v>
+        <v>-3.767440976047779e-14</v>
       </c>
       <c r="AR7" t="n">
-        <v>-58.10480824207055</v>
+        <v>-58.10480824201649</v>
       </c>
       <c r="AS7" t="n">
-        <v>127.8283289263687</v>
+        <v>127.8283289263759</v>
       </c>
     </row>
     <row r="8">
@@ -4825,124 +4825,124 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008788182861808262</v>
+        <v>0.000878818286180932</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000146469714363471</v>
+        <v>0.0001464697143634887</v>
       </c>
       <c r="H8" t="n">
-        <v>138.8532892165705</v>
+        <v>138.8532892165873</v>
       </c>
       <c r="I8" t="n">
-        <v>29293.94287269421</v>
+        <v>29293.94287269773</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.008617658990236473</v>
+        <v>-0.008617658990396852</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.319983641674853</v>
+        <v>-0.3199836416746615</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001454028388443984</v>
+        <v>0.001454028388444068</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03205627621734609</v>
+        <v>0.03205627621731389</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.006590736799513456</v>
+        <v>-0.006590736799541642</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.95222817975377e-14</v>
+        <v>-9.296542609148836e-15</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.06987906847835977</v>
+        <v>-0.06987906847877449</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.6908036589443535</v>
+        <v>-0.6908036589438927</v>
       </c>
       <c r="R8" t="n">
-        <v>0.00233284667462481</v>
+        <v>0.002332846674625</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03349161994976197</v>
+        <v>0.03349161994973283</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0002044443358872198</v>
+        <v>0.0002044443358560187</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.010917419802469e-13</v>
+        <v>-2.255910051777855e-14</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001454028388443984</v>
+        <v>0.001454028388444068</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.319983641674853</v>
+        <v>-0.3199836416746615</v>
       </c>
       <c r="X8" t="n">
-        <v>0.008617658990236473</v>
+        <v>0.008617658990396852</v>
       </c>
       <c r="Y8" t="n">
-        <v>-3.95222817975377e-14</v>
+        <v>-9.296542609148836e-15</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.006590736799513456</v>
+        <v>-0.006590736799541642</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.03205627621734609</v>
+        <v>-0.03205627621731389</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.00233284667462481</v>
+        <v>0.002332846674625</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.6908036589443535</v>
+        <v>-0.6908036589438927</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.06987906847835977</v>
+        <v>0.06987906847877449</v>
       </c>
       <c r="AE8" t="n">
-        <v>-1.010917419802469e-13</v>
+        <v>-2.255910051777855e-14</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0002044443358872198</v>
+        <v>0.0002044443358560187</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.03349161994976197</v>
+        <v>-0.03349161994973283</v>
       </c>
       <c r="AH8" t="n">
-        <v>-138.8532892165705</v>
+        <v>-138.8532892165873</v>
       </c>
       <c r="AI8" t="n">
-        <v>42.96349442948349</v>
+        <v>42.96349442946246</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-10.38529125065367</v>
+        <v>-10.38529125067246</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.752361559046339e-13</v>
+        <v>3.774728020148455e-14</v>
       </c>
       <c r="AL8" t="n">
-        <v>26.12743971176449</v>
+        <v>26.12743971182311</v>
       </c>
       <c r="AM8" t="n">
-        <v>129.9526376504382</v>
+        <v>129.9526376503774</v>
       </c>
       <c r="AN8" t="n">
-        <v>138.8532892165705</v>
+        <v>138.8532892165873</v>
       </c>
       <c r="AO8" t="n">
-        <v>-42.96349442948349</v>
+        <v>-42.96349442946246</v>
       </c>
       <c r="AP8" t="n">
-        <v>10.38529125065367</v>
+        <v>10.38529125067246</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.752361559046339e-13</v>
+        <v>-3.774728020148455e-14</v>
       </c>
       <c r="AR8" t="n">
-        <v>36.18430779215749</v>
+        <v>36.18430779221164</v>
       </c>
       <c r="AS8" t="n">
-        <v>127.8283289264627</v>
+        <v>127.8283289263974</v>
       </c>
     </row>
     <row r="9">
@@ -4964,124 +4964,124 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0006687758586765106</v>
+        <v>0.0006687758586766784</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001114626431127518</v>
+        <v>0.0001114626431127797</v>
       </c>
       <c r="H9" t="n">
-        <v>105.6665856708887</v>
+        <v>105.6665856709152</v>
       </c>
       <c r="I9" t="n">
-        <v>22292.52862255035</v>
+        <v>22292.52862255594</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.008617658990549991</v>
+        <v>-0.008617658990467861</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3200869679149329</v>
+        <v>-0.3200869679147415</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001215664955624186</v>
+        <v>0.0001215664955626805</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1813005936458454</v>
+        <v>0.1813005936458132</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.006590736799568158</v>
+        <v>-0.006590736799553908</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.952324315212423e-14</v>
+        <v>-9.303613152494448e-15</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.06987906847916199</v>
+        <v>-0.06987906847895559</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.6912454096237716</v>
+        <v>-0.6912454096233109</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0007903423542389292</v>
+        <v>0.000790342354239359</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0004776631797749287</v>
+        <v>0.0004776631797457648</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0002044443358281631</v>
+        <v>0.0002044443358421079</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.010136040492752e-13</v>
+        <v>-2.255697836653975e-14</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0001215664955624186</v>
+        <v>0.0001215664955626805</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3200869679149329</v>
+        <v>-0.3200869679147415</v>
       </c>
       <c r="X9" t="n">
-        <v>0.008617658990549991</v>
+        <v>0.008617658990467861</v>
       </c>
       <c r="Y9" t="n">
-        <v>-3.952324315212423e-14</v>
+        <v>-9.303613152494448e-15</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.006590736799568158</v>
+        <v>-0.006590736799553908</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.1813005936458454</v>
+        <v>-0.1813005936458132</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0007903423542389292</v>
+        <v>0.000790342354239359</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.6912454096237716</v>
+        <v>-0.6912454096233109</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.06987906847916199</v>
+        <v>0.06987906847895559</v>
       </c>
       <c r="AE9" t="n">
-        <v>-1.010136040492752e-13</v>
+        <v>-2.255697836653975e-14</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0002044443358281631</v>
+        <v>0.0002044443358421079</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.0004776631797749287</v>
+        <v>-0.0004776631797457648</v>
       </c>
       <c r="AH9" t="n">
-        <v>-105.6665856708887</v>
+        <v>-105.6665856709152</v>
       </c>
       <c r="AI9" t="n">
-        <v>-42.96349442944549</v>
+        <v>-42.96349442946655</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-10.38529125069003</v>
+        <v>-10.38529125068024</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.750110271688143e-13</v>
+        <v>3.772111637843662e-14</v>
       </c>
       <c r="AL9" t="n">
-        <v>26.12743971187681</v>
+        <v>26.12743971184766</v>
       </c>
       <c r="AM9" t="n">
-        <v>-262.6994518332286</v>
+        <v>-262.6994518332895</v>
       </c>
       <c r="AN9" t="n">
-        <v>105.6665856708887</v>
+        <v>105.6665856709152</v>
       </c>
       <c r="AO9" t="n">
-        <v>42.96349442944549</v>
+        <v>42.96349442946655</v>
       </c>
       <c r="AP9" t="n">
-        <v>10.38529125069003</v>
+        <v>10.38529125068024</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.750110271688143e-13</v>
+        <v>-3.772111637843662e-14</v>
       </c>
       <c r="AR9" t="n">
-        <v>36.18430779226336</v>
+        <v>36.18430779223377</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.918485256555641</v>
+        <v>4.918485256490328</v>
       </c>
     </row>
     <row r="10">
@@ -5103,124 +5103,124 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0006993215100614693</v>
+        <v>-0.000699321510061648</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0001165535850102449</v>
+        <v>-0.0001165535850102747</v>
       </c>
       <c r="H10" t="n">
-        <v>-110.4927985897122</v>
+        <v>-110.4927985897404</v>
       </c>
       <c r="I10" t="n">
-        <v>-23310.71700204898</v>
+        <v>-23310.71700205493</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.07036120329910434</v>
+        <v>-0.07036120329889795</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6912454096229569</v>
+        <v>-0.6912454096231312</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.002332846674624704</v>
+        <v>-0.002332846674625141</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0004776631797100466</v>
+        <v>0.0004776631797337471</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0355348953589887</v>
+        <v>-0.03553489535897476</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.010899116652667e-13</v>
+        <v>-2.254982535921031e-14</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4537190030256291</v>
+        <v>-0.4537190030253384</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.7504936950263797</v>
+        <v>-0.7504936950267934</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.003032168184686173</v>
+        <v>-0.003032168184686789</v>
       </c>
       <c r="S10" t="n">
-        <v>0.006590736799522585</v>
+        <v>0.006590736799546265</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.02907849070414583</v>
+        <v>-0.0290784907041432</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.611412101213256e-13</v>
+        <v>-3.586128221406856e-14</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.002332846674624704</v>
+        <v>-0.002332846674625141</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6912454096229569</v>
+        <v>-0.6912454096231312</v>
       </c>
       <c r="X10" t="n">
-        <v>0.07036120329910434</v>
+        <v>0.07036120329889795</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.010899116652667e-13</v>
+        <v>-2.254982535921031e-14</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.0355348953589887</v>
+        <v>-0.03553489535897476</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.0004776631797100466</v>
+        <v>-0.0004776631797337471</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.003032168184686173</v>
+        <v>-0.003032168184686789</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.7504936950263797</v>
+        <v>-0.7504936950267934</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.4537190030256291</v>
+        <v>0.4537190030253384</v>
       </c>
       <c r="AE10" t="n">
-        <v>-1.611412101213256e-13</v>
+        <v>-3.586128221406856e-14</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.02907849070414583</v>
+        <v>-0.0290784907041432</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.006590736799522585</v>
+        <v>-0.006590736799546265</v>
       </c>
       <c r="AH10" t="n">
-        <v>110.4927985897122</v>
+        <v>110.4927985897404</v>
       </c>
       <c r="AI10" t="n">
-        <v>9.383961081545465</v>
+        <v>9.38396108156951</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-46.7476849124899</v>
+        <v>-46.74768491248135</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.709152340672448e-13</v>
+        <v>3.788645412536577e-14</v>
       </c>
       <c r="AL10" t="n">
-        <v>135.4653152928859</v>
+        <v>135.4653152928687</v>
       </c>
       <c r="AM10" t="n">
-        <v>32.6755577232978</v>
+        <v>32.67555772336971</v>
       </c>
       <c r="AN10" t="n">
-        <v>-110.4927985897122</v>
+        <v>-110.4927985897404</v>
       </c>
       <c r="AO10" t="n">
-        <v>-9.383961081545465</v>
+        <v>-9.38396108156951</v>
       </c>
       <c r="AP10" t="n">
-        <v>46.7476849124899</v>
+        <v>46.74768491248135</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.709152340672448e-13</v>
+        <v>-3.788645412536577e-14</v>
       </c>
       <c r="AR10" t="n">
-        <v>145.0207941820534</v>
+        <v>145.0207941820194</v>
       </c>
       <c r="AS10" t="n">
-        <v>23.6282087659751</v>
+        <v>23.62820876604724</v>
       </c>
     </row>
     <row r="11">
@@ -5242,124 +5242,124 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0006662309464408056</v>
+        <v>-0.000666230946440811</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0001110384910734676</v>
+        <v>-0.0001110384910734685</v>
       </c>
       <c r="H11" t="n">
-        <v>-105.2644895376473</v>
+        <v>-105.2644895376481</v>
       </c>
       <c r="I11" t="n">
-        <v>-22207.69821469352</v>
+        <v>-22207.6982146937</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.07036120329830216</v>
+        <v>-0.07036120329871685</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6908036589435386</v>
+        <v>-0.6908036589437132</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0007903423542390336</v>
+        <v>-0.000790342354239219</v>
       </c>
       <c r="M11" t="n">
-        <v>0.03349161994969708</v>
+        <v>0.0334916199497208</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.03553489535892964</v>
+        <v>-0.03553489535896087</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.010500600582059e-13</v>
+        <v>-2.253216035953992e-14</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537190030243844</v>
+        <v>-0.4537190030250376</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.7505876822821378</v>
+        <v>-0.7505876822825513</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.001456573300679839</v>
+        <v>-0.00145657330068003</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0008825836814975517</v>
+        <v>-0.0008825836814738829</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.02907849070410424</v>
+        <v>-0.0290784907041274</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.611526070967156e-13</v>
+        <v>-3.586244829761654e-14</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0007903423542390336</v>
+        <v>-0.000790342354239219</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6908036589435386</v>
+        <v>-0.6908036589437132</v>
       </c>
       <c r="X11" t="n">
-        <v>0.07036120329830216</v>
+        <v>0.07036120329871685</v>
       </c>
       <c r="Y11" t="n">
-        <v>-1.010500600582059e-13</v>
+        <v>-2.253216035953992e-14</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.03553489535892964</v>
+        <v>-0.03553489535896087</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.03349161994969708</v>
+        <v>-0.0334916199497208</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.001456573300679839</v>
+        <v>-0.00145657330068003</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.7505876822821378</v>
+        <v>-0.7505876822825513</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.4537190030243844</v>
+        <v>0.4537190030250376</v>
       </c>
       <c r="AE11" t="n">
-        <v>-1.611526070967156e-13</v>
+        <v>-3.586244829761654e-14</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.02907849070410424</v>
+        <v>-0.0290784907041274</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0008825836814975517</v>
+        <v>0.0008825836814738829</v>
       </c>
       <c r="AH11" t="n">
-        <v>105.2644895376473</v>
+        <v>105.2644895376481</v>
       </c>
       <c r="AI11" t="n">
-        <v>-9.383961081613165</v>
+        <v>-9.38396108158932</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-46.74768491245524</v>
+        <v>-46.74768491247382</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.710610954172968e-13</v>
+        <v>3.7940050285295e-14</v>
       </c>
       <c r="AL11" t="n">
-        <v>135.4653152927949</v>
+        <v>135.4653152928447</v>
       </c>
       <c r="AM11" t="n">
-        <v>-53.58879393192353</v>
+        <v>-53.58879393185191</v>
       </c>
       <c r="AN11" t="n">
-        <v>-105.2644895376473</v>
+        <v>-105.2644895376481</v>
       </c>
       <c r="AO11" t="n">
-        <v>9.383961081613165</v>
+        <v>9.38396108158932</v>
       </c>
       <c r="AP11" t="n">
-        <v>46.74768491245524</v>
+        <v>46.74768491247382</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.710610954172968e-13</v>
+        <v>-3.7940050285295e-14</v>
       </c>
       <c r="AR11" t="n">
-        <v>145.0207941819365</v>
+        <v>145.0207941819982</v>
       </c>
       <c r="AS11" t="n">
-        <v>-2.714972557755459</v>
+        <v>-2.714972557683836</v>
       </c>
     </row>
     <row r="12">
@@ -5381,124 +5381,124 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>0.000699321510061491</v>
+        <v>0.000699321510061586</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0001165535850102485</v>
+        <v>0.0001165535850102643</v>
       </c>
       <c r="H12" t="n">
-        <v>110.4927985897156</v>
+        <v>110.4927985897306</v>
       </c>
       <c r="I12" t="n">
-        <v>23310.7170020497</v>
+        <v>23310.71700205286</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.06987906847835977</v>
+        <v>-0.06987906847877449</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6908036589443535</v>
+        <v>-0.6908036589438927</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00233284667462481</v>
+        <v>0.002332846674625</v>
       </c>
       <c r="M12" t="n">
-        <v>0.03349161994976197</v>
+        <v>0.03349161994973283</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0002044443358872198</v>
+        <v>0.0002044443358560187</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.010917419802469e-13</v>
+        <v>-2.255910051777855e-14</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537911944455522</v>
+        <v>-0.4537911944462054</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.7505876822834716</v>
+        <v>-0.7505876822828246</v>
       </c>
       <c r="R12" t="n">
-        <v>0.003032168184686301</v>
+        <v>0.003032168184686586</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0008825836814504936</v>
+        <v>-0.0008825836814639399</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1913477001706949</v>
+        <v>-0.1913477001707182</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.611381091097773e-13</v>
+        <v>-3.584592144909157e-14</v>
       </c>
       <c r="V12" t="n">
-        <v>0.00233284667462481</v>
+        <v>0.002332846674625</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6908036589443535</v>
+        <v>-0.6908036589438927</v>
       </c>
       <c r="X12" t="n">
-        <v>0.06987906847835977</v>
+        <v>0.06987906847877449</v>
       </c>
       <c r="Y12" t="n">
-        <v>-1.010917419802469e-13</v>
+        <v>-2.255910051777855e-14</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0002044443358872198</v>
+        <v>0.0002044443358560187</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.03349161994976197</v>
+        <v>-0.03349161994973283</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.003032168184686301</v>
+        <v>0.003032168184686586</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.7505876822834716</v>
+        <v>-0.7505876822828246</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.4537911944455522</v>
+        <v>0.4537911944462054</v>
       </c>
       <c r="AE12" t="n">
-        <v>-1.611381091097773e-13</v>
+        <v>-3.584592144909157e-14</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.1913477001706949</v>
+        <v>-0.1913477001707182</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0008825836814504936</v>
+        <v>0.0008825836814639399</v>
       </c>
       <c r="AH12" t="n">
-        <v>-110.4927985897156</v>
+        <v>-110.4927985897306</v>
       </c>
       <c r="AI12" t="n">
-        <v>-9.383961081568032</v>
+        <v>-9.38396108158247</v>
       </c>
       <c r="AJ12" t="n">
-        <v>46.7476849125169</v>
+        <v>46.74768491249836</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.709011987532788e-13</v>
+        <v>3.7816336496814e-14</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.505532197320065</v>
+        <v>1.505532197369803</v>
       </c>
       <c r="AM12" t="n">
-        <v>-53.58879393180126</v>
+        <v>-53.58879393183292</v>
       </c>
       <c r="AN12" t="n">
-        <v>110.4927985897156</v>
+        <v>110.4927985897306</v>
       </c>
       <c r="AO12" t="n">
-        <v>9.383961081568032</v>
+        <v>9.38396108158247</v>
       </c>
       <c r="AP12" t="n">
-        <v>-46.7476849125169</v>
+        <v>-46.74768491249836</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.709011987532788e-13</v>
+        <v>-3.7816336496814e-14</v>
       </c>
       <c r="AR12" t="n">
-        <v>-281.9916416724216</v>
+        <v>-281.99164167236</v>
       </c>
       <c r="AS12" t="n">
-        <v>-2.714972557606814</v>
+        <v>-2.714972557661781</v>
       </c>
     </row>
     <row r="13">
@@ -5520,124 +5520,124 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0006662309464407836</v>
+        <v>0.0006662309464408723</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0001110384910734639</v>
+        <v>0.0001110384910734787</v>
       </c>
       <c r="H13" t="n">
-        <v>105.2644895376438</v>
+        <v>105.2644895376578</v>
       </c>
       <c r="I13" t="n">
-        <v>22207.69821469278</v>
+        <v>22207.69821469574</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.06987906847916199</v>
+        <v>-0.06987906847895559</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6912454096237716</v>
+        <v>-0.6912454096233109</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0007903423542389292</v>
+        <v>0.000790342354239359</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0004776631797749287</v>
+        <v>0.0004776631797457648</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0002044443358281631</v>
+        <v>0.0002044443358421079</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.010136040492752e-13</v>
+        <v>-2.255697836653975e-14</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.453791194446797</v>
+        <v>-0.4537911944465061</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.7504936950277137</v>
+        <v>-0.7504936950270665</v>
       </c>
       <c r="R13" t="n">
-        <v>0.001456573300679713</v>
+        <v>0.001456573300680231</v>
       </c>
       <c r="S13" t="n">
-        <v>0.006590736799569702</v>
+        <v>0.006590736799556234</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1913477001707365</v>
+        <v>-0.1913477001707339</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.612105836505838e-13</v>
+        <v>-3.591934838764536e-14</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0007903423542389292</v>
+        <v>0.000790342354239359</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.6912454096237716</v>
+        <v>-0.6912454096233109</v>
       </c>
       <c r="X13" t="n">
-        <v>0.06987906847916199</v>
+        <v>0.06987906847895559</v>
       </c>
       <c r="Y13" t="n">
-        <v>-1.010136040492752e-13</v>
+        <v>-2.255697836653975e-14</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0002044443358281631</v>
+        <v>0.0002044443358421079</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.0004776631797749287</v>
+        <v>-0.0004776631797457648</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.001456573300679713</v>
+        <v>0.001456573300680231</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.7504936950277137</v>
+        <v>-0.7504936950270665</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.453791194446797</v>
+        <v>0.4537911944465061</v>
       </c>
       <c r="AE13" t="n">
-        <v>-1.612105836505838e-13</v>
+        <v>-3.591934838764536e-14</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.1913477001707365</v>
+        <v>-0.1913477001707339</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.006590736799569702</v>
+        <v>-0.006590736799556234</v>
       </c>
       <c r="AH13" t="n">
-        <v>-105.2644895376438</v>
+        <v>-105.2644895376578</v>
       </c>
       <c r="AI13" t="n">
-        <v>9.383961081590712</v>
+        <v>9.383961081576246</v>
       </c>
       <c r="AJ13" t="n">
-        <v>46.74768491248219</v>
+        <v>46.74768491249078</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.713298650191092e-13</v>
+        <v>3.803136082930058e-14</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.505532197411242</v>
+        <v>1.505532197393904</v>
       </c>
       <c r="AM13" t="n">
-        <v>32.6755577234203</v>
+        <v>32.67555772338847</v>
       </c>
       <c r="AN13" t="n">
-        <v>105.2644895376438</v>
+        <v>105.2644895376578</v>
       </c>
       <c r="AO13" t="n">
-        <v>-9.383961081590712</v>
+        <v>-9.383961081576246</v>
       </c>
       <c r="AP13" t="n">
-        <v>-46.74768491248219</v>
+        <v>-46.74768491249078</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-1.713298650191092e-13</v>
+        <v>-3.803136082930058e-14</v>
       </c>
       <c r="AR13" t="n">
-        <v>-281.9916416723045</v>
+        <v>-281.9916416723386</v>
       </c>
       <c r="AS13" t="n">
-        <v>23.62820876612409</v>
+        <v>23.62820876606884</v>
       </c>
     </row>
     <row r="14">
@@ -5659,124 +5659,124 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0001075661259879882</v>
+        <v>-0.0001075661259880563</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.79276876646647e-05</v>
+        <v>-1.792768766467605e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>-16.99544790610213</v>
+        <v>-16.99544790611289</v>
       </c>
       <c r="I14" t="n">
-        <v>-3585.537532932939</v>
+        <v>-3585.537532935209</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4537190030256291</v>
+        <v>-0.4537190030253384</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7504936950263797</v>
+        <v>-0.7504936950267934</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.003032168184686173</v>
+        <v>-0.003032168184686789</v>
       </c>
       <c r="M14" t="n">
-        <v>0.006590736799522585</v>
+        <v>0.006590736799546265</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.02907849070414583</v>
+        <v>-0.0290784907041432</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.611412101213256e-13</v>
+        <v>-3.586128221406856e-14</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.845791139355267</v>
+        <v>-0.8457911393550082</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.7611520690270692</v>
+        <v>-0.7611520690276043</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.003139734310674162</v>
+        <v>-0.003139734310674845</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0006683120527781236</v>
+        <v>-0.0006683120527693941</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.05000005721099737</v>
+        <v>-0.05000005721100176</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.899677898334275e-13</v>
+        <v>-4.797347225031697e-14</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.003032168184686173</v>
+        <v>-0.003032168184686789</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.7504936950263797</v>
+        <v>-0.7504936950267934</v>
       </c>
       <c r="X14" t="n">
-        <v>0.4537190030256291</v>
+        <v>0.4537190030253384</v>
       </c>
       <c r="Y14" t="n">
-        <v>-1.611412101213256e-13</v>
+        <v>-3.586128221406856e-14</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.02907849070414583</v>
+        <v>-0.0290784907041432</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.006590736799522585</v>
+        <v>-0.006590736799546265</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.003139734310674162</v>
+        <v>-0.003139734310674845</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.7611520690270692</v>
+        <v>-0.7611520690276043</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.845791139355267</v>
+        <v>0.8457911393550082</v>
       </c>
       <c r="AE14" t="n">
-        <v>-1.899677898334275e-13</v>
+        <v>-4.797347225031697e-14</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.05000005721099737</v>
+        <v>-0.05000005721100176</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0006683120527781236</v>
+        <v>0.0006683120527693941</v>
       </c>
       <c r="AH14" t="n">
-        <v>16.99544790610213</v>
+        <v>16.99544790611293</v>
       </c>
       <c r="AI14" t="n">
-        <v>-1.753528725754137</v>
+        <v>-1.753528725748197</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-38.19300150410469</v>
+        <v>-38.19300150411129</v>
       </c>
       <c r="AK14" t="n">
-        <v>8.204488071905921e-14</v>
+        <v>3.44731562570147e-14</v>
       </c>
       <c r="AL14" t="n">
-        <v>130.0609637273842</v>
+        <v>130.0609637274092</v>
       </c>
       <c r="AM14" t="n">
-        <v>-10.63228232796507</v>
+        <v>-10.63228232795814</v>
       </c>
       <c r="AN14" t="n">
-        <v>-16.99544790610213</v>
+        <v>-16.99544790611293</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.753528725754137</v>
+        <v>1.753528725748197</v>
       </c>
       <c r="AP14" t="n">
-        <v>38.19300150410469</v>
+        <v>38.19300150411129</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-8.204488071905921e-14</v>
+        <v>-3.44731562570147e-14</v>
       </c>
       <c r="AR14" t="n">
-        <v>99.09704529724391</v>
+        <v>99.09704529725843</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.1111099734400796</v>
+        <v>0.111109973468956</v>
       </c>
     </row>
     <row r="15">
@@ -5798,124 +5798,124 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0001024763015164182</v>
+        <v>-0.0001024763015164266</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.707938358606969e-05</v>
+        <v>-1.70793835860711e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>-16.19125563959407</v>
+        <v>-16.19125563959541</v>
       </c>
       <c r="I15" t="n">
-        <v>-3415.876717213939</v>
+        <v>-3415.876717214221</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4537190030243844</v>
+        <v>-0.4537190030250376</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7505876822821378</v>
+        <v>-0.7505876822825513</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.001456573300679839</v>
+        <v>-0.00145657330068003</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0008825836814975517</v>
+        <v>-0.0008825836814738829</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.02907849070410424</v>
+        <v>-0.0290784907041274</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.611526070967156e-13</v>
+        <v>-3.586244829761654e-14</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.8457911393537922</v>
+        <v>-0.8457911393545802</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.7611372713163034</v>
+        <v>-0.7611372713168385</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.001559049602196257</v>
+        <v>-0.001559049602196457</v>
       </c>
       <c r="S15" t="n">
-        <v>0.002029479946406675</v>
+        <v>0.00202947994641545</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.05000005721098015</v>
+        <v>-0.05000005721099056</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.900821841067412e-13</v>
+        <v>-4.795316946883113e-14</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.001456573300679839</v>
+        <v>-0.00145657330068003</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7505876822821378</v>
+        <v>-0.7505876822825513</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4537190030243844</v>
+        <v>0.4537190030250376</v>
       </c>
       <c r="Y15" t="n">
-        <v>-1.611526070967156e-13</v>
+        <v>-3.586244829761654e-14</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.02907849070410424</v>
+        <v>-0.0290784907041274</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0008825836814975517</v>
+        <v>0.0008825836814738829</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.001559049602196257</v>
+        <v>-0.001559049602196457</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.7611372713163034</v>
+        <v>-0.7611372713168385</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.8457911393537922</v>
+        <v>0.8457911393545802</v>
       </c>
       <c r="AE15" t="n">
-        <v>-1.900821841067412e-13</v>
+        <v>-4.795316946883113e-14</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.05000005721098015</v>
+        <v>-0.05000005721099056</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.002029479946406675</v>
+        <v>-0.00202947994641545</v>
       </c>
       <c r="AH15" t="n">
-        <v>16.19125563959406</v>
+        <v>16.19125563959543</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.753528725728103</v>
+        <v>1.753528725734071</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-38.19300150409149</v>
+        <v>-38.19300150409987</v>
       </c>
       <c r="AK15" t="n">
-        <v>8.233802687468803e-14</v>
+        <v>3.441205256422615e-14</v>
       </c>
       <c r="AL15" t="n">
-        <v>130.0609637273625</v>
+        <v>130.0609637273784</v>
       </c>
       <c r="AM15" t="n">
-        <v>7.415513261833325</v>
+        <v>7.415513261840374</v>
       </c>
       <c r="AN15" t="n">
-        <v>-16.19125563959406</v>
+        <v>-16.19125563959543</v>
       </c>
       <c r="AO15" t="n">
-        <v>-1.753528725728103</v>
+        <v>-1.753528725734071</v>
       </c>
       <c r="AP15" t="n">
-        <v>38.19300150409149</v>
+        <v>38.19300150409987</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-8.233802687468803e-14</v>
+        <v>-3.441205256422615e-14</v>
       </c>
       <c r="AR15" t="n">
-        <v>99.09704529718621</v>
+        <v>99.0970452972208</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.10565909253512</v>
+        <v>3.10565909256411</v>
       </c>
     </row>
     <row r="16">
@@ -5937,124 +5937,124 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0001075661259879821</v>
+        <v>0.0001075661259880263</v>
       </c>
       <c r="G16" t="n">
-        <v>1.792768766466369e-05</v>
+        <v>1.792768766467106e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>16.99544790610117</v>
+        <v>16.99544790610816</v>
       </c>
       <c r="I16" t="n">
-        <v>3585.537532932737</v>
+        <v>3585.537532934211</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4537911944455522</v>
+        <v>-0.4537911944462054</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7505876822834716</v>
+        <v>-0.7505876822828246</v>
       </c>
       <c r="L16" t="n">
-        <v>0.003032168184686301</v>
+        <v>0.003032168184686586</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0008825836814504936</v>
+        <v>-0.0008825836814639399</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1913477001706949</v>
+        <v>-0.1913477001707182</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.611381091097773e-13</v>
+        <v>-3.584592144909157e-14</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.8461134431639535</v>
+        <v>-0.8461134431647414</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.7611372713178689</v>
+        <v>-0.7611372713171778</v>
       </c>
       <c r="R16" t="n">
-        <v>0.003139734310674283</v>
+        <v>0.003139734310674613</v>
       </c>
       <c r="S16" t="n">
-        <v>0.00202947994642285</v>
+        <v>0.002029479946420887</v>
       </c>
       <c r="T16" t="n">
-        <v>0.008961453069781296</v>
+        <v>0.008961453069770897</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.900022251312968e-13</v>
+        <v>-4.795187645833391e-14</v>
       </c>
       <c r="V16" t="n">
-        <v>0.003032168184686301</v>
+        <v>0.003032168184686586</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7505876822834716</v>
+        <v>-0.7505876822828246</v>
       </c>
       <c r="X16" t="n">
-        <v>0.4537911944455522</v>
+        <v>0.4537911944462054</v>
       </c>
       <c r="Y16" t="n">
-        <v>-1.611381091097773e-13</v>
+        <v>-3.584592144909157e-14</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.1913477001706949</v>
+        <v>-0.1913477001707182</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0008825836814504936</v>
+        <v>0.0008825836814639399</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.003139734310674283</v>
+        <v>0.003139734310674613</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.7611372713178689</v>
+        <v>-0.7611372713171778</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.8461134431639535</v>
+        <v>0.8461134431647414</v>
       </c>
       <c r="AE16" t="n">
-        <v>-1.900022251312968e-13</v>
+        <v>-4.795187645833391e-14</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.008961453069781296</v>
+        <v>0.008961453069770897</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.00202947994642285</v>
+        <v>-0.002029479946420887</v>
       </c>
       <c r="AH16" t="n">
-        <v>-16.99544790610116</v>
+        <v>-16.99544790610815</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.753528725738448</v>
+        <v>1.75352872573896</v>
       </c>
       <c r="AJ16" t="n">
-        <v>38.19300150413709</v>
+        <v>38.19300150412879</v>
       </c>
       <c r="AK16" t="n">
-        <v>8.215171483047837e-14</v>
+        <v>3.445541041092048e-14</v>
       </c>
       <c r="AL16" t="n">
-        <v>-262.8077779103638</v>
+        <v>-262.8077779103483</v>
       </c>
       <c r="AM16" t="n">
-        <v>7.415513261841625</v>
+        <v>7.415513261851743</v>
       </c>
       <c r="AN16" t="n">
-        <v>16.99544790610116</v>
+        <v>16.99544790610815</v>
       </c>
       <c r="AO16" t="n">
-        <v>-1.753528725738448</v>
+        <v>-1.75352872573896</v>
       </c>
       <c r="AP16" t="n">
-        <v>-38.19300150413709</v>
+        <v>-38.19300150412879</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-8.215171483047837e-14</v>
+        <v>-3.445541041092048e-14</v>
       </c>
       <c r="AR16" t="n">
-        <v>33.64976888554114</v>
+        <v>33.64976888557555</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.105659092589121</v>
+        <v>3.105659092582187</v>
       </c>
     </row>
     <row r="17">
@@ -6076,124 +6076,124 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0001024763015164238</v>
+        <v>0.000102476301516457</v>
       </c>
       <c r="G17" t="n">
-        <v>1.707938358607064e-05</v>
+        <v>1.707938358607617e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>16.19125563959496</v>
+        <v>16.1912556396002</v>
       </c>
       <c r="I17" t="n">
-        <v>3415.876717214127</v>
+        <v>3415.876717215232</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.453791194446797</v>
+        <v>-0.4537911944465061</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7504936950277137</v>
+        <v>-0.7504936950270665</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001456573300679713</v>
+        <v>0.001456573300680231</v>
       </c>
       <c r="M17" t="n">
-        <v>0.006590736799569702</v>
+        <v>0.006590736799556234</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1913477001707365</v>
+        <v>-0.1913477001707339</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.612105836505838e-13</v>
+        <v>-3.591934838764536e-14</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.8461134431654285</v>
+        <v>-0.8461134431651695</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.7611520690286349</v>
+        <v>-0.7611520690279437</v>
       </c>
       <c r="R17" t="n">
-        <v>0.001559049602196137</v>
+        <v>0.001559049602196688</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0006683120527619788</v>
+        <v>-0.0006683120527639328</v>
       </c>
       <c r="T17" t="n">
-        <v>0.008961453069764045</v>
+        <v>0.008961453069759602</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.900474795736123e-13</v>
+        <v>-4.795728302061472e-14</v>
       </c>
       <c r="V17" t="n">
-        <v>0.001456573300679713</v>
+        <v>0.001456573300680231</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.7504936950277137</v>
+        <v>-0.7504936950270665</v>
       </c>
       <c r="X17" t="n">
-        <v>0.453791194446797</v>
+        <v>0.4537911944465061</v>
       </c>
       <c r="Y17" t="n">
-        <v>-1.612105836505838e-13</v>
+        <v>-3.591934838764536e-14</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.1913477001707365</v>
+        <v>-0.1913477001707339</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.006590736799569702</v>
+        <v>-0.006590736799556234</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.001559049602196137</v>
+        <v>0.001559049602196688</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.7611520690286349</v>
+        <v>-0.7611520690279437</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.8461134431654285</v>
+        <v>0.8461134431651695</v>
       </c>
       <c r="AE17" t="n">
-        <v>-1.900474795736123e-13</v>
+        <v>-4.795728302061472e-14</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.008961453069764045</v>
+        <v>0.008961453069759602</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0006683120527619788</v>
+        <v>0.0006683120527639328</v>
       </c>
       <c r="AH17" t="n">
-        <v>-16.19125563959497</v>
+        <v>-16.1912556396002</v>
       </c>
       <c r="AI17" t="n">
-        <v>-1.75352872574382</v>
+        <v>-1.75352872574328</v>
       </c>
       <c r="AJ17" t="n">
-        <v>38.19300150412386</v>
+        <v>38.19300150411733</v>
       </c>
       <c r="AK17" t="n">
-        <v>8.207424224246545e-14</v>
+        <v>3.426181395537433e-14</v>
       </c>
       <c r="AL17" t="n">
-        <v>-262.8077779103419</v>
+        <v>-262.8077779103172</v>
       </c>
       <c r="AM17" t="n">
-        <v>-10.63228232795689</v>
+        <v>-10.63228232794665</v>
       </c>
       <c r="AN17" t="n">
-        <v>16.19125563959497</v>
+        <v>16.1912556396002</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.75352872574382</v>
+        <v>1.75352872574328</v>
       </c>
       <c r="AP17" t="n">
-        <v>-38.19300150412386</v>
+        <v>-38.19300150411733</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-8.207424224246545e-14</v>
+        <v>-3.426181395537433e-14</v>
       </c>
       <c r="AR17" t="n">
-        <v>33.64976888559887</v>
+        <v>33.64976888561318</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.1111099734938534</v>
+        <v>0.1111099734872596</v>
       </c>
     </row>
     <row r="18">
@@ -6215,124 +6215,124 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0001033262400799706</v>
+        <v>0.0001033262400798596</v>
       </c>
       <c r="G18" t="n">
-        <v>1.291578000999632e-05</v>
+        <v>1.291578000998245e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>12.24415944947652</v>
+        <v>12.24415944946336</v>
       </c>
       <c r="I18" t="n">
-        <v>2583.156001999265</v>
+        <v>2583.15600199649</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.008506800363843648</v>
+        <v>-0.008506800363761516</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3200869679146143</v>
+        <v>-0.3200869679146637</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.001454028388443931</v>
+        <v>-0.001454028388444138</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1813005936457907</v>
+        <v>0.1813005936458008</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0008825836814519907</v>
+        <v>0.0008825836814662386</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.950848033461115e-14</v>
+        <v>-9.285603354946163e-15</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.008506800363530128</v>
+        <v>-0.008506800363690507</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.3199836416745343</v>
+        <v>-0.3199836416745839</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.0001215664955624709</v>
+        <v>-0.000121566495562611</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0320562762172913</v>
+        <v>0.03205627621730149</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0008825836815066833</v>
+        <v>0.0008825836814785056</v>
       </c>
       <c r="U18" t="n">
-        <v>-3.953174045802473e-14</v>
+        <v>-9.295205578831507e-15</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3200869679146143</v>
+        <v>-0.3200869679146637</v>
       </c>
       <c r="W18" t="n">
-        <v>0.008506800363843648</v>
+        <v>0.008506800363761516</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.001454028388443931</v>
+        <v>-0.001454028388444138</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.0008825836814519907</v>
+        <v>0.0008825836814662386</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.1813005936457907</v>
+        <v>-0.1813005936458008</v>
       </c>
       <c r="AA18" t="n">
-        <v>-3.950848033461115e-14</v>
+        <v>-9.285603354946163e-15</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.3199836416745343</v>
+        <v>-0.3199836416745839</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.008506800363530128</v>
+        <v>0.008506800363690507</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.0001215664955624709</v>
+        <v>-0.000121566495562611</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.0008825836815066833</v>
+        <v>0.0008825836814785056</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.0320562762172913</v>
+        <v>-0.03205627621730149</v>
       </c>
       <c r="AG18" t="n">
-        <v>-3.953174045802473e-14</v>
+        <v>-9.295205578831507e-15</v>
       </c>
       <c r="AH18" t="n">
-        <v>-12.24415944947395</v>
+        <v>-12.24415944946668</v>
       </c>
       <c r="AI18" t="n">
-        <v>-2.747801985947262e-13</v>
+        <v>-3.448352714485736e-13</v>
       </c>
       <c r="AJ18" t="n">
-        <v>88.6711377647799</v>
+        <v>88.67113776478836</v>
       </c>
       <c r="AK18" t="n">
-        <v>-1.167475404545426e-13</v>
+        <v>-2.618521718900091e-14</v>
       </c>
       <c r="AL18" t="n">
-        <v>-437.5151472319367</v>
+        <v>-437.5151472319706</v>
       </c>
       <c r="AM18" t="n">
-        <v>-1.086242207293253e-12</v>
+        <v>-1.374012015276094e-12</v>
       </c>
       <c r="AN18" t="n">
-        <v>12.24415944947395</v>
+        <v>12.24415944946668</v>
       </c>
       <c r="AO18" t="n">
-        <v>2.747801985947262e-13</v>
+        <v>3.448352714485736e-13</v>
       </c>
       <c r="AP18" t="n">
-        <v>-88.6711377647799</v>
+        <v>-88.67113776478836</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.167475404545426e-13</v>
+        <v>2.618521718900091e-14</v>
       </c>
       <c r="AR18" t="n">
-        <v>-271.8539548863024</v>
+        <v>-271.8539548863363</v>
       </c>
       <c r="AS18" t="n">
-        <v>-1.111999381464557e-12</v>
+        <v>-1.384670156312495e-12</v>
       </c>
     </row>
     <row r="19">
@@ -6366,112 +6366,112 @@
         <v>-2771.465667658624</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.008506800363530128</v>
+        <v>-0.008506800363690507</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3199836416745343</v>
+        <v>-0.3199836416745839</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0001215664955624709</v>
+        <v>-0.000121566495562611</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0320562762172913</v>
+        <v>0.03205627621730149</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0008825836815066833</v>
+        <v>0.0008825836814785056</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.953174045802473e-14</v>
+        <v>-9.295205578831507e-15</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.008617658990236473</v>
+        <v>-0.008617658990396852</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.319983641674853</v>
+        <v>-0.3199836416746615</v>
       </c>
       <c r="R19" t="n">
-        <v>0.001454028388443984</v>
+        <v>0.001454028388444068</v>
       </c>
       <c r="S19" t="n">
-        <v>0.03205627621734609</v>
+        <v>0.03205627621731389</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.006590736799513456</v>
+        <v>-0.006590736799541642</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.95222817975377e-14</v>
+        <v>-9.296542609148836e-15</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.008506800363530128</v>
+        <v>-0.008506800363690507</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3199836416745343</v>
+        <v>-0.3199836416745839</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.0001215664955624709</v>
+        <v>-0.000121566495562611</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.0320562762172913</v>
+        <v>0.03205627621730149</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.0008825836815066833</v>
+        <v>0.0008825836814785056</v>
       </c>
       <c r="AA19" t="n">
-        <v>-3.953174045802473e-14</v>
+        <v>-9.295205578831507e-15</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.008617658990236473</v>
+        <v>-0.008617658990396852</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.319983641674853</v>
+        <v>-0.3199836416746615</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.001454028388443984</v>
+        <v>0.001454028388444068</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.03205627621734609</v>
+        <v>0.03205627621731389</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.006590736799513456</v>
+        <v>-0.006590736799541642</v>
       </c>
       <c r="AG19" t="n">
-        <v>-3.95222817975377e-14</v>
+        <v>-9.296542609148836e-15</v>
       </c>
       <c r="AH19" t="n">
         <v>13.13674726470185</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.629008122312371e-13</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.212058392753398</v>
+        <v>2.212058392776836</v>
       </c>
       <c r="AK19" t="n">
-        <v>-1.169619956442602e-13</v>
+        <v>-2.646494134950217e-14</v>
       </c>
       <c r="AL19" t="n">
-        <v>-4.700540704047413</v>
+        <v>-4.70054070414116</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.023181539494544e-12</v>
+        <v>1.392663762089796e-12</v>
       </c>
       <c r="AN19" t="n">
         <v>-13.13674726470185</v>
       </c>
       <c r="AO19" t="n">
-        <v>-2.629008122312371e-13</v>
+        <v>-3.410605131648481e-13</v>
       </c>
       <c r="AP19" t="n">
-        <v>-2.212058392753398</v>
+        <v>-2.212058392776836</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.169619956442602e-13</v>
+        <v>2.646494134950217e-14</v>
       </c>
       <c r="AR19" t="n">
-        <v>-12.99592643797977</v>
+        <v>-12.99592643807352</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.051603248924948e-12</v>
+        <v>1.392663762089796e-12</v>
       </c>
     </row>
     <row r="20">
@@ -6493,124 +6493,124 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0001033262400798596</v>
+        <v>0.0001033262400799706</v>
       </c>
       <c r="G20" t="n">
-        <v>1.291578000998245e-05</v>
+        <v>1.291578000999632e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>12.24415944946336</v>
+        <v>12.24415944947652</v>
       </c>
       <c r="I20" t="n">
-        <v>2583.15600199649</v>
+        <v>2583.156001999265</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.008617658990236473</v>
+        <v>-0.008617658990396852</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.319983641674853</v>
+        <v>-0.3199836416746615</v>
       </c>
       <c r="L20" t="n">
-        <v>0.001454028388443984</v>
+        <v>0.001454028388444068</v>
       </c>
       <c r="M20" t="n">
-        <v>0.03205627621734609</v>
+        <v>0.03205627621731389</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.006590736799513456</v>
+        <v>-0.006590736799541642</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.95222817975377e-14</v>
+        <v>-9.296542609148836e-15</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.008617658990549991</v>
+        <v>-0.008617658990467861</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.3200869679149329</v>
+        <v>-0.3200869679147415</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0001215664955624186</v>
+        <v>0.0001215664955626805</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1813005936458454</v>
+        <v>0.1813005936458132</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.006590736799568158</v>
+        <v>-0.006590736799553908</v>
       </c>
       <c r="U20" t="n">
-        <v>-3.952324315212423e-14</v>
+        <v>-9.303613152494448e-15</v>
       </c>
       <c r="V20" t="n">
-        <v>0.319983641674853</v>
+        <v>0.3199836416746615</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.008617658990236473</v>
+        <v>-0.008617658990396852</v>
       </c>
       <c r="X20" t="n">
-        <v>0.001454028388443984</v>
+        <v>0.001454028388444068</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.006590736799513456</v>
+        <v>0.006590736799541642</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.03205627621734609</v>
+        <v>0.03205627621731389</v>
       </c>
       <c r="AA20" t="n">
-        <v>-3.95222817975377e-14</v>
+        <v>-9.296542609148836e-15</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.3200869679149329</v>
+        <v>0.3200869679147415</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.008617658990549991</v>
+        <v>-0.008617658990467861</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.0001215664955624186</v>
+        <v>0.0001215664955626805</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.006590736799568158</v>
+        <v>0.006590736799553908</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.1813005936458454</v>
+        <v>0.1813005936458132</v>
       </c>
       <c r="AG20" t="n">
-        <v>-3.952324315212423e-14</v>
+        <v>-9.303613152494448e-15</v>
       </c>
       <c r="AH20" t="n">
-        <v>-12.24415944946668</v>
+        <v>-12.24415944947395</v>
       </c>
       <c r="AI20" t="n">
-        <v>-2.771116669464391e-13</v>
+        <v>-3.529398995283373e-13</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-88.67113776482549</v>
+        <v>-88.67113776479871</v>
       </c>
       <c r="AK20" t="n">
-        <v>-1.167677066149508e-13</v>
+        <v>-2.618391614639393e-14</v>
       </c>
       <c r="AL20" t="n">
-        <v>271.8539548864848</v>
+        <v>271.8539548863777</v>
       </c>
       <c r="AM20" t="n">
-        <v>-1.108002578575906e-12</v>
+        <v>-1.407318706014848e-12</v>
       </c>
       <c r="AN20" t="n">
-        <v>12.24415944946668</v>
+        <v>12.24415944947395</v>
       </c>
       <c r="AO20" t="n">
-        <v>2.771116669464391e-13</v>
+        <v>3.529398995283373e-13</v>
       </c>
       <c r="AP20" t="n">
-        <v>88.67113776482549</v>
+        <v>88.67113776479871</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.167677066149508e-13</v>
+        <v>2.618391614639393e-14</v>
       </c>
       <c r="AR20" t="n">
-        <v>437.515147232119</v>
+        <v>437.515147232012</v>
       </c>
       <c r="AS20" t="n">
-        <v>-1.109334846205456e-12</v>
+        <v>-1.415756401002e-12</v>
       </c>
     </row>
     <row r="21">
@@ -6632,124 +6632,124 @@
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0001108586267063432</v>
+        <v>-0.0001108586267063449</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.38573283382929e-05</v>
+        <v>-1.385732833829312e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>-13.13674726470167</v>
+        <v>-13.13674726470188</v>
       </c>
       <c r="I21" t="n">
-        <v>-2771.46566765858</v>
+        <v>-2771.465667658624</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.008617658990549991</v>
+        <v>-0.008617658990467861</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3200869679149329</v>
+        <v>-0.3200869679147415</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0001215664955624186</v>
+        <v>0.0001215664955626805</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1813005936458454</v>
+        <v>0.1813005936458132</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.006590736799568158</v>
+        <v>-0.006590736799553908</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.952324315212423e-14</v>
+        <v>-9.303613152494448e-15</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.008506800363843648</v>
+        <v>-0.008506800363761516</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.3200869679146143</v>
+        <v>-0.3200869679146637</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.001454028388443931</v>
+        <v>-0.001454028388444138</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1813005936457907</v>
+        <v>0.1813005936458008</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0008825836814519907</v>
+        <v>0.0008825836814662386</v>
       </c>
       <c r="U21" t="n">
-        <v>-3.950848033461115e-14</v>
+        <v>-9.285603354946163e-15</v>
       </c>
       <c r="V21" t="n">
-        <v>0.008617658990549991</v>
+        <v>0.008617658990467861</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3200869679149329</v>
+        <v>-0.3200869679147415</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.0001215664955624186</v>
+        <v>-0.0001215664955626805</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.1813005936458454</v>
+        <v>-0.1813005936458132</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.006590736799568158</v>
+        <v>-0.006590736799553908</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.952324315212423e-14</v>
+        <v>9.303613152494448e-15</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.008506800363843648</v>
+        <v>0.008506800363761516</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.3200869679146143</v>
+        <v>-0.3200869679146637</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.001454028388443931</v>
+        <v>0.001454028388444138</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.1813005936457907</v>
+        <v>-0.1813005936458008</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.0008825836814519907</v>
+        <v>0.0008825836814662386</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.950848033461115e-14</v>
+        <v>9.285603354946163e-15</v>
       </c>
       <c r="AH21" t="n">
-        <v>13.13674726470174</v>
+        <v>13.13674726470185</v>
       </c>
       <c r="AI21" t="n">
-        <v>-2.557953848736361e-13</v>
+        <v>-3.552713678800501e-13</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.212058392798944</v>
+        <v>2.212058392787033</v>
       </c>
       <c r="AK21" t="n">
-        <v>-1.168509733417977e-13</v>
+        <v>-2.653433028854124e-14</v>
       </c>
       <c r="AL21" t="n">
-        <v>-12.99592643816196</v>
+        <v>-12.99592643811431</v>
       </c>
       <c r="AM21" t="n">
-        <v>-9.947598300641403e-13</v>
+        <v>-1.392663762089796e-12</v>
       </c>
       <c r="AN21" t="n">
-        <v>-13.13674726470174</v>
+        <v>-13.13674726470185</v>
       </c>
       <c r="AO21" t="n">
-        <v>2.557953848736361e-13</v>
+        <v>3.552713678800501e-13</v>
       </c>
       <c r="AP21" t="n">
-        <v>-2.212058392798944</v>
+        <v>-2.212058392787033</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.168509733417977e-13</v>
+        <v>2.653433028854124e-14</v>
       </c>
       <c r="AR21" t="n">
-        <v>-4.700540704229594</v>
+        <v>-4.70054070418195</v>
       </c>
       <c r="AS21" t="n">
-        <v>-9.947598300641403e-13</v>
+        <v>-1.449507180950604e-12</v>
       </c>
     </row>
     <row r="22">
@@ -6771,124 +6771,124 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0004417506794183179</v>
+        <v>0.0004417506794179848</v>
       </c>
       <c r="G22" t="n">
-        <v>5.521883492728974e-05</v>
+        <v>5.521883492724811e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>52.34745551107067</v>
+        <v>52.34745551103121</v>
       </c>
       <c r="I22" t="n">
-        <v>11043.76698545795</v>
+        <v>11043.76698544962</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.07036120329910434</v>
+        <v>-0.07036120329889795</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6912454096229569</v>
+        <v>-0.6912454096231312</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.002332846674624704</v>
+        <v>-0.002332846674625141</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0004776631797100466</v>
+        <v>0.0004776631797337471</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0355348953589887</v>
+        <v>-0.03553489535897476</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.010899116652667e-13</v>
+        <v>-2.254982535921031e-14</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.07036120329830216</v>
+        <v>-0.07036120329871685</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.6908036589435386</v>
+        <v>-0.6908036589437132</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.0007903423542390336</v>
+        <v>-0.000790342354239219</v>
       </c>
       <c r="S22" t="n">
-        <v>0.03349161994969708</v>
+        <v>0.0334916199497208</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.03553489535892964</v>
+        <v>-0.03553489535896087</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.010500600582059e-13</v>
+        <v>-2.253216035953992e-14</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6912454096229569</v>
+        <v>-0.6912454096231312</v>
       </c>
       <c r="W22" t="n">
-        <v>0.07036120329910434</v>
+        <v>0.07036120329889795</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.002332846674624704</v>
+        <v>-0.002332846674625141</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.0355348953589887</v>
+        <v>-0.03553489535897476</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.0004776631797100466</v>
+        <v>-0.0004776631797337471</v>
       </c>
       <c r="AA22" t="n">
-        <v>-1.010899116652667e-13</v>
+        <v>-2.254982535921031e-14</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.6908036589435386</v>
+        <v>-0.6908036589437132</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.07036120329830216</v>
+        <v>0.07036120329871685</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.0007903423542390336</v>
+        <v>-0.000790342354239219</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.03553489535892964</v>
+        <v>-0.03553489535896087</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.03349161994969708</v>
+        <v>-0.0334916199497208</v>
       </c>
       <c r="AG22" t="n">
-        <v>-1.010500600582059e-13</v>
+        <v>-2.253216035953992e-14</v>
       </c>
       <c r="AH22" t="n">
-        <v>-52.34745551107335</v>
+        <v>-52.34745551102969</v>
       </c>
       <c r="AI22" t="n">
-        <v>-6.643574579356937e-13</v>
+        <v>7.904787935331115e-14</v>
       </c>
       <c r="AJ22" t="n">
-        <v>13.97919724677558</v>
+        <v>13.97919724679529</v>
       </c>
       <c r="AK22" t="n">
-        <v>-1.260797022339943e-13</v>
+        <v>-2.964295475749168e-14</v>
       </c>
       <c r="AL22" t="n">
-        <v>-37.59404297975952</v>
+        <v>-37.59404297983836</v>
       </c>
       <c r="AM22" t="n">
-        <v>-2.682298827494378e-12</v>
+        <v>3.055333763768431e-13</v>
       </c>
       <c r="AN22" t="n">
-        <v>52.34745551107335</v>
+        <v>52.34745551102969</v>
       </c>
       <c r="AO22" t="n">
-        <v>6.643574579356937e-13</v>
+        <v>-7.904787935331115e-14</v>
       </c>
       <c r="AP22" t="n">
-        <v>-13.97919724677558</v>
+        <v>-13.97919724679529</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.260797022339943e-13</v>
+        <v>2.964295475749168e-14</v>
       </c>
       <c r="AR22" t="n">
-        <v>-74.23953499444512</v>
+        <v>-74.23953499452399</v>
       </c>
       <c r="AS22" t="n">
-        <v>-2.636113549669972e-12</v>
+        <v>3.268496584496461e-13</v>
       </c>
     </row>
     <row r="23">
@@ -6910,124 +6910,124 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0004821348199423869</v>
+        <v>0.0004821348199423592</v>
       </c>
       <c r="G23" t="n">
-        <v>6.026685249279837e-05</v>
+        <v>6.02668524927949e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>57.13297616317285</v>
+        <v>57.13297616316957</v>
       </c>
       <c r="I23" t="n">
-        <v>12053.37049855967</v>
+        <v>12053.37049855898</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.07036120329830216</v>
+        <v>-0.07036120329871685</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6908036589435386</v>
+        <v>-0.6908036589437132</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0007903423542390336</v>
+        <v>-0.000790342354239219</v>
       </c>
       <c r="M23" t="n">
-        <v>0.03349161994969708</v>
+        <v>0.0334916199497208</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.03553489535892964</v>
+        <v>-0.03553489535896087</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.010500600582059e-13</v>
+        <v>-2.253216035953992e-14</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.06987906847835977</v>
+        <v>-0.06987906847877449</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.6908036589443535</v>
+        <v>-0.6908036589438927</v>
       </c>
       <c r="R23" t="n">
-        <v>0.00233284667462481</v>
+        <v>0.002332846674625</v>
       </c>
       <c r="S23" t="n">
-        <v>0.03349161994976197</v>
+        <v>0.03349161994973283</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0002044443358872198</v>
+        <v>0.0002044443358560187</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.010917419802469e-13</v>
+        <v>-2.255910051777855e-14</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.07036120329830216</v>
+        <v>-0.07036120329871685</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6908036589435386</v>
+        <v>-0.6908036589437132</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.0007903423542390336</v>
+        <v>-0.000790342354239219</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.03349161994969708</v>
+        <v>0.0334916199497208</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.03553489535892964</v>
+        <v>-0.03553489535896087</v>
       </c>
       <c r="AA23" t="n">
-        <v>-1.010500600582059e-13</v>
+        <v>-2.253216035953992e-14</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.06987906847835977</v>
+        <v>-0.06987906847877449</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.6908036589443535</v>
+        <v>-0.6908036589438927</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.00233284667462481</v>
+        <v>0.002332846674625</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.03349161994976197</v>
+        <v>0.03349161994973283</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.0002044443358872198</v>
+        <v>0.0002044443358560187</v>
       </c>
       <c r="AG23" t="n">
-        <v>-1.010917419802469e-13</v>
+        <v>-2.255910051777855e-14</v>
       </c>
       <c r="AH23" t="n">
-        <v>-57.13297616317323</v>
+        <v>-57.13297616316959</v>
       </c>
       <c r="AI23" t="n">
-        <v>6.679101716144942e-13</v>
+        <v>-8.526512829121202e-14</v>
       </c>
       <c r="AJ23" t="n">
-        <v>14.38129338002526</v>
+        <v>14.38129338005121</v>
       </c>
       <c r="AK23" t="n">
-        <v>-1.385142001097961e-13</v>
+        <v>-2.568778523226456e-14</v>
       </c>
       <c r="AL23" t="n">
-        <v>-77.36050705072442</v>
+        <v>-77.36050705082822</v>
       </c>
       <c r="AM23" t="n">
-        <v>2.728484105318785e-12</v>
+        <v>-3.410605131648481e-13</v>
       </c>
       <c r="AN23" t="n">
-        <v>57.13297616317323</v>
+        <v>57.13297616316959</v>
       </c>
       <c r="AO23" t="n">
-        <v>-6.679101716144942e-13</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="AP23" t="n">
-        <v>-14.38129338002526</v>
+        <v>-14.38129338005121</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.385142001097961e-13</v>
+        <v>2.568778523226456e-14</v>
       </c>
       <c r="AR23" t="n">
-        <v>-37.68983998947769</v>
+        <v>-37.68983998958147</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.671640686457977e-12</v>
+        <v>-3.410605131648481e-13</v>
       </c>
     </row>
     <row r="24">
@@ -7049,124 +7049,124 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0004417506794180959</v>
+        <v>0.0004417506794182069</v>
       </c>
       <c r="G24" t="n">
-        <v>5.521883492726198e-05</v>
+        <v>5.521883492727586e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>52.34745551104436</v>
+        <v>52.34745551105752</v>
       </c>
       <c r="I24" t="n">
-        <v>11043.7669854524</v>
+        <v>11043.76698545517</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.06987906847835977</v>
+        <v>-0.06987906847877449</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6908036589443535</v>
+        <v>-0.6908036589438927</v>
       </c>
       <c r="L24" t="n">
-        <v>0.00233284667462481</v>
+        <v>0.002332846674625</v>
       </c>
       <c r="M24" t="n">
-        <v>0.03349161994976197</v>
+        <v>0.03349161994973283</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0002044443358872198</v>
+        <v>0.0002044443358560187</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.010917419802469e-13</v>
+        <v>-2.255910051777855e-14</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.06987906847916199</v>
+        <v>-0.06987906847895559</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.6912454096237716</v>
+        <v>-0.6912454096233109</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0007903423542389292</v>
+        <v>0.000790342354239359</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0004776631797749287</v>
+        <v>0.0004776631797457648</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0002044443358281631</v>
+        <v>0.0002044443358421079</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.010136040492752e-13</v>
+        <v>-2.255697836653975e-14</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6908036589443535</v>
+        <v>0.6908036589438927</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.06987906847835977</v>
+        <v>-0.06987906847877449</v>
       </c>
       <c r="X24" t="n">
-        <v>0.00233284667462481</v>
+        <v>0.002332846674625</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.0002044443358872198</v>
+        <v>-0.0002044443358560187</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.03349161994976197</v>
+        <v>0.03349161994973283</v>
       </c>
       <c r="AA24" t="n">
-        <v>-1.010917419802469e-13</v>
+        <v>-2.255910051777855e-14</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.6912454096237716</v>
+        <v>0.6912454096233109</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.06987906847916199</v>
+        <v>-0.06987906847895559</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.0007903423542389292</v>
+        <v>0.000790342354239359</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.0002044443358281631</v>
+        <v>-0.0002044443358421079</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.0004776631797749287</v>
+        <v>0.0004776631797457648</v>
       </c>
       <c r="AG24" t="n">
-        <v>-1.010136040492752e-13</v>
+        <v>-2.255697836653975e-14</v>
       </c>
       <c r="AH24" t="n">
-        <v>-52.34745551104425</v>
+        <v>-52.3474555110588</v>
       </c>
       <c r="AI24" t="n">
-        <v>-6.45705711121991e-13</v>
+        <v>6.661338147750939e-14</v>
       </c>
       <c r="AJ24" t="n">
-        <v>-13.97919724682958</v>
+        <v>-13.97919724680534</v>
       </c>
       <c r="AK24" t="n">
-        <v>-1.260634392014071e-13</v>
+        <v>-2.969423752025024e-14</v>
       </c>
       <c r="AL24" t="n">
-        <v>74.23953499466113</v>
+        <v>74.23953499456417</v>
       </c>
       <c r="AM24" t="n">
-        <v>-2.62545540863357e-12</v>
+        <v>2.593480985524366e-13</v>
       </c>
       <c r="AN24" t="n">
-        <v>52.34745551104425</v>
+        <v>52.3474555110588</v>
       </c>
       <c r="AO24" t="n">
-        <v>6.45705711121991e-13</v>
+        <v>-6.661338147750939e-14</v>
       </c>
       <c r="AP24" t="n">
-        <v>13.97919724682958</v>
+        <v>13.97919724680534</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.260634392014071e-13</v>
+        <v>2.969423752025024e-14</v>
       </c>
       <c r="AR24" t="n">
-        <v>37.5940429799755</v>
+        <v>37.59404297987852</v>
       </c>
       <c r="AS24" t="n">
-        <v>-2.540190280342358e-12</v>
+        <v>2.664535259100376e-13</v>
       </c>
     </row>
     <row r="25">
@@ -7188,124 +7188,124 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0004821348199423453</v>
+        <v>0.0004821348199423592</v>
       </c>
       <c r="G25" t="n">
-        <v>6.026685249279316e-05</v>
+        <v>6.02668524927949e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>57.13297616316792</v>
+        <v>57.13297616316957</v>
       </c>
       <c r="I25" t="n">
-        <v>12053.37049855863</v>
+        <v>12053.37049855898</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.06987906847916199</v>
+        <v>-0.06987906847895559</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6912454096237716</v>
+        <v>-0.6912454096233109</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0007903423542389292</v>
+        <v>0.000790342354239359</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0004776631797749287</v>
+        <v>0.0004776631797457648</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0002044443358281631</v>
+        <v>0.0002044443358421079</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.010136040492752e-13</v>
+        <v>-2.255697836653975e-14</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.07036120329910434</v>
+        <v>-0.07036120329889795</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.6912454096229569</v>
+        <v>-0.6912454096231312</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.002332846674624704</v>
+        <v>-0.002332846674625141</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0004776631797100466</v>
+        <v>0.0004776631797337471</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0355348953589887</v>
+        <v>-0.03553489535897476</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.010899116652667e-13</v>
+        <v>-2.254982535921031e-14</v>
       </c>
       <c r="V25" t="n">
-        <v>0.06987906847916199</v>
+        <v>0.06987906847895559</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.6912454096237716</v>
+        <v>-0.6912454096233109</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.0007903423542389292</v>
+        <v>-0.000790342354239359</v>
       </c>
       <c r="Y25" t="n">
-        <v>-0.0004776631797749287</v>
+        <v>-0.0004776631797457648</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.0002044443358281631</v>
+        <v>0.0002044443358421079</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.010136040492752e-13</v>
+        <v>2.255697836653975e-14</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.07036120329910434</v>
+        <v>0.07036120329889795</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.6912454096229569</v>
+        <v>-0.6912454096231312</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.002332846674624704</v>
+        <v>0.002332846674625141</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.0004776631797100466</v>
+        <v>-0.0004776631797337471</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.0355348953589887</v>
+        <v>-0.03553489535897476</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.010899116652667e-13</v>
+        <v>2.254982535921031e-14</v>
       </c>
       <c r="AH25" t="n">
-        <v>-57.13297616316777</v>
+        <v>-57.13297616316959</v>
       </c>
       <c r="AI25" t="n">
-        <v>-6.394884621840902e-13</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="AJ25" t="n">
-        <v>14.38129338007445</v>
+        <v>14.38129338006276</v>
       </c>
       <c r="AK25" t="n">
-        <v>-1.384983707580778e-13</v>
+        <v>-2.565309076274502e-14</v>
       </c>
       <c r="AL25" t="n">
-        <v>-37.68983998967445</v>
+        <v>-37.68983998962765</v>
       </c>
       <c r="AM25" t="n">
-        <v>-2.614797267597169e-12</v>
+        <v>2.842170943040401e-13</v>
       </c>
       <c r="AN25" t="n">
-        <v>57.13297616316777</v>
+        <v>57.13297616316959</v>
       </c>
       <c r="AO25" t="n">
-        <v>6.394884621840902e-13</v>
+        <v>-8.526512829121202e-14</v>
       </c>
       <c r="AP25" t="n">
-        <v>-14.38129338007445</v>
+        <v>-14.38129338006276</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.384983707580778e-13</v>
+        <v>2.565309076274502e-14</v>
       </c>
       <c r="AR25" t="n">
-        <v>-77.36050705092119</v>
+        <v>-77.36050705087436</v>
       </c>
       <c r="AS25" t="n">
-        <v>-2.501110429875553e-12</v>
+        <v>2.842170943040401e-13</v>
       </c>
     </row>
     <row r="26">
@@ -7327,124 +7327,124 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-9.398725575804345e-05</v>
+        <v>-9.398725575793243e-05</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.174840696975543e-05</v>
+        <v>-1.174840696974155e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>-11.13748980732815</v>
+        <v>-11.13748980731499</v>
       </c>
       <c r="I26" t="n">
-        <v>-2349.681393951086</v>
+        <v>-2349.68139394831</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4537190030256291</v>
+        <v>-0.4537190030253384</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.7504936950263797</v>
+        <v>-0.7504936950267934</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.003032168184686173</v>
+        <v>-0.003032168184686789</v>
       </c>
       <c r="M26" t="n">
-        <v>0.006590736799522585</v>
+        <v>0.006590736799546265</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.02907849070414583</v>
+        <v>-0.0290784907041432</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.611412101213256e-13</v>
+        <v>-3.586128221406856e-14</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.4537190030243844</v>
+        <v>-0.4537190030250376</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.7505876822821378</v>
+        <v>-0.7505876822825513</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.001456573300679839</v>
+        <v>-0.00145657330068003</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0008825836814975517</v>
+        <v>-0.0008825836814738829</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.02907849070410424</v>
+        <v>-0.0290784907041274</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.611526070967156e-13</v>
+        <v>-3.586244829761654e-14</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.7504936950263797</v>
+        <v>-0.7504936950267934</v>
       </c>
       <c r="W26" t="n">
-        <v>0.4537190030256291</v>
+        <v>0.4537190030253384</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.003032168184686173</v>
+        <v>-0.003032168184686789</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.02907849070414583</v>
+        <v>-0.0290784907041432</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.006590736799522585</v>
+        <v>-0.006590736799546265</v>
       </c>
       <c r="AA26" t="n">
-        <v>-1.611412101213256e-13</v>
+        <v>-3.586128221406856e-14</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.7505876822821378</v>
+        <v>-0.7505876822825513</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.4537190030243844</v>
+        <v>0.4537190030250376</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.001456573300679839</v>
+        <v>-0.00145657330068003</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.02907849070410424</v>
+        <v>-0.0290784907041274</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.0008825836814975517</v>
+        <v>0.0008825836814738829</v>
       </c>
       <c r="AG26" t="n">
-        <v>-1.611526070967156e-13</v>
+        <v>-3.586244829761654e-14</v>
       </c>
       <c r="AH26" t="n">
         <v>11.13748980732635</v>
       </c>
       <c r="AI26" t="n">
-        <v>-4.632738637155853e-12</v>
+        <v>1.435296326235402e-12</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.212058392761011</v>
+        <v>2.212058392780676</v>
       </c>
       <c r="AK26" t="n">
-        <v>-8.879008639439689e-14</v>
+        <v>-3.371608547908522e-14</v>
       </c>
       <c r="AL26" t="n">
-        <v>-12.99592643801022</v>
+        <v>-12.99592643808889</v>
       </c>
       <c r="AM26" t="n">
-        <v>-1.853095454862341e-11</v>
+        <v>5.74118530494161e-12</v>
       </c>
       <c r="AN26" t="n">
         <v>-11.13748980732635</v>
       </c>
       <c r="AO26" t="n">
-        <v>4.632738637155853e-12</v>
+        <v>-1.435296326235402e-12</v>
       </c>
       <c r="AP26" t="n">
-        <v>-2.212058392761011</v>
+        <v>-2.212058392780676</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8.879008639439689e-14</v>
+        <v>3.371608547908522e-14</v>
       </c>
       <c r="AR26" t="n">
-        <v>-4.700540704077868</v>
+        <v>-4.700540704156521</v>
       </c>
       <c r="AS26" t="n">
-        <v>-1.853095454862341e-11</v>
+        <v>5.74118530494161e-12</v>
       </c>
     </row>
     <row r="27">
@@ -7478,112 +7478,112 @@
         <v>-1804.785529194164</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4537190030243844</v>
+        <v>-0.4537190030250376</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.7505876822821378</v>
+        <v>-0.7505876822825513</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.001456573300679839</v>
+        <v>-0.00145657330068003</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0008825836814975517</v>
+        <v>-0.0008825836814738829</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.02907849070410424</v>
+        <v>-0.0290784907041274</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.611526070967156e-13</v>
+        <v>-3.586244829761654e-14</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.4537911944455522</v>
+        <v>-0.4537911944462054</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.7505876822834716</v>
+        <v>-0.7505876822828246</v>
       </c>
       <c r="R27" t="n">
-        <v>0.003032168184686301</v>
+        <v>0.003032168184686586</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.0008825836814504936</v>
+        <v>-0.0008825836814639399</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.1913477001706949</v>
+        <v>-0.1913477001707182</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.611381091097773e-13</v>
+        <v>-3.584592144909157e-14</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.4537190030243844</v>
+        <v>-0.4537190030250376</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.7505876822821378</v>
+        <v>-0.7505876822825513</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.001456573300679839</v>
+        <v>-0.00145657330068003</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.0008825836814975517</v>
+        <v>-0.0008825836814738829</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.02907849070410424</v>
+        <v>-0.0290784907041274</v>
       </c>
       <c r="AA27" t="n">
-        <v>-1.611526070967156e-13</v>
+        <v>-3.586244829761654e-14</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.4537911944455522</v>
+        <v>-0.4537911944462054</v>
       </c>
       <c r="AC27" t="n">
-        <v>-0.7505876822834716</v>
+        <v>-0.7505876822828246</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.003032168184686301</v>
+        <v>0.003032168184686586</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.0008825836814504936</v>
+        <v>-0.0008825836814639399</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.1913477001706949</v>
+        <v>-0.1913477001707182</v>
       </c>
       <c r="AG27" t="n">
-        <v>-1.611381091097773e-13</v>
+        <v>-3.584592144909157e-14</v>
       </c>
       <c r="AH27" t="n">
         <v>8.554683408379788</v>
       </c>
       <c r="AI27" t="n">
-        <v>4.661160346586257e-12</v>
+        <v>-1.4210854715202e-12</v>
       </c>
       <c r="AJ27" t="n">
-        <v>91.28529229081425</v>
+        <v>91.28529229083352</v>
       </c>
       <c r="AK27" t="n">
-        <v>-1.00450897599913e-13</v>
+        <v>-2.122434172857623e-14</v>
       </c>
       <c r="AL27" t="n">
-        <v>-275.0817579092991</v>
+        <v>-275.0817579093762</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.858779796748422e-11</v>
+        <v>-5.74118530494161e-12</v>
       </c>
       <c r="AN27" t="n">
         <v>-8.554683408379788</v>
       </c>
       <c r="AO27" t="n">
-        <v>-4.661160346586257e-12</v>
+        <v>1.4210854715202e-12</v>
       </c>
       <c r="AP27" t="n">
-        <v>-91.28529229081425</v>
+        <v>-91.28529229083352</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.00450897599913e-13</v>
+        <v>2.122434172857623e-14</v>
       </c>
       <c r="AR27" t="n">
-        <v>-455.2005804172148</v>
+        <v>-455.2005804172919</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.864464138634503e-11</v>
+        <v>-5.684341886080801e-12</v>
       </c>
     </row>
     <row r="28">
@@ -7605,124 +7605,124 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>-9.398725575793243e-05</v>
+        <v>-9.398725575804345e-05</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.174840696974155e-05</v>
+        <v>-1.174840696975543e-05</v>
       </c>
       <c r="H28" t="n">
-        <v>-11.13748980731499</v>
+        <v>-11.13748980732815</v>
       </c>
       <c r="I28" t="n">
-        <v>-2349.68139394831</v>
+        <v>-2349.681393951086</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4537911944455522</v>
+        <v>-0.4537911944462054</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.7505876822834716</v>
+        <v>-0.7505876822828246</v>
       </c>
       <c r="L28" t="n">
-        <v>0.003032168184686301</v>
+        <v>0.003032168184686586</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0008825836814504936</v>
+        <v>-0.0008825836814639399</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.1913477001706949</v>
+        <v>-0.1913477001707182</v>
       </c>
       <c r="O28" t="n">
-        <v>-1.611381091097773e-13</v>
+        <v>-3.584592144909157e-14</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.453791194446797</v>
+        <v>-0.4537911944465061</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.7504936950277137</v>
+        <v>-0.7504936950270665</v>
       </c>
       <c r="R28" t="n">
-        <v>0.001456573300679713</v>
+        <v>0.001456573300680231</v>
       </c>
       <c r="S28" t="n">
-        <v>0.006590736799569702</v>
+        <v>0.006590736799556234</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.1913477001707365</v>
+        <v>-0.1913477001707339</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.612105836505838e-13</v>
+        <v>-3.591934838764536e-14</v>
       </c>
       <c r="V28" t="n">
-        <v>0.7505876822834716</v>
+        <v>0.7505876822828246</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.4537911944455522</v>
+        <v>-0.4537911944462054</v>
       </c>
       <c r="X28" t="n">
-        <v>0.003032168184686301</v>
+        <v>0.003032168184686586</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.1913477001706949</v>
+        <v>0.1913477001707182</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.0008825836814504936</v>
+        <v>-0.0008825836814639399</v>
       </c>
       <c r="AA28" t="n">
-        <v>-1.611381091097773e-13</v>
+        <v>-3.584592144909157e-14</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.7504936950277137</v>
+        <v>0.7504936950270665</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.453791194446797</v>
+        <v>-0.4537911944465061</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.001456573300679713</v>
+        <v>0.001456573300680231</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.1913477001707365</v>
+        <v>0.1913477001707339</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.006590736799569702</v>
+        <v>0.006590736799556234</v>
       </c>
       <c r="AG28" t="n">
-        <v>-1.612105836505838e-13</v>
+        <v>-3.591934838764536e-14</v>
       </c>
       <c r="AH28" t="n">
         <v>11.13748980732635</v>
       </c>
       <c r="AI28" t="n">
-        <v>-4.646949491871055e-12</v>
+        <v>1.4210854715202e-12</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-2.212058392800185</v>
+        <v>-2.212058392789006</v>
       </c>
       <c r="AK28" t="n">
-        <v>-8.876233081878127e-14</v>
+        <v>-3.352873534367973e-14</v>
       </c>
       <c r="AL28" t="n">
-        <v>4.70054070423453</v>
+        <v>4.700540704189827</v>
       </c>
       <c r="AM28" t="n">
-        <v>-1.853095454862341e-11</v>
+        <v>5.712763595511205e-12</v>
       </c>
       <c r="AN28" t="n">
         <v>-11.13748980732635</v>
       </c>
       <c r="AO28" t="n">
-        <v>4.646949491871055e-12</v>
+        <v>-1.4210854715202e-12</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.212058392800185</v>
+        <v>2.212058392789006</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8.876233081878127e-14</v>
+        <v>3.352873534367973e-14</v>
       </c>
       <c r="AR28" t="n">
-        <v>12.99592643816695</v>
+        <v>12.99592643812222</v>
       </c>
       <c r="AS28" t="n">
-        <v>-1.861621967691462e-11</v>
+        <v>5.627498467219993e-12</v>
       </c>
     </row>
     <row r="29">
@@ -7744,124 +7744,124 @@
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>-7.219142116787758e-05</v>
+        <v>-7.219142116776656e-05</v>
       </c>
       <c r="G29" t="n">
-        <v>-9.023927645984697e-06</v>
+        <v>-9.02392764597082e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>-8.554683408393494</v>
+        <v>-8.554683408380336</v>
       </c>
       <c r="I29" t="n">
-        <v>-1804.785529196939</v>
+        <v>-1804.785529194164</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.453791194446797</v>
+        <v>-0.4537911944465061</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.7504936950277137</v>
+        <v>-0.7504936950270665</v>
       </c>
       <c r="L29" t="n">
-        <v>0.001456573300679713</v>
+        <v>0.001456573300680231</v>
       </c>
       <c r="M29" t="n">
-        <v>0.006590736799569702</v>
+        <v>0.006590736799556234</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.1913477001707365</v>
+        <v>-0.1913477001707339</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.612105836505838e-13</v>
+        <v>-3.591934838764536e-14</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.4537190030256291</v>
+        <v>-0.4537190030253384</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.7504936950263797</v>
+        <v>-0.7504936950267934</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.003032168184686173</v>
+        <v>-0.003032168184686789</v>
       </c>
       <c r="S29" t="n">
-        <v>0.006590736799522585</v>
+        <v>0.006590736799546265</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.02907849070414583</v>
+        <v>-0.0290784907041432</v>
       </c>
       <c r="U29" t="n">
-        <v>-1.611412101213256e-13</v>
+        <v>-3.586128221406856e-14</v>
       </c>
       <c r="V29" t="n">
-        <v>0.453791194446797</v>
+        <v>0.4537911944465061</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.7504936950277137</v>
+        <v>-0.7504936950270665</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.001456573300679713</v>
+        <v>-0.001456573300680231</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.006590736799569702</v>
+        <v>-0.006590736799556234</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.1913477001707365</v>
+        <v>-0.1913477001707339</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.612105836505838e-13</v>
+        <v>3.591934838764536e-14</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.4537190030256291</v>
+        <v>0.4537190030253384</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.7504936950263797</v>
+        <v>-0.7504936950267934</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.003032168184686173</v>
+        <v>0.003032168184686789</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.006590736799522585</v>
+        <v>-0.006590736799546265</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.02907849070414583</v>
+        <v>-0.0290784907041432</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.611412101213256e-13</v>
+        <v>3.586128221406856e-14</v>
       </c>
       <c r="AH29" t="n">
-        <v>8.554683408394339</v>
+        <v>8.554683408379788</v>
       </c>
       <c r="AI29" t="n">
-        <v>-4.632738637155853e-12</v>
+        <v>1.449507180950604e-12</v>
       </c>
       <c r="AJ29" t="n">
-        <v>91.28529229084891</v>
+        <v>91.2852922908466</v>
       </c>
       <c r="AK29" t="n">
-        <v>-1.005775324136593e-13</v>
+        <v>-2.127811815633152e-14</v>
       </c>
       <c r="AL29" t="n">
-        <v>-455.2005804173534</v>
+        <v>-455.2005804173441</v>
       </c>
       <c r="AM29" t="n">
-        <v>-1.84741111297626e-11</v>
+        <v>5.854872142663226e-12</v>
       </c>
       <c r="AN29" t="n">
-        <v>-8.554683408394339</v>
+        <v>-8.554683408379788</v>
       </c>
       <c r="AO29" t="n">
-        <v>4.632738637155853e-12</v>
+        <v>-1.449507180950604e-12</v>
       </c>
       <c r="AP29" t="n">
-        <v>-91.28529229084891</v>
+        <v>-91.2852922908466</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.005775324136593e-13</v>
+        <v>2.127811815633152e-14</v>
       </c>
       <c r="AR29" t="n">
-        <v>-275.0817579094377</v>
+        <v>-275.0817579094285</v>
       </c>
       <c r="AS29" t="n">
-        <v>-1.858779796748422e-11</v>
+        <v>5.798028723802418e-12</v>
       </c>
     </row>
     <row r="30">
@@ -7895,112 +7895,112 @@
         <v>369.9427691461476</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.845791139355267</v>
+        <v>-0.8457911393550082</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.7611520690270692</v>
+        <v>-0.7611520690276043</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.003139734310674162</v>
+        <v>-0.003139734310674845</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0006683120527781236</v>
+        <v>-0.0006683120527693941</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.05000005721099737</v>
+        <v>-0.05000005721100176</v>
       </c>
       <c r="O30" t="n">
-        <v>-1.899677898334275e-13</v>
+        <v>-4.797347225031697e-14</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.8457911393537922</v>
+        <v>-0.8457911393545802</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.7611372713163034</v>
+        <v>-0.7611372713168385</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.001559049602196257</v>
+        <v>-0.001559049602196457</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002029479946406675</v>
+        <v>0.00202947994641545</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.05000005721098015</v>
+        <v>-0.05000005721099056</v>
       </c>
       <c r="U30" t="n">
-        <v>-1.900821841067412e-13</v>
+        <v>-4.795316946883113e-14</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.7611520690270692</v>
+        <v>-0.7611520690276043</v>
       </c>
       <c r="W30" t="n">
-        <v>0.845791139355267</v>
+        <v>0.8457911393550082</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.003139734310674162</v>
+        <v>-0.003139734310674845</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.05000005721099737</v>
+        <v>-0.05000005721100176</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.0006683120527781236</v>
+        <v>0.0006683120527693941</v>
       </c>
       <c r="AA30" t="n">
-        <v>-1.899677898334275e-13</v>
+        <v>-4.797347225031697e-14</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.7611372713163034</v>
+        <v>-0.7611372713168385</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.8457911393537922</v>
+        <v>0.8457911393545802</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.001559049602196257</v>
+        <v>-0.001559049602196457</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.05000005721098015</v>
+        <v>-0.05000005721099056</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.002029479946406675</v>
+        <v>-0.00202947994641545</v>
       </c>
       <c r="AG30" t="n">
-        <v>-1.900821841067412e-13</v>
+        <v>-4.795316946883113e-14</v>
       </c>
       <c r="AH30" t="n">
-        <v>-1.753528725748765</v>
+        <v>-1.753528725763317</v>
       </c>
       <c r="AI30" t="n">
-        <v>-4.732214620162267e-12</v>
+        <v>4.604316927725449e-12</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.4020961332469026</v>
+        <v>0.4020961332541386</v>
       </c>
       <c r="AK30" t="n">
-        <v>-3.67622599029005e-14</v>
+        <v>-2.389755060505649e-14</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0.1111099734400467</v>
+        <v>-0.1111099734689656</v>
       </c>
       <c r="AM30" t="n">
-        <v>-1.887201506178826e-11</v>
+        <v>1.84172677109018e-11</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.753528725748765</v>
+        <v>1.753528725763317</v>
       </c>
       <c r="AO30" t="n">
-        <v>4.732214620162267e-12</v>
+        <v>-4.604316927725449e-12</v>
       </c>
       <c r="AP30" t="n">
-        <v>-0.4020961332469026</v>
+        <v>-0.4020961332541386</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.67622599029005e-14</v>
+        <v>2.389755060505649e-14</v>
       </c>
       <c r="AR30" t="n">
-        <v>-3.105659092535173</v>
+        <v>-3.105659092564143</v>
       </c>
       <c r="AS30" t="n">
-        <v>-1.904254531837068e-11</v>
+        <v>1.84172677109018e-11</v>
       </c>
     </row>
     <row r="31">
@@ -8022,124 +8022,124 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0003223038101612952</v>
+        <v>-0.0003223038101611841</v>
       </c>
       <c r="G31" t="n">
-        <v>-4.02879762701619e-05</v>
+        <v>-4.028797627014802e-05</v>
       </c>
       <c r="H31" t="n">
-        <v>-38.19300150411348</v>
+        <v>-38.19300150410032</v>
       </c>
       <c r="I31" t="n">
-        <v>-8057.595254032378</v>
+        <v>-8057.595254029604</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8457911393537922</v>
+        <v>-0.8457911393545802</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.7611372713163034</v>
+        <v>-0.7611372713168385</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.001559049602196257</v>
+        <v>-0.001559049602196457</v>
       </c>
       <c r="M31" t="n">
-        <v>0.002029479946406675</v>
+        <v>0.00202947994641545</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.05000005721098015</v>
+        <v>-0.05000005721099056</v>
       </c>
       <c r="O31" t="n">
-        <v>-1.900821841067412e-13</v>
+        <v>-4.795316946883113e-14</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.8461134431639535</v>
+        <v>-0.8461134431647414</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.7611372713178689</v>
+        <v>-0.7611372713171778</v>
       </c>
       <c r="R31" t="n">
-        <v>0.003139734310674283</v>
+        <v>0.003139734310674613</v>
       </c>
       <c r="S31" t="n">
-        <v>0.00202947994642285</v>
+        <v>0.002029479946420887</v>
       </c>
       <c r="T31" t="n">
-        <v>0.008961453069781296</v>
+        <v>0.008961453069770897</v>
       </c>
       <c r="U31" t="n">
-        <v>-1.900022251312968e-13</v>
+        <v>-4.795187645833391e-14</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.8457911393537922</v>
+        <v>-0.8457911393545802</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.7611372713163034</v>
+        <v>-0.7611372713168385</v>
       </c>
       <c r="X31" t="n">
-        <v>-0.001559049602196257</v>
+        <v>-0.001559049602196457</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.002029479946406675</v>
+        <v>0.00202947994641545</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.05000005721098015</v>
+        <v>-0.05000005721099056</v>
       </c>
       <c r="AA31" t="n">
-        <v>-1.900821841067412e-13</v>
+        <v>-4.795316946883113e-14</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.8461134431639535</v>
+        <v>-0.8461134431647414</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.7611372713178689</v>
+        <v>-0.7611372713171778</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.003139734310674283</v>
+        <v>0.003139734310674613</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.00202947994642285</v>
+        <v>0.002029479946420887</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.008961453069781296</v>
+        <v>0.008961453069770897</v>
       </c>
       <c r="AG31" t="n">
-        <v>-1.900022251312968e-13</v>
+        <v>-4.795187645833391e-14</v>
       </c>
       <c r="AH31" t="n">
-        <v>38.19300150411436</v>
+        <v>38.19300150409981</v>
       </c>
       <c r="AI31" t="n">
-        <v>4.703792910731863e-12</v>
+        <v>-4.632738637155853e-12</v>
       </c>
       <c r="AJ31" t="n">
-        <v>16.59335177284094</v>
+        <v>16.59335177284954</v>
       </c>
       <c r="AK31" t="n">
-        <v>-3.452880342758036e-14</v>
+        <v>-1.160616741602283e-14</v>
       </c>
       <c r="AL31" t="n">
-        <v>-99.09704529718634</v>
+        <v>-99.09704529722077</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.875832822406664e-11</v>
+        <v>-1.84741111297626e-11</v>
       </c>
       <c r="AN31" t="n">
-        <v>-38.19300150411436</v>
+        <v>-38.19300150409981</v>
       </c>
       <c r="AO31" t="n">
-        <v>-4.703792910731863e-12</v>
+        <v>4.632738637155853e-12</v>
       </c>
       <c r="AP31" t="n">
-        <v>-16.59335177284094</v>
+        <v>-16.59335177284954</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.452880342758036e-14</v>
+        <v>1.160616741602283e-14</v>
       </c>
       <c r="AR31" t="n">
-        <v>-33.64976888554113</v>
+        <v>-33.64976888557555</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.887201506178826e-11</v>
+        <v>-1.84741111297626e-11</v>
       </c>
     </row>
     <row r="32">
@@ -8173,112 +8173,112 @@
         <v>369.9427691489232</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8461134431639535</v>
+        <v>-0.8461134431647414</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.7611372713178689</v>
+        <v>-0.7611372713171778</v>
       </c>
       <c r="L32" t="n">
-        <v>0.003139734310674283</v>
+        <v>0.003139734310674613</v>
       </c>
       <c r="M32" t="n">
-        <v>0.00202947994642285</v>
+        <v>0.002029479946420887</v>
       </c>
       <c r="N32" t="n">
-        <v>0.008961453069781296</v>
+        <v>0.008961453069770897</v>
       </c>
       <c r="O32" t="n">
-        <v>-1.900022251312968e-13</v>
+        <v>-4.795187645833391e-14</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.8461134431654285</v>
+        <v>-0.8461134431651695</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.7611520690286349</v>
+        <v>-0.7611520690279437</v>
       </c>
       <c r="R32" t="n">
-        <v>0.001559049602196137</v>
+        <v>0.001559049602196688</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.0006683120527619788</v>
+        <v>-0.0006683120527639328</v>
       </c>
       <c r="T32" t="n">
-        <v>0.008961453069764045</v>
+        <v>0.008961453069759602</v>
       </c>
       <c r="U32" t="n">
-        <v>-1.900474795736123e-13</v>
+        <v>-4.795728302061472e-14</v>
       </c>
       <c r="V32" t="n">
-        <v>0.7611372713178689</v>
+        <v>0.7611372713171778</v>
       </c>
       <c r="W32" t="n">
-        <v>-0.8461134431639535</v>
+        <v>-0.8461134431647414</v>
       </c>
       <c r="X32" t="n">
-        <v>0.003139734310674283</v>
+        <v>0.003139734310674613</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.008961453069781296</v>
+        <v>-0.008961453069770897</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.00202947994642285</v>
+        <v>0.002029479946420887</v>
       </c>
       <c r="AA32" t="n">
-        <v>-1.900022251312968e-13</v>
+        <v>-4.795187645833391e-14</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.7611520690286349</v>
+        <v>0.7611520690279437</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.8461134431654285</v>
+        <v>-0.8461134431651695</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.001559049602196137</v>
+        <v>0.001559049602196688</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.008961453069764045</v>
+        <v>-0.008961453069759602</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.0006683120527619788</v>
+        <v>-0.0006683120527639328</v>
       </c>
       <c r="AG32" t="n">
-        <v>-1.900474795736123e-13</v>
+        <v>-4.795728302061472e-14</v>
       </c>
       <c r="AH32" t="n">
         <v>-1.753528725763317</v>
       </c>
       <c r="AI32" t="n">
-        <v>-4.718003765447065e-12</v>
+        <v>4.604316927725449e-12</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-0.4020961332603305</v>
+        <v>-0.4020961332587234</v>
       </c>
       <c r="AK32" t="n">
-        <v>-3.682470994803566e-14</v>
+        <v>-2.410918686912566e-14</v>
       </c>
       <c r="AL32" t="n">
-        <v>3.105659092588902</v>
+        <v>3.105659092582468</v>
       </c>
       <c r="AM32" t="n">
-        <v>-1.881517164292745e-11</v>
+        <v>1.84741111297626e-11</v>
       </c>
       <c r="AN32" t="n">
         <v>1.753528725763317</v>
       </c>
       <c r="AO32" t="n">
-        <v>4.718003765447065e-12</v>
+        <v>-4.604316927725449e-12</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.4020961332603305</v>
+        <v>0.4020961332587234</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.682470994803566e-14</v>
+        <v>2.410918686912566e-14</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.1111099734937417</v>
+        <v>0.1111099734873178</v>
       </c>
       <c r="AS32" t="n">
-        <v>-1.887201506178826e-11</v>
+        <v>1.84741111297626e-11</v>
       </c>
     </row>
     <row r="33">
@@ -8300,124 +8300,124 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.0003223038101615172</v>
+        <v>-0.0003223038101612952</v>
       </c>
       <c r="G33" t="n">
-        <v>-4.028797627018965e-05</v>
+        <v>-4.02879762701619e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>-38.19300150413979</v>
+        <v>-38.19300150411348</v>
       </c>
       <c r="I33" t="n">
-        <v>-8057.595254037929</v>
+        <v>-8057.595254032378</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.8461134431654285</v>
+        <v>-0.8461134431651695</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.7611520690286349</v>
+        <v>-0.7611520690279437</v>
       </c>
       <c r="L33" t="n">
-        <v>0.001559049602196137</v>
+        <v>0.001559049602196688</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.0006683120527619788</v>
+        <v>-0.0006683120527639328</v>
       </c>
       <c r="N33" t="n">
-        <v>0.008961453069764045</v>
+        <v>0.008961453069759602</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.900474795736123e-13</v>
+        <v>-4.795728302061472e-14</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.845791139355267</v>
+        <v>-0.8457911393550082</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.7611520690270692</v>
+        <v>-0.7611520690276043</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.003139734310674162</v>
+        <v>-0.003139734310674845</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.0006683120527781236</v>
+        <v>-0.0006683120527693941</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.05000005721099737</v>
+        <v>-0.05000005721100176</v>
       </c>
       <c r="U33" t="n">
-        <v>-1.899677898334275e-13</v>
+        <v>-4.797347225031697e-14</v>
       </c>
       <c r="V33" t="n">
-        <v>0.8461134431654285</v>
+        <v>0.8461134431651695</v>
       </c>
       <c r="W33" t="n">
-        <v>-0.7611520690286349</v>
+        <v>-0.7611520690279437</v>
       </c>
       <c r="X33" t="n">
-        <v>-0.001559049602196137</v>
+        <v>-0.001559049602196688</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.0006683120527619788</v>
+        <v>0.0006683120527639328</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.008961453069764045</v>
+        <v>0.008961453069759602</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.900474795736123e-13</v>
+        <v>4.795728302061472e-14</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.845791139355267</v>
+        <v>0.8457911393550082</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.7611520690270692</v>
+        <v>-0.7611520690276043</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.003139734310674162</v>
+        <v>0.003139734310674845</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.0006683120527781236</v>
+        <v>0.0006683120527693941</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.05000005721099737</v>
+        <v>-0.05000005721100176</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.899677898334275e-13</v>
+        <v>4.797347225031697e-14</v>
       </c>
       <c r="AH33" t="n">
-        <v>38.19300150414347</v>
+        <v>38.19300150411436</v>
       </c>
       <c r="AI33" t="n">
-        <v>-4.746425474877469e-12</v>
+        <v>4.618527782440651e-12</v>
       </c>
       <c r="AJ33" t="n">
-        <v>16.59335177285531</v>
+        <v>16.59335177285886</v>
       </c>
       <c r="AK33" t="n">
-        <v>-3.446266709505874e-14</v>
+        <v>-1.165777543943314e-14</v>
       </c>
       <c r="AL33" t="n">
-        <v>-33.64976888559865</v>
+        <v>-33.64976888561286</v>
       </c>
       <c r="AM33" t="n">
-        <v>-1.892885848064907e-11</v>
+        <v>1.84741111297626e-11</v>
       </c>
       <c r="AN33" t="n">
-        <v>-38.19300150414347</v>
+        <v>-38.19300150411436</v>
       </c>
       <c r="AO33" t="n">
-        <v>4.746425474877469e-12</v>
+        <v>-4.618527782440651e-12</v>
       </c>
       <c r="AP33" t="n">
-        <v>-16.59335177285531</v>
+        <v>-16.59335177285886</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.446266709505874e-14</v>
+        <v>1.165777543943314e-14</v>
       </c>
       <c r="AR33" t="n">
-        <v>-99.09704529724382</v>
+        <v>-99.09704529725796</v>
       </c>
       <c r="AS33" t="n">
-        <v>-1.904254531837068e-11</v>
+        <v>1.84741111297626e-11</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/validation_frame_nodal_loads.xlsx
+++ b/outputs/validation_frame_nodal_loads.xlsx
@@ -643,25 +643,25 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.008506800363761516</v>
+        <v>-0.008506800363843648</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3200869679146637</v>
+        <v>-0.3200869679146143</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.001454028388444138</v>
+        <v>-0.001454028388443931</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1813005936458008</v>
+        <v>0.1813005936457907</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008825836814662386</v>
+        <v>0.0008825836814519907</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.285603354946163e-15</v>
+        <v>-3.950848033461115e-14</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3202032899265501</v>
+        <v>0.3202032899265028</v>
       </c>
     </row>
     <row r="7">
@@ -678,25 +678,25 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.008506800363690507</v>
+        <v>-0.008506800363530128</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3199836416745839</v>
+        <v>-0.3199836416745343</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.000121566495562611</v>
+        <v>-0.0001215664955624709</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03205627621730149</v>
+        <v>0.0320562762172913</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008825836814785056</v>
+        <v>0.0008825836815066833</v>
       </c>
       <c r="J7" t="n">
-        <v>-9.295205578831507e-15</v>
+        <v>-3.953174045802473e-14</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3200967218985052</v>
+        <v>0.3200967218984515</v>
       </c>
     </row>
     <row r="8">
@@ -713,25 +713,25 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.008617658990396852</v>
+        <v>-0.008617658990236473</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3199836416746615</v>
+        <v>-0.319983641674853</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001454028388444068</v>
+        <v>0.001454028388443984</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03205627621731389</v>
+        <v>0.03205627621734609</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.006590736799541642</v>
+        <v>-0.006590736799513456</v>
       </c>
       <c r="J8" t="n">
-        <v>-9.296542609148836e-15</v>
+        <v>-3.95222817975377e-14</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3201029665348439</v>
+        <v>0.3201029665350309</v>
       </c>
     </row>
     <row r="9">
@@ -748,25 +748,25 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.008617658990467861</v>
+        <v>-0.008617658990549991</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3200869679147415</v>
+        <v>-0.3200869679149329</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001215664955626805</v>
+        <v>0.0001215664955624186</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1813005936458132</v>
+        <v>0.1813005936458454</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.006590736799553908</v>
+        <v>-0.006590736799568158</v>
       </c>
       <c r="J9" t="n">
-        <v>-9.303613152494448e-15</v>
+        <v>-3.952324315212423e-14</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3202029760226185</v>
+        <v>0.320202976022812</v>
       </c>
     </row>
     <row r="10">
@@ -783,25 +783,25 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.07036120329889795</v>
+        <v>-0.07036120329910434</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6912454096231312</v>
+        <v>-0.6912454096229569</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.002332846674625141</v>
+        <v>-0.002332846674624704</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0004776631797337471</v>
+        <v>0.0004776631797100466</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.03553489535897476</v>
+        <v>-0.0355348953589887</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.254982535921031e-14</v>
+        <v>-1.010899116652667e-13</v>
       </c>
       <c r="K10" t="n">
-        <v>0.69482109742604</v>
+        <v>0.6948210974258875</v>
       </c>
     </row>
     <row r="11">
@@ -818,25 +818,25 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.07036120329871685</v>
+        <v>-0.07036120329830216</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6908036589437132</v>
+        <v>-0.6908036589435386</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.000790342354239219</v>
+        <v>-0.0007903423542390336</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0334916199497208</v>
+        <v>0.03349161994969708</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.03553489535896087</v>
+        <v>-0.03553489535892964</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.253216035953992e-14</v>
+        <v>-1.010500600582059e-13</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6943781525802077</v>
+        <v>0.694378152579992</v>
       </c>
     </row>
     <row r="12">
@@ -853,25 +853,25 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.06987906847877449</v>
+        <v>-0.06987906847835977</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6908036589438927</v>
+        <v>-0.6908036589443535</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002332846674625</v>
+        <v>0.00233284667462481</v>
       </c>
       <c r="H12" t="n">
-        <v>0.03349161994973283</v>
+        <v>0.03349161994976197</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0002044443358560187</v>
+        <v>0.0002044443358872198</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.255910051777855e-14</v>
+        <v>-1.010917419802469e-13</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6943329328177792</v>
+        <v>0.6943329328181957</v>
       </c>
     </row>
     <row r="13">
@@ -888,25 +888,25 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.06987906847895559</v>
+        <v>-0.06987906847916199</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6912454096233109</v>
+        <v>-0.6912454096237716</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000790342354239359</v>
+        <v>0.0007903423542389292</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0004776631797457648</v>
+        <v>0.0004776631797749287</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0002044443358421079</v>
+        <v>0.0002044443358281631</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.255697836653975e-14</v>
+        <v>-1.010136040492752e-13</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6947689725209542</v>
+        <v>0.6947689725214332</v>
       </c>
     </row>
     <row r="14">
@@ -923,25 +923,25 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4537190030253384</v>
+        <v>-0.4537190030256291</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7504936950267934</v>
+        <v>-0.7504936950263797</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.003032168184686789</v>
+        <v>-0.003032168184686173</v>
       </c>
       <c r="H14" t="n">
-        <v>0.006590736799546265</v>
+        <v>0.006590736799522585</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0290784907041432</v>
+        <v>-0.02907849070414583</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.586128221406856e-14</v>
+        <v>-1.611412101213256e-13</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8769896886652527</v>
+        <v>0.8769896886650491</v>
       </c>
     </row>
     <row r="15">
@@ -958,25 +958,25 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4537190030250376</v>
+        <v>-0.4537190030243844</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7505876822825513</v>
+        <v>-0.7505876822821378</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.00145657330068003</v>
+        <v>-0.001456573300679839</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0008825836814738829</v>
+        <v>-0.0008825836814975517</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0290784907041274</v>
+        <v>-0.02907849070410424</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.586244829761654e-14</v>
+        <v>-1.611526070967156e-13</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8770660887904096</v>
+        <v>0.8770660887897178</v>
       </c>
     </row>
     <row r="16">
@@ -993,25 +993,25 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4537911944462054</v>
+        <v>-0.4537911944455522</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7505876822828246</v>
+        <v>-0.7505876822834716</v>
       </c>
       <c r="G16" t="n">
-        <v>0.003032168184686586</v>
+        <v>0.003032168184686301</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0008825836814639399</v>
+        <v>-0.0008825836814504936</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1913477001707182</v>
+        <v>-0.1913477001706949</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.584592144909157e-14</v>
+        <v>-1.611381091097773e-13</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8771074683272948</v>
+        <v>0.8771074683275105</v>
       </c>
     </row>
     <row r="17">
@@ -1028,25 +1028,25 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4537911944465061</v>
+        <v>-0.453791194446797</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7504936950270665</v>
+        <v>-0.7504936950277137</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001456573300680231</v>
+        <v>0.001456573300679713</v>
       </c>
       <c r="H17" t="n">
-        <v>0.006590736799556234</v>
+        <v>0.006590736799569702</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1913477001707339</v>
+        <v>-0.1913477001707365</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.591934838764536e-14</v>
+        <v>-1.612105836505838e-13</v>
       </c>
       <c r="K17" t="n">
-        <v>0.87702300770182</v>
+        <v>0.8770230077025242</v>
       </c>
     </row>
     <row r="18">
@@ -1063,25 +1063,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8457911393550082</v>
+        <v>-0.845791139355267</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7611520690276043</v>
+        <v>-0.7611520690270692</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.003139734310674845</v>
+        <v>-0.003139734310674162</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0006683120527693941</v>
+        <v>-0.0006683120527781236</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.05000005721100176</v>
+        <v>-0.05000005721099737</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.797347225031697e-14</v>
+        <v>-1.899677898334275e-13</v>
       </c>
       <c r="K18" t="n">
-        <v>1.137859825078638</v>
+        <v>1.137859825078472</v>
       </c>
     </row>
     <row r="19">
@@ -1098,25 +1098,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8457911393545802</v>
+        <v>-0.8457911393537922</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7611372713168385</v>
+        <v>-0.7611372713163034</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.001559049602196457</v>
+        <v>-0.001559049602196257</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00202947994641545</v>
+        <v>0.002029479946406675</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.05000005721099056</v>
+        <v>-0.05000005721098015</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.795316946883113e-14</v>
+        <v>-1.900821841067412e-13</v>
       </c>
       <c r="K19" t="n">
-        <v>1.137846662707249</v>
+        <v>1.137846662706305</v>
       </c>
     </row>
     <row r="20">
@@ -1133,25 +1133,25 @@
         <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8461134431647414</v>
+        <v>-0.8461134431639535</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7611372713171778</v>
+        <v>-0.7611372713178689</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003139734310674613</v>
+        <v>0.003139734310674283</v>
       </c>
       <c r="H20" t="n">
-        <v>0.002029479946420887</v>
+        <v>0.00202947994642285</v>
       </c>
       <c r="I20" t="n">
-        <v>0.008961453069770897</v>
+        <v>0.008961453069781296</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.795187645833391e-14</v>
+        <v>-1.900022251312968e-13</v>
       </c>
       <c r="K20" t="n">
-        <v>1.138089523026987</v>
+        <v>1.138089523026864</v>
       </c>
     </row>
     <row r="21">
@@ -1168,25 +1168,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8461134431651695</v>
+        <v>-0.8461134431654285</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7611520690279437</v>
+        <v>-0.7611520690286349</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001559049602196688</v>
+        <v>0.001559049602196137</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0006683120527639328</v>
+        <v>-0.0006683120527619788</v>
       </c>
       <c r="I21" t="n">
-        <v>0.008961453069759602</v>
+        <v>0.008961453069764045</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.795728302061472e-14</v>
+        <v>-1.900474795736123e-13</v>
       </c>
       <c r="K21" t="n">
-        <v>1.138096156537751</v>
+        <v>1.138096156538405</v>
       </c>
     </row>
   </sheetData>
@@ -1245,16 +1245,16 @@
         <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>1.138096156537751</v>
+        <v>1.138096156538405</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.8461134431651695</v>
+        <v>-0.8461134431654285</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7611520690279437</v>
+        <v>-0.7611520690286349</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001559049602196688</v>
+        <v>0.001559049602196137</v>
       </c>
     </row>
     <row r="3">
@@ -1267,16 +1267,16 @@
         <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.8461134431651695</v>
+        <v>-0.8461134431654285</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.8461134431651695</v>
+        <v>-0.8461134431654285</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7611520690279437</v>
+        <v>-0.7611520690286349</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001559049602196688</v>
+        <v>0.001559049602196137</v>
       </c>
     </row>
     <row r="4">
@@ -1289,16 +1289,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.7611520690279437</v>
+        <v>-0.7611520690286349</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8461134431651695</v>
+        <v>-0.8461134431654285</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7611520690279437</v>
+        <v>-0.7611520690286349</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001559049602196688</v>
+        <v>0.001559049602196137</v>
       </c>
     </row>
     <row r="5">
@@ -1308,19 +1308,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.003139734310674845</v>
+        <v>0.003139734310674283</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8457911393550082</v>
+        <v>-0.8461134431639535</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7611520690276043</v>
+        <v>-0.7611372713178689</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.003139734310674845</v>
+        <v>0.003139734310674283</v>
       </c>
     </row>
   </sheetData>
@@ -1379,22 +1379,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.751456014012857</v>
+        <v>2.751456014022573</v>
       </c>
       <c r="C2" t="n">
-        <v>-55.20765387894221</v>
+        <v>-55.20765387894689</v>
       </c>
       <c r="D2" t="n">
-        <v>229.7364853741738</v>
+        <v>229.7364853741411</v>
       </c>
       <c r="E2" t="n">
-        <v>31.46052233893406</v>
+        <v>31.46052233895557</v>
       </c>
       <c r="F2" t="n">
-        <v>7.601256117753555</v>
+        <v>7.601256117793246</v>
       </c>
       <c r="G2" t="n">
-        <v>2.642825570253907e-14</v>
+        <v>1.124472132600471e-13</v>
       </c>
     </row>
     <row r="3">
@@ -1402,22 +1402,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2.751456014004419</v>
+        <v>2.75145601398571</v>
       </c>
       <c r="C3" t="n">
-        <v>55.2076538789276</v>
+        <v>55.2076538789229</v>
       </c>
       <c r="D3" t="n">
-        <v>19.20750629889254</v>
+        <v>19.2075062988704</v>
       </c>
       <c r="E3" t="n">
-        <v>-189.3446060375859</v>
+        <v>-189.3446060375642</v>
       </c>
       <c r="F3" t="n">
-        <v>7.601256117719164</v>
+        <v>7.601256117642186</v>
       </c>
       <c r="G3" t="n">
-        <v>2.645558510898198e-14</v>
+        <v>1.125134151497627e-13</v>
       </c>
     </row>
     <row r="4">
@@ -1425,22 +1425,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>-2.751456014029591</v>
+        <v>-2.751456014048294</v>
       </c>
       <c r="C4" t="n">
-        <v>55.20765387893758</v>
+        <v>55.20765387896097</v>
       </c>
       <c r="D4" t="n">
-        <v>-229.7364853741628</v>
+        <v>-229.7364853741495</v>
       </c>
       <c r="E4" t="n">
-        <v>-189.344606037625</v>
+        <v>-189.344606037719</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.37722281042796</v>
+        <v>-3.377222810504925</v>
       </c>
       <c r="G4" t="n">
-        <v>2.645939050296207e-14</v>
+        <v>1.124864943468381e-13</v>
       </c>
     </row>
     <row r="5">
@@ -1448,22 +1448,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-2.751456014021153</v>
+        <v>-2.751456014011439</v>
       </c>
       <c r="C5" t="n">
-        <v>-55.20765387893223</v>
+        <v>-55.20765387890883</v>
       </c>
       <c r="D5" t="n">
-        <v>-19.20750629890353</v>
+        <v>-19.20750629886214</v>
       </c>
       <c r="E5" t="n">
-        <v>31.46052233889492</v>
+        <v>31.4605223388009</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.377222810393567</v>
+        <v>-3.377222810353881</v>
       </c>
       <c r="G5" t="n">
-        <v>2.647951435709958e-14</v>
+        <v>1.12489230509892e-13</v>
       </c>
     </row>
   </sheetData>
@@ -1606,52 +1606,52 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.001454028388444138</v>
+        <v>-0.001454028388443931</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0002423380647406897</v>
+        <v>-0.0002423380647406551</v>
       </c>
       <c r="H2" t="n">
-        <v>-229.7364853741738</v>
+        <v>-229.736485374141</v>
       </c>
       <c r="I2" t="n">
-        <v>-48467.61294813793</v>
+        <v>-48467.61294813102</v>
       </c>
       <c r="J2" t="n">
-        <v>229.7364853741738</v>
+        <v>229.7364853741411</v>
       </c>
       <c r="K2" t="n">
-        <v>-55.20765387894221</v>
+        <v>-55.20765387894689</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.751456014012857</v>
+        <v>-2.751456014022573</v>
       </c>
       <c r="M2" t="n">
-        <v>2.642825570253907e-14</v>
+        <v>1.124472132600471e-13</v>
       </c>
       <c r="N2" t="n">
-        <v>7.601256117753555</v>
+        <v>7.601256117793246</v>
       </c>
       <c r="O2" t="n">
-        <v>-31.46052233893405</v>
+        <v>-31.46052233895557</v>
       </c>
       <c r="P2" t="n">
-        <v>-229.7364853741738</v>
+        <v>-229.7364853741411</v>
       </c>
       <c r="Q2" t="n">
-        <v>55.20765387894221</v>
+        <v>55.20765387894689</v>
       </c>
       <c r="R2" t="n">
-        <v>2.751456014012857</v>
+        <v>2.751456014022573</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.642825570253907e-14</v>
+        <v>-1.124472132600471e-13</v>
       </c>
       <c r="T2" t="n">
-        <v>8.907479966323589</v>
+        <v>8.907479966342192</v>
       </c>
       <c r="U2" t="n">
-        <v>-299.7854009347192</v>
+        <v>-299.7854009347257</v>
       </c>
     </row>
     <row r="3">
@@ -1673,52 +1673,52 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.000121566495562611</v>
+        <v>-0.0001215664955624709</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.02610825937685e-05</v>
+        <v>-2.026108259374515e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>-19.20750629889253</v>
+        <v>-19.2075062988704</v>
       </c>
       <c r="I3" t="n">
-        <v>-4052.216518753698</v>
+        <v>-4052.216518749029</v>
       </c>
       <c r="J3" t="n">
-        <v>19.20750629889254</v>
+        <v>19.2075062988704</v>
       </c>
       <c r="K3" t="n">
-        <v>55.2076538789276</v>
+        <v>55.2076538789229</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.751456014004419</v>
+        <v>-2.75145601398571</v>
       </c>
       <c r="M3" t="n">
-        <v>2.645558510898198e-14</v>
+        <v>1.125134151497627e-13</v>
       </c>
       <c r="N3" t="n">
-        <v>7.601256117719164</v>
+        <v>7.601256117642186</v>
       </c>
       <c r="O3" t="n">
-        <v>189.3446060375859</v>
+        <v>189.3446060375642</v>
       </c>
       <c r="P3" t="n">
-        <v>-19.20750629889254</v>
+        <v>-19.2075062988704</v>
       </c>
       <c r="Q3" t="n">
-        <v>-55.2076538789276</v>
+        <v>-55.2076538789229</v>
       </c>
       <c r="R3" t="n">
-        <v>2.751456014004419</v>
+        <v>2.75145601398571</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.645558510898198e-14</v>
+        <v>-1.125134151497627e-13</v>
       </c>
       <c r="T3" t="n">
-        <v>8.907479966307353</v>
+        <v>8.907479966272078</v>
       </c>
       <c r="U3" t="n">
-        <v>141.9013172359797</v>
+        <v>141.9013172359731</v>
       </c>
     </row>
     <row r="4">
@@ -1740,52 +1740,52 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001454028388444068</v>
+        <v>0.001454028388443984</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002423380647406781</v>
+        <v>0.000242338064740664</v>
       </c>
       <c r="H4" t="n">
-        <v>229.7364853741628</v>
+        <v>229.7364853741495</v>
       </c>
       <c r="I4" t="n">
-        <v>48467.61294813561</v>
+        <v>48467.6129481328</v>
       </c>
       <c r="J4" t="n">
-        <v>-229.7364853741628</v>
+        <v>-229.7364853741495</v>
       </c>
       <c r="K4" t="n">
-        <v>55.20765387893758</v>
+        <v>55.20765387896097</v>
       </c>
       <c r="L4" t="n">
-        <v>2.751456014029591</v>
+        <v>2.751456014048294</v>
       </c>
       <c r="M4" t="n">
-        <v>2.645939050296207e-14</v>
+        <v>1.124864943468381e-13</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.377222810427959</v>
+        <v>-3.377222810504925</v>
       </c>
       <c r="O4" t="n">
-        <v>189.344606037625</v>
+        <v>189.344606037719</v>
       </c>
       <c r="P4" t="n">
-        <v>229.7364853741628</v>
+        <v>229.7364853741495</v>
       </c>
       <c r="Q4" t="n">
-        <v>-55.20765387893758</v>
+        <v>-55.20765387896097</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.751456014029591</v>
+        <v>-2.751456014048294</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.645939050296207e-14</v>
+        <v>-1.124864943468381e-13</v>
       </c>
       <c r="T4" t="n">
-        <v>-13.13151327374959</v>
+        <v>-13.13151327378484</v>
       </c>
       <c r="U4" t="n">
-        <v>141.9013172360004</v>
+        <v>141.9013172360468</v>
       </c>
     </row>
     <row r="5">
@@ -1807,52 +1807,52 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001215664955626805</v>
+        <v>0.0001215664955624186</v>
       </c>
       <c r="G5" t="n">
-        <v>2.026108259378009e-05</v>
+        <v>2.026108259373643e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>19.20750629890352</v>
+        <v>19.20750629886214</v>
       </c>
       <c r="I5" t="n">
-        <v>4052.216518756018</v>
+        <v>4052.216518747287</v>
       </c>
       <c r="J5" t="n">
-        <v>-19.20750629890353</v>
+        <v>-19.20750629886214</v>
       </c>
       <c r="K5" t="n">
-        <v>-55.20765387893223</v>
+        <v>-55.20765387890883</v>
       </c>
       <c r="L5" t="n">
-        <v>2.751456014021153</v>
+        <v>2.751456014011439</v>
       </c>
       <c r="M5" t="n">
-        <v>2.647951435709958e-14</v>
+        <v>1.12489230509892e-13</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.377222810393566</v>
+        <v>-3.377222810353881</v>
       </c>
       <c r="O5" t="n">
-        <v>-31.4605223388949</v>
+        <v>-31.4605223388009</v>
       </c>
       <c r="P5" t="n">
-        <v>19.20750629890353</v>
+        <v>19.20750629886214</v>
       </c>
       <c r="Q5" t="n">
-        <v>55.20765387893223</v>
+        <v>55.20765387890883</v>
       </c>
       <c r="R5" t="n">
-        <v>-2.751456014021153</v>
+        <v>-2.751456014011439</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.647951435709958e-14</v>
+        <v>-1.12489230509892e-13</v>
       </c>
       <c r="T5" t="n">
-        <v>-13.13151327373335</v>
+        <v>-13.13151327371476</v>
       </c>
       <c r="U5" t="n">
-        <v>-299.7854009346985</v>
+        <v>-299.7854009346521</v>
       </c>
     </row>
     <row r="6">
@@ -1874,52 +1874,52 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0008788182861810029</v>
+        <v>-0.0008788182861807735</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0001464697143635005</v>
+        <v>-0.0001464697143634622</v>
       </c>
       <c r="H6" t="n">
-        <v>-138.8532892165985</v>
+        <v>-138.8532892165622</v>
       </c>
       <c r="I6" t="n">
-        <v>-29293.9428727001</v>
+        <v>-29293.94287269245</v>
       </c>
       <c r="J6" t="n">
-        <v>138.8532892165985</v>
+        <v>138.8532892165622</v>
       </c>
       <c r="K6" t="n">
-        <v>-42.9634944294736</v>
+        <v>-42.9634944294793</v>
       </c>
       <c r="L6" t="n">
-        <v>10.38529125068932</v>
+        <v>10.38529125067953</v>
       </c>
       <c r="M6" t="n">
-        <v>3.775201647367488e-14</v>
+        <v>1.752702276334041e-13</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.206939262141617</v>
+        <v>-4.206939262112485</v>
       </c>
       <c r="O6" t="n">
-        <v>-262.6994518333104</v>
+        <v>-262.6994518333376</v>
       </c>
       <c r="P6" t="n">
-        <v>-138.8532892165985</v>
+        <v>-138.8532892165622</v>
       </c>
       <c r="Q6" t="n">
-        <v>42.9634944294736</v>
+        <v>42.9634944294793</v>
       </c>
       <c r="R6" t="n">
-        <v>-10.38529125068932</v>
+        <v>-10.38529125067953</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.775201647367488e-14</v>
+        <v>-1.752702276334041e-13</v>
       </c>
       <c r="T6" t="n">
-        <v>-58.10480824199429</v>
+        <v>-58.10480824196471</v>
       </c>
       <c r="U6" t="n">
-        <v>4.918485256468898</v>
+        <v>4.918485256461651</v>
       </c>
     </row>
     <row r="7">
@@ -1941,52 +1941,52 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.000668775858676608</v>
+        <v>-0.0006687758586765627</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.000111462643112768</v>
+        <v>-0.0001114626431127605</v>
       </c>
       <c r="H7" t="n">
-        <v>-105.6665856709041</v>
+        <v>-105.6665856708969</v>
       </c>
       <c r="I7" t="n">
-        <v>-22292.5286225536</v>
+        <v>-22292.52862255209</v>
       </c>
       <c r="J7" t="n">
-        <v>105.6665856709041</v>
+        <v>105.6665856708969</v>
       </c>
       <c r="K7" t="n">
-        <v>42.96349442945541</v>
+        <v>42.96349442944967</v>
       </c>
       <c r="L7" t="n">
-        <v>10.38529125069712</v>
+        <v>10.38529125071589</v>
       </c>
       <c r="M7" t="n">
-        <v>3.767440976047779e-14</v>
+        <v>1.750906019389773e-13</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.206939262166223</v>
+        <v>-4.206939262224786</v>
       </c>
       <c r="O7" t="n">
-        <v>129.9526376503565</v>
+        <v>129.9526376503293</v>
       </c>
       <c r="P7" t="n">
-        <v>-105.6665856709041</v>
+        <v>-105.6665856708969</v>
       </c>
       <c r="Q7" t="n">
-        <v>-42.96349442945541</v>
+        <v>-42.96349442944967</v>
       </c>
       <c r="R7" t="n">
-        <v>-10.38529125069712</v>
+        <v>-10.38529125071589</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.767440976047779e-14</v>
+        <v>-1.750906019389773e-13</v>
       </c>
       <c r="T7" t="n">
-        <v>-58.10480824201649</v>
+        <v>-58.10480824207055</v>
       </c>
       <c r="U7" t="n">
-        <v>127.8283289263759</v>
+        <v>127.8283289263687</v>
       </c>
     </row>
     <row r="8">
@@ -2008,52 +2008,52 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>0.000878818286180932</v>
+        <v>0.0008788182861808262</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001464697143634887</v>
+        <v>0.000146469714363471</v>
       </c>
       <c r="H8" t="n">
-        <v>138.8532892165873</v>
+        <v>138.8532892165705</v>
       </c>
       <c r="I8" t="n">
-        <v>29293.94287269773</v>
+        <v>29293.94287269421</v>
       </c>
       <c r="J8" t="n">
-        <v>-138.8532892165873</v>
+        <v>-138.8532892165705</v>
       </c>
       <c r="K8" t="n">
-        <v>42.96349442946246</v>
+        <v>42.96349442948349</v>
       </c>
       <c r="L8" t="n">
-        <v>-10.38529125067246</v>
+        <v>-10.38529125065367</v>
       </c>
       <c r="M8" t="n">
-        <v>3.774728020148455e-14</v>
+        <v>1.752361559046339e-13</v>
       </c>
       <c r="N8" t="n">
-        <v>26.12743971182311</v>
+        <v>26.12743971176449</v>
       </c>
       <c r="O8" t="n">
-        <v>129.9526376503774</v>
+        <v>129.9526376504382</v>
       </c>
       <c r="P8" t="n">
-        <v>138.8532892165873</v>
+        <v>138.8532892165705</v>
       </c>
       <c r="Q8" t="n">
-        <v>-42.96349442946246</v>
+        <v>-42.96349442948349</v>
       </c>
       <c r="R8" t="n">
-        <v>10.38529125067246</v>
+        <v>10.38529125065367</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.774728020148455e-14</v>
+        <v>-1.752361559046339e-13</v>
       </c>
       <c r="T8" t="n">
-        <v>36.18430779221164</v>
+        <v>36.18430779215749</v>
       </c>
       <c r="U8" t="n">
-        <v>127.8283289263974</v>
+        <v>127.8283289264627</v>
       </c>
     </row>
     <row r="9">
@@ -2075,52 +2075,52 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0006687758586766784</v>
+        <v>0.0006687758586765106</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001114626431127797</v>
+        <v>0.0001114626431127518</v>
       </c>
       <c r="H9" t="n">
-        <v>105.6665856709152</v>
+        <v>105.6665856708887</v>
       </c>
       <c r="I9" t="n">
-        <v>22292.52862255594</v>
+        <v>22292.52862255035</v>
       </c>
       <c r="J9" t="n">
-        <v>-105.6665856709152</v>
+        <v>-105.6665856708887</v>
       </c>
       <c r="K9" t="n">
-        <v>-42.96349442946655</v>
+        <v>-42.96349442944549</v>
       </c>
       <c r="L9" t="n">
-        <v>-10.38529125068024</v>
+        <v>-10.38529125069003</v>
       </c>
       <c r="M9" t="n">
-        <v>3.772111637843662e-14</v>
+        <v>1.750110271688143e-13</v>
       </c>
       <c r="N9" t="n">
-        <v>26.12743971184766</v>
+        <v>26.12743971187681</v>
       </c>
       <c r="O9" t="n">
-        <v>-262.6994518332895</v>
+        <v>-262.6994518332286</v>
       </c>
       <c r="P9" t="n">
-        <v>105.6665856709152</v>
+        <v>105.6665856708887</v>
       </c>
       <c r="Q9" t="n">
-        <v>42.96349442946655</v>
+        <v>42.96349442944549</v>
       </c>
       <c r="R9" t="n">
-        <v>10.38529125068024</v>
+        <v>10.38529125069003</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.772111637843662e-14</v>
+        <v>-1.750110271688143e-13</v>
       </c>
       <c r="T9" t="n">
-        <v>36.18430779223377</v>
+        <v>36.18430779226336</v>
       </c>
       <c r="U9" t="n">
-        <v>4.918485256490328</v>
+        <v>4.918485256555641</v>
       </c>
     </row>
     <row r="10">
@@ -2142,52 +2142,52 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.000699321510061648</v>
+        <v>-0.0006993215100614693</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0001165535850102747</v>
+        <v>-0.0001165535850102449</v>
       </c>
       <c r="H10" t="n">
-        <v>-110.4927985897404</v>
+        <v>-110.4927985897122</v>
       </c>
       <c r="I10" t="n">
-        <v>-23310.71700205493</v>
+        <v>-23310.71700204898</v>
       </c>
       <c r="J10" t="n">
-        <v>110.4927985897404</v>
+        <v>110.4927985897122</v>
       </c>
       <c r="K10" t="n">
-        <v>9.38396108156951</v>
+        <v>9.383961081545465</v>
       </c>
       <c r="L10" t="n">
-        <v>-46.74768491248135</v>
+        <v>-46.7476849124899</v>
       </c>
       <c r="M10" t="n">
-        <v>3.788645412536577e-14</v>
+        <v>1.709152340672448e-13</v>
       </c>
       <c r="N10" t="n">
-        <v>135.4653152928687</v>
+        <v>135.4653152928859</v>
       </c>
       <c r="O10" t="n">
-        <v>32.67555772336971</v>
+        <v>32.6755577232978</v>
       </c>
       <c r="P10" t="n">
-        <v>-110.4927985897404</v>
+        <v>-110.4927985897122</v>
       </c>
       <c r="Q10" t="n">
-        <v>-9.38396108156951</v>
+        <v>-9.383961081545465</v>
       </c>
       <c r="R10" t="n">
-        <v>46.74768491248135</v>
+        <v>46.7476849124899</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.788645412536577e-14</v>
+        <v>-1.709152340672448e-13</v>
       </c>
       <c r="T10" t="n">
-        <v>145.0207941820194</v>
+        <v>145.0207941820534</v>
       </c>
       <c r="U10" t="n">
-        <v>23.62820876604724</v>
+        <v>23.6282087659751</v>
       </c>
     </row>
     <row r="11">
@@ -2209,52 +2209,52 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.000666230946440811</v>
+        <v>-0.0006662309464408056</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0001110384910734685</v>
+        <v>-0.0001110384910734676</v>
       </c>
       <c r="H11" t="n">
-        <v>-105.2644895376481</v>
+        <v>-105.2644895376473</v>
       </c>
       <c r="I11" t="n">
-        <v>-22207.6982146937</v>
+        <v>-22207.69821469352</v>
       </c>
       <c r="J11" t="n">
-        <v>105.2644895376481</v>
+        <v>105.2644895376473</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.38396108158932</v>
+        <v>-9.383961081613165</v>
       </c>
       <c r="L11" t="n">
-        <v>-46.74768491247382</v>
+        <v>-46.74768491245524</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7940050285295e-14</v>
+        <v>1.710610954172968e-13</v>
       </c>
       <c r="N11" t="n">
-        <v>135.4653152928447</v>
+        <v>135.4653152927949</v>
       </c>
       <c r="O11" t="n">
-        <v>-53.58879393185191</v>
+        <v>-53.58879393192353</v>
       </c>
       <c r="P11" t="n">
-        <v>-105.2644895376481</v>
+        <v>-105.2644895376473</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.38396108158932</v>
+        <v>9.383961081613165</v>
       </c>
       <c r="R11" t="n">
-        <v>46.74768491247382</v>
+        <v>46.74768491245524</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.7940050285295e-14</v>
+        <v>-1.710610954172968e-13</v>
       </c>
       <c r="T11" t="n">
-        <v>145.0207941819982</v>
+        <v>145.0207941819365</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.714972557683836</v>
+        <v>-2.714972557755459</v>
       </c>
     </row>
     <row r="12">
@@ -2276,52 +2276,52 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>0.000699321510061586</v>
+        <v>0.000699321510061491</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0001165535850102643</v>
+        <v>0.0001165535850102485</v>
       </c>
       <c r="H12" t="n">
-        <v>110.4927985897306</v>
+        <v>110.4927985897156</v>
       </c>
       <c r="I12" t="n">
-        <v>23310.71700205286</v>
+        <v>23310.7170020497</v>
       </c>
       <c r="J12" t="n">
-        <v>-110.4927985897306</v>
+        <v>-110.4927985897156</v>
       </c>
       <c r="K12" t="n">
-        <v>-9.38396108158247</v>
+        <v>-9.383961081568032</v>
       </c>
       <c r="L12" t="n">
-        <v>46.74768491249836</v>
+        <v>46.7476849125169</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7816336496814e-14</v>
+        <v>1.709011987532788e-13</v>
       </c>
       <c r="N12" t="n">
-        <v>1.505532197369803</v>
+        <v>1.505532197320065</v>
       </c>
       <c r="O12" t="n">
-        <v>-53.58879393183292</v>
+        <v>-53.58879393180126</v>
       </c>
       <c r="P12" t="n">
-        <v>110.4927985897306</v>
+        <v>110.4927985897156</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.38396108158247</v>
+        <v>9.383961081568032</v>
       </c>
       <c r="R12" t="n">
-        <v>-46.74768491249836</v>
+        <v>-46.7476849125169</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.7816336496814e-14</v>
+        <v>-1.709011987532788e-13</v>
       </c>
       <c r="T12" t="n">
-        <v>-281.99164167236</v>
+        <v>-281.9916416724216</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.714972557661781</v>
+        <v>-2.714972557606814</v>
       </c>
     </row>
     <row r="13">
@@ -2343,52 +2343,52 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0006662309464408723</v>
+        <v>0.0006662309464407836</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0001110384910734787</v>
+        <v>0.0001110384910734639</v>
       </c>
       <c r="H13" t="n">
-        <v>105.2644895376578</v>
+        <v>105.2644895376438</v>
       </c>
       <c r="I13" t="n">
-        <v>22207.69821469574</v>
+        <v>22207.69821469278</v>
       </c>
       <c r="J13" t="n">
-        <v>-105.2644895376578</v>
+        <v>-105.2644895376438</v>
       </c>
       <c r="K13" t="n">
-        <v>9.383961081576246</v>
+        <v>9.383961081590712</v>
       </c>
       <c r="L13" t="n">
-        <v>46.74768491249078</v>
+        <v>46.74768491248219</v>
       </c>
       <c r="M13" t="n">
-        <v>3.803136082930058e-14</v>
+        <v>1.713298650191092e-13</v>
       </c>
       <c r="N13" t="n">
-        <v>1.505532197393904</v>
+        <v>1.505532197411242</v>
       </c>
       <c r="O13" t="n">
-        <v>32.67555772338847</v>
+        <v>32.6755577234203</v>
       </c>
       <c r="P13" t="n">
-        <v>105.2644895376578</v>
+        <v>105.2644895376438</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.383961081576246</v>
+        <v>-9.383961081590712</v>
       </c>
       <c r="R13" t="n">
-        <v>-46.74768491249078</v>
+        <v>-46.74768491248219</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.803136082930058e-14</v>
+        <v>-1.713298650191092e-13</v>
       </c>
       <c r="T13" t="n">
-        <v>-281.9916416723386</v>
+        <v>-281.9916416723045</v>
       </c>
       <c r="U13" t="n">
-        <v>23.62820876606884</v>
+        <v>23.62820876612409</v>
       </c>
     </row>
     <row r="14">
@@ -2410,52 +2410,52 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0001075661259880563</v>
+        <v>-0.0001075661259879882</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.792768766467605e-05</v>
+        <v>-1.79276876646647e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>-16.99544790611289</v>
+        <v>-16.99544790610213</v>
       </c>
       <c r="I14" t="n">
-        <v>-3585.537532935209</v>
+        <v>-3585.537532932939</v>
       </c>
       <c r="J14" t="n">
-        <v>16.99544790611293</v>
+        <v>16.99544790610213</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.753528725748197</v>
+        <v>-1.753528725754137</v>
       </c>
       <c r="L14" t="n">
-        <v>-38.19300150411129</v>
+        <v>-38.19300150410469</v>
       </c>
       <c r="M14" t="n">
-        <v>3.44731562570147e-14</v>
+        <v>8.204488071905921e-14</v>
       </c>
       <c r="N14" t="n">
-        <v>130.0609637274092</v>
+        <v>130.0609637273842</v>
       </c>
       <c r="O14" t="n">
-        <v>-10.63228232795814</v>
+        <v>-10.63228232796507</v>
       </c>
       <c r="P14" t="n">
-        <v>-16.99544790611293</v>
+        <v>-16.99544790610213</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.753528725748197</v>
+        <v>1.753528725754137</v>
       </c>
       <c r="R14" t="n">
-        <v>38.19300150411129</v>
+        <v>38.19300150410469</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.44731562570147e-14</v>
+        <v>-8.204488071905921e-14</v>
       </c>
       <c r="T14" t="n">
-        <v>99.09704529725843</v>
+        <v>99.09704529724391</v>
       </c>
       <c r="U14" t="n">
-        <v>0.111109973468956</v>
+        <v>0.1111099734400796</v>
       </c>
     </row>
     <row r="15">
@@ -2477,52 +2477,52 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0001024763015164266</v>
+        <v>-0.0001024763015164182</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.70793835860711e-05</v>
+        <v>-1.707938358606969e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>-16.19125563959541</v>
+        <v>-16.19125563959407</v>
       </c>
       <c r="I15" t="n">
-        <v>-3415.876717214221</v>
+        <v>-3415.876717213939</v>
       </c>
       <c r="J15" t="n">
-        <v>16.19125563959543</v>
+        <v>16.19125563959406</v>
       </c>
       <c r="K15" t="n">
-        <v>1.753528725734071</v>
+        <v>1.753528725728103</v>
       </c>
       <c r="L15" t="n">
-        <v>-38.19300150409987</v>
+        <v>-38.19300150409149</v>
       </c>
       <c r="M15" t="n">
-        <v>3.441205256422615e-14</v>
+        <v>8.233802687468803e-14</v>
       </c>
       <c r="N15" t="n">
-        <v>130.0609637273784</v>
+        <v>130.0609637273625</v>
       </c>
       <c r="O15" t="n">
-        <v>7.415513261840374</v>
+        <v>7.415513261833325</v>
       </c>
       <c r="P15" t="n">
-        <v>-16.19125563959543</v>
+        <v>-16.19125563959406</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.753528725734071</v>
+        <v>-1.753528725728103</v>
       </c>
       <c r="R15" t="n">
-        <v>38.19300150409987</v>
+        <v>38.19300150409149</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.441205256422615e-14</v>
+        <v>-8.233802687468803e-14</v>
       </c>
       <c r="T15" t="n">
-        <v>99.0970452972208</v>
+        <v>99.09704529718621</v>
       </c>
       <c r="U15" t="n">
-        <v>3.10565909256411</v>
+        <v>3.10565909253512</v>
       </c>
     </row>
     <row r="16">
@@ -2544,52 +2544,52 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0001075661259880263</v>
+        <v>0.0001075661259879821</v>
       </c>
       <c r="G16" t="n">
-        <v>1.792768766467106e-05</v>
+        <v>1.792768766466369e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>16.99544790610816</v>
+        <v>16.99544790610117</v>
       </c>
       <c r="I16" t="n">
-        <v>3585.537532934211</v>
+        <v>3585.537532932737</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.99544790610815</v>
+        <v>-16.99544790610116</v>
       </c>
       <c r="K16" t="n">
-        <v>1.75352872573896</v>
+        <v>1.753528725738448</v>
       </c>
       <c r="L16" t="n">
-        <v>38.19300150412879</v>
+        <v>38.19300150413709</v>
       </c>
       <c r="M16" t="n">
-        <v>3.445541041092048e-14</v>
+        <v>8.215171483047837e-14</v>
       </c>
       <c r="N16" t="n">
-        <v>-262.8077779103483</v>
+        <v>-262.8077779103638</v>
       </c>
       <c r="O16" t="n">
-        <v>7.415513261851743</v>
+        <v>7.415513261841625</v>
       </c>
       <c r="P16" t="n">
-        <v>16.99544790610815</v>
+        <v>16.99544790610116</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.75352872573896</v>
+        <v>-1.753528725738448</v>
       </c>
       <c r="R16" t="n">
-        <v>-38.19300150412879</v>
+        <v>-38.19300150413709</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.445541041092048e-14</v>
+        <v>-8.215171483047837e-14</v>
       </c>
       <c r="T16" t="n">
-        <v>33.64976888557555</v>
+        <v>33.64976888554114</v>
       </c>
       <c r="U16" t="n">
-        <v>3.105659092582187</v>
+        <v>3.105659092589121</v>
       </c>
     </row>
     <row r="17">
@@ -2611,52 +2611,52 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>0.000102476301516457</v>
+        <v>0.0001024763015164238</v>
       </c>
       <c r="G17" t="n">
-        <v>1.707938358607617e-05</v>
+        <v>1.707938358607064e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>16.1912556396002</v>
+        <v>16.19125563959496</v>
       </c>
       <c r="I17" t="n">
-        <v>3415.876717215232</v>
+        <v>3415.876717214127</v>
       </c>
       <c r="J17" t="n">
-        <v>-16.1912556396002</v>
+        <v>-16.19125563959497</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.75352872574328</v>
+        <v>-1.75352872574382</v>
       </c>
       <c r="L17" t="n">
-        <v>38.19300150411733</v>
+        <v>38.19300150412386</v>
       </c>
       <c r="M17" t="n">
-        <v>3.426181395537433e-14</v>
+        <v>8.207424224246545e-14</v>
       </c>
       <c r="N17" t="n">
-        <v>-262.8077779103172</v>
+        <v>-262.8077779103419</v>
       </c>
       <c r="O17" t="n">
-        <v>-10.63228232794665</v>
+        <v>-10.63228232795689</v>
       </c>
       <c r="P17" t="n">
-        <v>16.1912556396002</v>
+        <v>16.19125563959497</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.75352872574328</v>
+        <v>1.75352872574382</v>
       </c>
       <c r="R17" t="n">
-        <v>-38.19300150411733</v>
+        <v>-38.19300150412386</v>
       </c>
       <c r="S17" t="n">
-        <v>-3.426181395537433e-14</v>
+        <v>-8.207424224246545e-14</v>
       </c>
       <c r="T17" t="n">
-        <v>33.64976888561318</v>
+        <v>33.64976888559887</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1111099734872596</v>
+        <v>0.1111099734938534</v>
       </c>
     </row>
     <row r="18">
@@ -2678,52 +2678,52 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0001033262400798596</v>
+        <v>0.0001033262400799706</v>
       </c>
       <c r="G18" t="n">
-        <v>1.291578000998245e-05</v>
+        <v>1.291578000999632e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>12.24415944946336</v>
+        <v>12.24415944947652</v>
       </c>
       <c r="I18" t="n">
-        <v>2583.15600199649</v>
+        <v>2583.156001999265</v>
       </c>
       <c r="J18" t="n">
-        <v>-12.24415944946668</v>
+        <v>-12.24415944947395</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.448352714485736e-13</v>
+        <v>-2.747801985947262e-13</v>
       </c>
       <c r="L18" t="n">
-        <v>88.67113776478836</v>
+        <v>88.6711377647799</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.618521718900091e-14</v>
+        <v>-1.167475404545426e-13</v>
       </c>
       <c r="N18" t="n">
-        <v>-437.5151472319706</v>
+        <v>-437.5151472319367</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.374012015276094e-12</v>
+        <v>-1.086242207293253e-12</v>
       </c>
       <c r="P18" t="n">
-        <v>12.24415944946668</v>
+        <v>12.24415944947395</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.448352714485736e-13</v>
+        <v>2.747801985947262e-13</v>
       </c>
       <c r="R18" t="n">
-        <v>-88.67113776478836</v>
+        <v>-88.6711377647799</v>
       </c>
       <c r="S18" t="n">
-        <v>2.618521718900091e-14</v>
+        <v>1.167475404545426e-13</v>
       </c>
       <c r="T18" t="n">
-        <v>-271.8539548863363</v>
+        <v>-271.8539548863024</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.384670156312495e-12</v>
+        <v>-1.111999381464557e-12</v>
       </c>
     </row>
     <row r="19">
@@ -2760,37 +2760,37 @@
         <v>13.13674726470185</v>
       </c>
       <c r="K19" t="n">
-        <v>3.410605131648481e-13</v>
+        <v>2.629008122312371e-13</v>
       </c>
       <c r="L19" t="n">
-        <v>2.212058392776836</v>
+        <v>2.212058392753398</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.646494134950217e-14</v>
+        <v>-1.169619956442602e-13</v>
       </c>
       <c r="N19" t="n">
-        <v>-4.70054070414116</v>
+        <v>-4.700540704047413</v>
       </c>
       <c r="O19" t="n">
-        <v>1.392663762089796e-12</v>
+        <v>1.023181539494544e-12</v>
       </c>
       <c r="P19" t="n">
         <v>-13.13674726470185</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.410605131648481e-13</v>
+        <v>-2.629008122312371e-13</v>
       </c>
       <c r="R19" t="n">
-        <v>-2.212058392776836</v>
+        <v>-2.212058392753398</v>
       </c>
       <c r="S19" t="n">
-        <v>2.646494134950217e-14</v>
+        <v>1.169619956442602e-13</v>
       </c>
       <c r="T19" t="n">
-        <v>-12.99592643807352</v>
+        <v>-12.99592643797977</v>
       </c>
       <c r="U19" t="n">
-        <v>1.392663762089796e-12</v>
+        <v>1.051603248924948e-12</v>
       </c>
     </row>
     <row r="20">
@@ -2812,52 +2812,52 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0001033262400799706</v>
+        <v>0.0001033262400798596</v>
       </c>
       <c r="G20" t="n">
-        <v>1.291578000999632e-05</v>
+        <v>1.291578000998245e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>12.24415944947652</v>
+        <v>12.24415944946336</v>
       </c>
       <c r="I20" t="n">
-        <v>2583.156001999265</v>
+        <v>2583.15600199649</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.24415944947395</v>
+        <v>-12.24415944946668</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.529398995283373e-13</v>
+        <v>-2.771116669464391e-13</v>
       </c>
       <c r="L20" t="n">
-        <v>-88.67113776479871</v>
+        <v>-88.67113776482549</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.618391614639393e-14</v>
+        <v>-1.167677066149508e-13</v>
       </c>
       <c r="N20" t="n">
-        <v>271.8539548863777</v>
+        <v>271.8539548864848</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.407318706014848e-12</v>
+        <v>-1.108002578575906e-12</v>
       </c>
       <c r="P20" t="n">
-        <v>12.24415944947395</v>
+        <v>12.24415944946668</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.529398995283373e-13</v>
+        <v>2.771116669464391e-13</v>
       </c>
       <c r="R20" t="n">
-        <v>88.67113776479871</v>
+        <v>88.67113776482549</v>
       </c>
       <c r="S20" t="n">
-        <v>2.618391614639393e-14</v>
+        <v>1.167677066149508e-13</v>
       </c>
       <c r="T20" t="n">
-        <v>437.515147232012</v>
+        <v>437.515147232119</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.415756401002e-12</v>
+        <v>-1.109334846205456e-12</v>
       </c>
     </row>
     <row r="21">
@@ -2879,52 +2879,52 @@
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0001108586267063449</v>
+        <v>-0.0001108586267063432</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.385732833829312e-05</v>
+        <v>-1.38573283382929e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>-13.13674726470188</v>
+        <v>-13.13674726470167</v>
       </c>
       <c r="I21" t="n">
-        <v>-2771.465667658624</v>
+        <v>-2771.46566765858</v>
       </c>
       <c r="J21" t="n">
-        <v>13.13674726470185</v>
+        <v>13.13674726470174</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.552713678800501e-13</v>
+        <v>-2.557953848736361e-13</v>
       </c>
       <c r="L21" t="n">
-        <v>2.212058392787033</v>
+        <v>2.212058392798944</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.653433028854124e-14</v>
+        <v>-1.168509733417977e-13</v>
       </c>
       <c r="N21" t="n">
-        <v>-12.99592643811431</v>
+        <v>-12.99592643816196</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.392663762089796e-12</v>
+        <v>-9.947598300641403e-13</v>
       </c>
       <c r="P21" t="n">
-        <v>-13.13674726470185</v>
+        <v>-13.13674726470174</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.552713678800501e-13</v>
+        <v>2.557953848736361e-13</v>
       </c>
       <c r="R21" t="n">
-        <v>-2.212058392787033</v>
+        <v>-2.212058392798944</v>
       </c>
       <c r="S21" t="n">
-        <v>2.653433028854124e-14</v>
+        <v>1.168509733417977e-13</v>
       </c>
       <c r="T21" t="n">
-        <v>-4.70054070418195</v>
+        <v>-4.700540704229594</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.449507180950604e-12</v>
+        <v>-9.947598300641403e-13</v>
       </c>
     </row>
     <row r="22">
@@ -2946,52 +2946,52 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0004417506794179848</v>
+        <v>0.0004417506794183179</v>
       </c>
       <c r="G22" t="n">
-        <v>5.521883492724811e-05</v>
+        <v>5.521883492728974e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>52.34745551103121</v>
+        <v>52.34745551107067</v>
       </c>
       <c r="I22" t="n">
-        <v>11043.76698544962</v>
+        <v>11043.76698545795</v>
       </c>
       <c r="J22" t="n">
-        <v>-52.34745551102969</v>
+        <v>-52.34745551107335</v>
       </c>
       <c r="K22" t="n">
-        <v>7.904787935331115e-14</v>
+        <v>-6.643574579356937e-13</v>
       </c>
       <c r="L22" t="n">
-        <v>13.97919724679529</v>
+        <v>13.97919724677558</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.964295475749168e-14</v>
+        <v>-1.260797022339943e-13</v>
       </c>
       <c r="N22" t="n">
-        <v>-37.59404297983836</v>
+        <v>-37.59404297975952</v>
       </c>
       <c r="O22" t="n">
-        <v>3.055333763768431e-13</v>
+        <v>-2.682298827494378e-12</v>
       </c>
       <c r="P22" t="n">
-        <v>52.34745551102969</v>
+        <v>52.34745551107335</v>
       </c>
       <c r="Q22" t="n">
-        <v>-7.904787935331115e-14</v>
+        <v>6.643574579356937e-13</v>
       </c>
       <c r="R22" t="n">
-        <v>-13.97919724679529</v>
+        <v>-13.97919724677558</v>
       </c>
       <c r="S22" t="n">
-        <v>2.964295475749168e-14</v>
+        <v>1.260797022339943e-13</v>
       </c>
       <c r="T22" t="n">
-        <v>-74.23953499452399</v>
+        <v>-74.23953499444512</v>
       </c>
       <c r="U22" t="n">
-        <v>3.268496584496461e-13</v>
+        <v>-2.636113549669972e-12</v>
       </c>
     </row>
     <row r="23">
@@ -3013,52 +3013,52 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0004821348199423592</v>
+        <v>0.0004821348199423869</v>
       </c>
       <c r="G23" t="n">
-        <v>6.02668524927949e-05</v>
+        <v>6.026685249279837e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>57.13297616316957</v>
+        <v>57.13297616317285</v>
       </c>
       <c r="I23" t="n">
-        <v>12053.37049855898</v>
+        <v>12053.37049855967</v>
       </c>
       <c r="J23" t="n">
-        <v>-57.13297616316959</v>
+        <v>-57.13297616317323</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.526512829121202e-14</v>
+        <v>6.679101716144942e-13</v>
       </c>
       <c r="L23" t="n">
-        <v>14.38129338005121</v>
+        <v>14.38129338002526</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.568778523226456e-14</v>
+        <v>-1.385142001097961e-13</v>
       </c>
       <c r="N23" t="n">
-        <v>-77.36050705082822</v>
+        <v>-77.36050705072442</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.410605131648481e-13</v>
+        <v>2.728484105318785e-12</v>
       </c>
       <c r="P23" t="n">
-        <v>57.13297616316959</v>
+        <v>57.13297616317323</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>-6.679101716144942e-13</v>
       </c>
       <c r="R23" t="n">
-        <v>-14.38129338005121</v>
+        <v>-14.38129338002526</v>
       </c>
       <c r="S23" t="n">
-        <v>2.568778523226456e-14</v>
+        <v>1.385142001097961e-13</v>
       </c>
       <c r="T23" t="n">
-        <v>-37.68983998958147</v>
+        <v>-37.68983998947769</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.410605131648481e-13</v>
+        <v>2.671640686457977e-12</v>
       </c>
     </row>
     <row r="24">
@@ -3080,52 +3080,52 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0004417506794182069</v>
+        <v>0.0004417506794180959</v>
       </c>
       <c r="G24" t="n">
-        <v>5.521883492727586e-05</v>
+        <v>5.521883492726198e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>52.34745551105752</v>
+        <v>52.34745551104436</v>
       </c>
       <c r="I24" t="n">
-        <v>11043.76698545517</v>
+        <v>11043.7669854524</v>
       </c>
       <c r="J24" t="n">
-        <v>-52.3474555110588</v>
+        <v>-52.34745551104425</v>
       </c>
       <c r="K24" t="n">
-        <v>6.661338147750939e-14</v>
+        <v>-6.45705711121991e-13</v>
       </c>
       <c r="L24" t="n">
-        <v>-13.97919724680534</v>
+        <v>-13.97919724682958</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.969423752025024e-14</v>
+        <v>-1.260634392014071e-13</v>
       </c>
       <c r="N24" t="n">
-        <v>74.23953499456417</v>
+        <v>74.23953499466113</v>
       </c>
       <c r="O24" t="n">
-        <v>2.593480985524366e-13</v>
+        <v>-2.62545540863357e-12</v>
       </c>
       <c r="P24" t="n">
-        <v>52.3474555110588</v>
+        <v>52.34745551104425</v>
       </c>
       <c r="Q24" t="n">
-        <v>-6.661338147750939e-14</v>
+        <v>6.45705711121991e-13</v>
       </c>
       <c r="R24" t="n">
-        <v>13.97919724680534</v>
+        <v>13.97919724682958</v>
       </c>
       <c r="S24" t="n">
-        <v>2.969423752025024e-14</v>
+        <v>1.260634392014071e-13</v>
       </c>
       <c r="T24" t="n">
-        <v>37.59404297987852</v>
+        <v>37.5940429799755</v>
       </c>
       <c r="U24" t="n">
-        <v>2.664535259100376e-13</v>
+        <v>-2.540190280342358e-12</v>
       </c>
     </row>
     <row r="25">
@@ -3147,52 +3147,52 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0004821348199423592</v>
+        <v>0.0004821348199423453</v>
       </c>
       <c r="G25" t="n">
-        <v>6.02668524927949e-05</v>
+        <v>6.026685249279316e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>57.13297616316957</v>
+        <v>57.13297616316792</v>
       </c>
       <c r="I25" t="n">
-        <v>12053.37049855898</v>
+        <v>12053.37049855863</v>
       </c>
       <c r="J25" t="n">
-        <v>-57.13297616316959</v>
+        <v>-57.13297616316777</v>
       </c>
       <c r="K25" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>-6.394884621840902e-13</v>
       </c>
       <c r="L25" t="n">
-        <v>14.38129338006276</v>
+        <v>14.38129338007445</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.565309076274502e-14</v>
+        <v>-1.384983707580778e-13</v>
       </c>
       <c r="N25" t="n">
-        <v>-37.68983998962765</v>
+        <v>-37.68983998967445</v>
       </c>
       <c r="O25" t="n">
-        <v>2.842170943040401e-13</v>
+        <v>-2.614797267597169e-12</v>
       </c>
       <c r="P25" t="n">
-        <v>57.13297616316959</v>
+        <v>57.13297616316777</v>
       </c>
       <c r="Q25" t="n">
-        <v>-8.526512829121202e-14</v>
+        <v>6.394884621840902e-13</v>
       </c>
       <c r="R25" t="n">
-        <v>-14.38129338006276</v>
+        <v>-14.38129338007445</v>
       </c>
       <c r="S25" t="n">
-        <v>2.565309076274502e-14</v>
+        <v>1.384983707580778e-13</v>
       </c>
       <c r="T25" t="n">
-        <v>-77.36050705087436</v>
+        <v>-77.36050705092119</v>
       </c>
       <c r="U25" t="n">
-        <v>2.842170943040401e-13</v>
+        <v>-2.501110429875553e-12</v>
       </c>
     </row>
     <row r="26">
@@ -3214,52 +3214,52 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-9.398725575793243e-05</v>
+        <v>-9.398725575804345e-05</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.174840696974155e-05</v>
+        <v>-1.174840696975543e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>-11.13748980731499</v>
+        <v>-11.13748980732815</v>
       </c>
       <c r="I26" t="n">
-        <v>-2349.68139394831</v>
+        <v>-2349.681393951086</v>
       </c>
       <c r="J26" t="n">
         <v>11.13748980732635</v>
       </c>
       <c r="K26" t="n">
-        <v>1.435296326235402e-12</v>
+        <v>-4.632738637155853e-12</v>
       </c>
       <c r="L26" t="n">
-        <v>2.212058392780676</v>
+        <v>2.212058392761011</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.371608547908522e-14</v>
+        <v>-8.879008639439689e-14</v>
       </c>
       <c r="N26" t="n">
-        <v>-12.99592643808889</v>
+        <v>-12.99592643801022</v>
       </c>
       <c r="O26" t="n">
-        <v>5.74118530494161e-12</v>
+        <v>-1.853095454862341e-11</v>
       </c>
       <c r="P26" t="n">
         <v>-11.13748980732635</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.435296326235402e-12</v>
+        <v>4.632738637155853e-12</v>
       </c>
       <c r="R26" t="n">
-        <v>-2.212058392780676</v>
+        <v>-2.212058392761011</v>
       </c>
       <c r="S26" t="n">
-        <v>3.371608547908522e-14</v>
+        <v>8.879008639439689e-14</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.700540704156521</v>
+        <v>-4.700540704077868</v>
       </c>
       <c r="U26" t="n">
-        <v>5.74118530494161e-12</v>
+        <v>-1.853095454862341e-11</v>
       </c>
     </row>
     <row r="27">
@@ -3296,37 +3296,37 @@
         <v>8.554683408379788</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.4210854715202e-12</v>
+        <v>4.661160346586257e-12</v>
       </c>
       <c r="L27" t="n">
-        <v>91.28529229083352</v>
+        <v>91.28529229081425</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.122434172857623e-14</v>
+        <v>-1.00450897599913e-13</v>
       </c>
       <c r="N27" t="n">
-        <v>-275.0817579093762</v>
+        <v>-275.0817579092991</v>
       </c>
       <c r="O27" t="n">
-        <v>-5.74118530494161e-12</v>
+        <v>1.858779796748422e-11</v>
       </c>
       <c r="P27" t="n">
         <v>-8.554683408379788</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.4210854715202e-12</v>
+        <v>-4.661160346586257e-12</v>
       </c>
       <c r="R27" t="n">
-        <v>-91.28529229083352</v>
+        <v>-91.28529229081425</v>
       </c>
       <c r="S27" t="n">
-        <v>2.122434172857623e-14</v>
+        <v>1.00450897599913e-13</v>
       </c>
       <c r="T27" t="n">
-        <v>-455.2005804172919</v>
+        <v>-455.2005804172148</v>
       </c>
       <c r="U27" t="n">
-        <v>-5.684341886080801e-12</v>
+        <v>1.864464138634503e-11</v>
       </c>
     </row>
     <row r="28">
@@ -3348,52 +3348,52 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>-9.398725575804345e-05</v>
+        <v>-9.398725575793243e-05</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.174840696975543e-05</v>
+        <v>-1.174840696974155e-05</v>
       </c>
       <c r="H28" t="n">
-        <v>-11.13748980732815</v>
+        <v>-11.13748980731499</v>
       </c>
       <c r="I28" t="n">
-        <v>-2349.681393951086</v>
+        <v>-2349.68139394831</v>
       </c>
       <c r="J28" t="n">
         <v>11.13748980732635</v>
       </c>
       <c r="K28" t="n">
-        <v>1.4210854715202e-12</v>
+        <v>-4.646949491871055e-12</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.212058392789006</v>
+        <v>-2.212058392800185</v>
       </c>
       <c r="M28" t="n">
-        <v>-3.352873534367973e-14</v>
+        <v>-8.876233081878127e-14</v>
       </c>
       <c r="N28" t="n">
-        <v>4.700540704189827</v>
+        <v>4.70054070423453</v>
       </c>
       <c r="O28" t="n">
-        <v>5.712763595511205e-12</v>
+        <v>-1.853095454862341e-11</v>
       </c>
       <c r="P28" t="n">
         <v>-11.13748980732635</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1.4210854715202e-12</v>
+        <v>4.646949491871055e-12</v>
       </c>
       <c r="R28" t="n">
-        <v>2.212058392789006</v>
+        <v>2.212058392800185</v>
       </c>
       <c r="S28" t="n">
-        <v>3.352873534367973e-14</v>
+        <v>8.876233081878127e-14</v>
       </c>
       <c r="T28" t="n">
-        <v>12.99592643812222</v>
+        <v>12.99592643816695</v>
       </c>
       <c r="U28" t="n">
-        <v>5.627498467219993e-12</v>
+        <v>-1.861621967691462e-11</v>
       </c>
     </row>
     <row r="29">
@@ -3415,52 +3415,52 @@
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>-7.219142116776656e-05</v>
+        <v>-7.219142116787758e-05</v>
       </c>
       <c r="G29" t="n">
-        <v>-9.02392764597082e-06</v>
+        <v>-9.023927645984697e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>-8.554683408380336</v>
+        <v>-8.554683408393494</v>
       </c>
       <c r="I29" t="n">
-        <v>-1804.785529194164</v>
+        <v>-1804.785529196939</v>
       </c>
       <c r="J29" t="n">
-        <v>8.554683408379788</v>
+        <v>8.554683408394339</v>
       </c>
       <c r="K29" t="n">
-        <v>1.449507180950604e-12</v>
+        <v>-4.632738637155853e-12</v>
       </c>
       <c r="L29" t="n">
-        <v>91.2852922908466</v>
+        <v>91.28529229084891</v>
       </c>
       <c r="M29" t="n">
-        <v>-2.127811815633152e-14</v>
+        <v>-1.005775324136593e-13</v>
       </c>
       <c r="N29" t="n">
-        <v>-455.2005804173441</v>
+        <v>-455.2005804173534</v>
       </c>
       <c r="O29" t="n">
-        <v>5.854872142663226e-12</v>
+        <v>-1.84741111297626e-11</v>
       </c>
       <c r="P29" t="n">
-        <v>-8.554683408379788</v>
+        <v>-8.554683408394339</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1.449507180950604e-12</v>
+        <v>4.632738637155853e-12</v>
       </c>
       <c r="R29" t="n">
-        <v>-91.2852922908466</v>
+        <v>-91.28529229084891</v>
       </c>
       <c r="S29" t="n">
-        <v>2.127811815633152e-14</v>
+        <v>1.005775324136593e-13</v>
       </c>
       <c r="T29" t="n">
-        <v>-275.0817579094285</v>
+        <v>-275.0817579094377</v>
       </c>
       <c r="U29" t="n">
-        <v>5.798028723802418e-12</v>
+        <v>-1.858779796748422e-11</v>
       </c>
     </row>
     <row r="30">
@@ -3494,40 +3494,40 @@
         <v>369.9427691461476</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.753528725763317</v>
+        <v>-1.753528725748765</v>
       </c>
       <c r="K30" t="n">
-        <v>4.604316927725449e-12</v>
+        <v>-4.732214620162267e-12</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4020961332541386</v>
+        <v>0.4020961332469026</v>
       </c>
       <c r="M30" t="n">
-        <v>-2.389755060505649e-14</v>
+        <v>-3.67622599029005e-14</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.1111099734689656</v>
+        <v>-0.1111099734400467</v>
       </c>
       <c r="O30" t="n">
-        <v>1.84172677109018e-11</v>
+        <v>-1.887201506178826e-11</v>
       </c>
       <c r="P30" t="n">
-        <v>1.753528725763317</v>
+        <v>1.753528725748765</v>
       </c>
       <c r="Q30" t="n">
-        <v>-4.604316927725449e-12</v>
+        <v>4.732214620162267e-12</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.4020961332541386</v>
+        <v>-0.4020961332469026</v>
       </c>
       <c r="S30" t="n">
-        <v>2.389755060505649e-14</v>
+        <v>3.67622599029005e-14</v>
       </c>
       <c r="T30" t="n">
-        <v>-3.105659092564143</v>
+        <v>-3.105659092535173</v>
       </c>
       <c r="U30" t="n">
-        <v>1.84172677109018e-11</v>
+        <v>-1.904254531837068e-11</v>
       </c>
     </row>
     <row r="31">
@@ -3549,52 +3549,52 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0003223038101611841</v>
+        <v>-0.0003223038101612952</v>
       </c>
       <c r="G31" t="n">
-        <v>-4.028797627014802e-05</v>
+        <v>-4.02879762701619e-05</v>
       </c>
       <c r="H31" t="n">
-        <v>-38.19300150410032</v>
+        <v>-38.19300150411348</v>
       </c>
       <c r="I31" t="n">
-        <v>-8057.595254029604</v>
+        <v>-8057.595254032378</v>
       </c>
       <c r="J31" t="n">
-        <v>38.19300150409981</v>
+        <v>38.19300150411436</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.632738637155853e-12</v>
+        <v>4.703792910731863e-12</v>
       </c>
       <c r="L31" t="n">
-        <v>16.59335177284954</v>
+        <v>16.59335177284094</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.160616741602283e-14</v>
+        <v>-3.452880342758036e-14</v>
       </c>
       <c r="N31" t="n">
-        <v>-99.09704529722077</v>
+        <v>-99.09704529718634</v>
       </c>
       <c r="O31" t="n">
-        <v>-1.84741111297626e-11</v>
+        <v>1.875832822406664e-11</v>
       </c>
       <c r="P31" t="n">
-        <v>-38.19300150409981</v>
+        <v>-38.19300150411436</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.632738637155853e-12</v>
+        <v>-4.703792910731863e-12</v>
       </c>
       <c r="R31" t="n">
-        <v>-16.59335177284954</v>
+        <v>-16.59335177284094</v>
       </c>
       <c r="S31" t="n">
-        <v>1.160616741602283e-14</v>
+        <v>3.452880342758036e-14</v>
       </c>
       <c r="T31" t="n">
-        <v>-33.64976888557555</v>
+        <v>-33.64976888554113</v>
       </c>
       <c r="U31" t="n">
-        <v>-1.84741111297626e-11</v>
+        <v>1.887201506178826e-11</v>
       </c>
     </row>
     <row r="32">
@@ -3631,37 +3631,37 @@
         <v>-1.753528725763317</v>
       </c>
       <c r="K32" t="n">
-        <v>4.604316927725449e-12</v>
+        <v>-4.718003765447065e-12</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.4020961332587234</v>
+        <v>-0.4020961332603305</v>
       </c>
       <c r="M32" t="n">
-        <v>-2.410918686912566e-14</v>
+        <v>-3.682470994803566e-14</v>
       </c>
       <c r="N32" t="n">
-        <v>3.105659092582468</v>
+        <v>3.105659092588902</v>
       </c>
       <c r="O32" t="n">
-        <v>1.84741111297626e-11</v>
+        <v>-1.881517164292745e-11</v>
       </c>
       <c r="P32" t="n">
         <v>1.753528725763317</v>
       </c>
       <c r="Q32" t="n">
-        <v>-4.604316927725449e-12</v>
+        <v>4.718003765447065e-12</v>
       </c>
       <c r="R32" t="n">
-        <v>0.4020961332587234</v>
+        <v>0.4020961332603305</v>
       </c>
       <c r="S32" t="n">
-        <v>2.410918686912566e-14</v>
+        <v>3.682470994803566e-14</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1111099734873178</v>
+        <v>0.1111099734937417</v>
       </c>
       <c r="U32" t="n">
-        <v>1.84741111297626e-11</v>
+        <v>-1.887201506178826e-11</v>
       </c>
     </row>
     <row r="33">
@@ -3683,52 +3683,52 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.0003223038101612952</v>
+        <v>-0.0003223038101615172</v>
       </c>
       <c r="G33" t="n">
-        <v>-4.02879762701619e-05</v>
+        <v>-4.028797627018965e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>-38.19300150411348</v>
+        <v>-38.19300150413979</v>
       </c>
       <c r="I33" t="n">
-        <v>-8057.595254032378</v>
+        <v>-8057.595254037929</v>
       </c>
       <c r="J33" t="n">
-        <v>38.19300150411436</v>
+        <v>38.19300150414347</v>
       </c>
       <c r="K33" t="n">
-        <v>4.618527782440651e-12</v>
+        <v>-4.746425474877469e-12</v>
       </c>
       <c r="L33" t="n">
-        <v>16.59335177285886</v>
+        <v>16.59335177285531</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.165777543943314e-14</v>
+        <v>-3.446266709505874e-14</v>
       </c>
       <c r="N33" t="n">
-        <v>-33.64976888561286</v>
+        <v>-33.64976888559865</v>
       </c>
       <c r="O33" t="n">
-        <v>1.84741111297626e-11</v>
+        <v>-1.892885848064907e-11</v>
       </c>
       <c r="P33" t="n">
-        <v>-38.19300150411436</v>
+        <v>-38.19300150414347</v>
       </c>
       <c r="Q33" t="n">
-        <v>-4.618527782440651e-12</v>
+        <v>4.746425474877469e-12</v>
       </c>
       <c r="R33" t="n">
-        <v>-16.59335177285886</v>
+        <v>-16.59335177285531</v>
       </c>
       <c r="S33" t="n">
-        <v>1.165777543943314e-14</v>
+        <v>3.446266709505874e-14</v>
       </c>
       <c r="T33" t="n">
-        <v>-99.09704529725796</v>
+        <v>-99.09704529724382</v>
       </c>
       <c r="U33" t="n">
-        <v>1.84741111297626e-11</v>
+        <v>-1.904254531837068e-11</v>
       </c>
     </row>
   </sheetData>
@@ -3991,16 +3991,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.001454028388444138</v>
+        <v>-0.001454028388443931</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0002423380647406897</v>
+        <v>-0.0002423380647406551</v>
       </c>
       <c r="H2" t="n">
-        <v>-229.7364853741738</v>
+        <v>-229.736485374141</v>
       </c>
       <c r="I2" t="n">
-        <v>-48467.61294813793</v>
+        <v>-48467.61294813102</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -4021,22 +4021,22 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.008506800363761516</v>
+        <v>-0.008506800363843648</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.3200869679146637</v>
+        <v>-0.3200869679146143</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.001454028388444138</v>
+        <v>-0.001454028388443931</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1813005936458008</v>
+        <v>0.1813005936457907</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008825836814662386</v>
+        <v>0.0008825836814519907</v>
       </c>
       <c r="U2" t="n">
-        <v>-9.285603354946163e-15</v>
+        <v>-3.950848033461115e-14</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -4057,58 +4057,58 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.001454028388444138</v>
+        <v>-0.001454028388443931</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.3200869679146637</v>
+        <v>-0.3200869679146143</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.008506800363761516</v>
+        <v>0.008506800363843648</v>
       </c>
       <c r="AE2" t="n">
-        <v>-9.285603354946163e-15</v>
+        <v>-3.950848033461115e-14</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0008825836814662386</v>
+        <v>0.0008825836814519907</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.1813005936458008</v>
+        <v>-0.1813005936457907</v>
       </c>
       <c r="AH2" t="n">
-        <v>229.7364853741738</v>
+        <v>229.7364853741411</v>
       </c>
       <c r="AI2" t="n">
-        <v>-55.20765387894221</v>
+        <v>-55.20765387894689</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-2.751456014012857</v>
+        <v>-2.751456014022573</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.642825570253907e-14</v>
+        <v>1.124472132600471e-13</v>
       </c>
       <c r="AL2" t="n">
-        <v>7.601256117753555</v>
+        <v>7.601256117793246</v>
       </c>
       <c r="AM2" t="n">
-        <v>-31.46052233893405</v>
+        <v>-31.46052233895557</v>
       </c>
       <c r="AN2" t="n">
-        <v>-229.7364853741738</v>
+        <v>-229.7364853741411</v>
       </c>
       <c r="AO2" t="n">
-        <v>55.20765387894221</v>
+        <v>55.20765387894689</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.751456014012857</v>
+        <v>2.751456014022573</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-2.642825570253907e-14</v>
+        <v>-1.124472132600471e-13</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.907479966323589</v>
+        <v>8.907479966342192</v>
       </c>
       <c r="AS2" t="n">
-        <v>-299.7854009347192</v>
+        <v>-299.7854009347257</v>
       </c>
     </row>
     <row r="3">
@@ -4130,16 +4130,16 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.000121566495562611</v>
+        <v>-0.0001215664955624709</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.02610825937685e-05</v>
+        <v>-2.026108259374515e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>-19.20750629889253</v>
+        <v>-19.2075062988704</v>
       </c>
       <c r="I3" t="n">
-        <v>-4052.216518753698</v>
+        <v>-4052.216518749029</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -4160,22 +4160,22 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.008506800363690507</v>
+        <v>-0.008506800363530128</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3199836416745839</v>
+        <v>-0.3199836416745343</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.000121566495562611</v>
+        <v>-0.0001215664955624709</v>
       </c>
       <c r="S3" t="n">
-        <v>0.03205627621730149</v>
+        <v>0.0320562762172913</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008825836814785056</v>
+        <v>0.0008825836815066833</v>
       </c>
       <c r="U3" t="n">
-        <v>-9.295205578831507e-15</v>
+        <v>-3.953174045802473e-14</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -4196,58 +4196,58 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.000121566495562611</v>
+        <v>-0.0001215664955624709</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.3199836416745839</v>
+        <v>-0.3199836416745343</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.008506800363690507</v>
+        <v>0.008506800363530128</v>
       </c>
       <c r="AE3" t="n">
-        <v>-9.295205578831507e-15</v>
+        <v>-3.953174045802473e-14</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0008825836814785056</v>
+        <v>0.0008825836815066833</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.03205627621730149</v>
+        <v>-0.0320562762172913</v>
       </c>
       <c r="AH3" t="n">
-        <v>19.20750629889254</v>
+        <v>19.2075062988704</v>
       </c>
       <c r="AI3" t="n">
-        <v>55.2076538789276</v>
+        <v>55.2076538789229</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-2.751456014004419</v>
+        <v>-2.75145601398571</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.645558510898198e-14</v>
+        <v>1.125134151497627e-13</v>
       </c>
       <c r="AL3" t="n">
-        <v>7.601256117719164</v>
+        <v>7.601256117642186</v>
       </c>
       <c r="AM3" t="n">
-        <v>189.3446060375859</v>
+        <v>189.3446060375642</v>
       </c>
       <c r="AN3" t="n">
-        <v>-19.20750629889254</v>
+        <v>-19.2075062988704</v>
       </c>
       <c r="AO3" t="n">
-        <v>-55.2076538789276</v>
+        <v>-55.2076538789229</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.751456014004419</v>
+        <v>2.75145601398571</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-2.645558510898198e-14</v>
+        <v>-1.125134151497627e-13</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.907479966307353</v>
+        <v>8.907479966272078</v>
       </c>
       <c r="AS3" t="n">
-        <v>141.9013172359797</v>
+        <v>141.9013172359731</v>
       </c>
     </row>
     <row r="4">
@@ -4269,16 +4269,16 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001454028388444068</v>
+        <v>0.001454028388443984</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002423380647406781</v>
+        <v>0.000242338064740664</v>
       </c>
       <c r="H4" t="n">
-        <v>229.7364853741628</v>
+        <v>229.7364853741495</v>
       </c>
       <c r="I4" t="n">
-        <v>48467.61294813561</v>
+        <v>48467.6129481328</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.008617658990396852</v>
+        <v>-0.008617658990236473</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.3199836416746615</v>
+        <v>-0.319983641674853</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001454028388444068</v>
+        <v>0.001454028388443984</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03205627621731389</v>
+        <v>0.03205627621734609</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.006590736799541642</v>
+        <v>-0.006590736799513456</v>
       </c>
       <c r="U4" t="n">
-        <v>-9.296542609148836e-15</v>
+        <v>-3.95222817975377e-14</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -4335,58 +4335,58 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001454028388444068</v>
+        <v>0.001454028388443984</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.3199836416746615</v>
+        <v>-0.319983641674853</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.008617658990396852</v>
+        <v>0.008617658990236473</v>
       </c>
       <c r="AE4" t="n">
-        <v>-9.296542609148836e-15</v>
+        <v>-3.95222817975377e-14</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.006590736799541642</v>
+        <v>-0.006590736799513456</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.03205627621731389</v>
+        <v>-0.03205627621734609</v>
       </c>
       <c r="AH4" t="n">
-        <v>-229.7364853741628</v>
+        <v>-229.7364853741495</v>
       </c>
       <c r="AI4" t="n">
-        <v>55.20765387893758</v>
+        <v>55.20765387896097</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.751456014029591</v>
+        <v>2.751456014048294</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.645939050296207e-14</v>
+        <v>1.124864943468381e-13</v>
       </c>
       <c r="AL4" t="n">
-        <v>-3.377222810427959</v>
+        <v>-3.377222810504925</v>
       </c>
       <c r="AM4" t="n">
-        <v>189.344606037625</v>
+        <v>189.344606037719</v>
       </c>
       <c r="AN4" t="n">
-        <v>229.7364853741628</v>
+        <v>229.7364853741495</v>
       </c>
       <c r="AO4" t="n">
-        <v>-55.20765387893758</v>
+        <v>-55.20765387896097</v>
       </c>
       <c r="AP4" t="n">
-        <v>-2.751456014029591</v>
+        <v>-2.751456014048294</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-2.645939050296207e-14</v>
+        <v>-1.124864943468381e-13</v>
       </c>
       <c r="AR4" t="n">
-        <v>-13.13151327374959</v>
+        <v>-13.13151327378484</v>
       </c>
       <c r="AS4" t="n">
-        <v>141.9013172360004</v>
+        <v>141.9013172360468</v>
       </c>
     </row>
     <row r="5">
@@ -4408,16 +4408,16 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001215664955626805</v>
+        <v>0.0001215664955624186</v>
       </c>
       <c r="G5" t="n">
-        <v>2.026108259378009e-05</v>
+        <v>2.026108259373643e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>19.20750629890352</v>
+        <v>19.20750629886214</v>
       </c>
       <c r="I5" t="n">
-        <v>4052.216518756018</v>
+        <v>4052.216518747287</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -4438,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.008617658990467861</v>
+        <v>-0.008617658990549991</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3200869679147415</v>
+        <v>-0.3200869679149329</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001215664955626805</v>
+        <v>0.0001215664955624186</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1813005936458132</v>
+        <v>0.1813005936458454</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.006590736799553908</v>
+        <v>-0.006590736799568158</v>
       </c>
       <c r="U5" t="n">
-        <v>-9.303613152494448e-15</v>
+        <v>-3.952324315212423e-14</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -4474,58 +4474,58 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001215664955626805</v>
+        <v>0.0001215664955624186</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.3200869679147415</v>
+        <v>-0.3200869679149329</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.008617658990467861</v>
+        <v>0.008617658990549991</v>
       </c>
       <c r="AE5" t="n">
-        <v>-9.303613152494448e-15</v>
+        <v>-3.952324315212423e-14</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.006590736799553908</v>
+        <v>-0.006590736799568158</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.1813005936458132</v>
+        <v>-0.1813005936458454</v>
       </c>
       <c r="AH5" t="n">
-        <v>-19.20750629890353</v>
+        <v>-19.20750629886214</v>
       </c>
       <c r="AI5" t="n">
-        <v>-55.20765387893223</v>
+        <v>-55.20765387890883</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.751456014021153</v>
+        <v>2.751456014011439</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.647951435709958e-14</v>
+        <v>1.12489230509892e-13</v>
       </c>
       <c r="AL5" t="n">
-        <v>-3.377222810393566</v>
+        <v>-3.377222810353881</v>
       </c>
       <c r="AM5" t="n">
-        <v>-31.4605223388949</v>
+        <v>-31.4605223388009</v>
       </c>
       <c r="AN5" t="n">
-        <v>19.20750629890353</v>
+        <v>19.20750629886214</v>
       </c>
       <c r="AO5" t="n">
-        <v>55.20765387893223</v>
+        <v>55.20765387890883</v>
       </c>
       <c r="AP5" t="n">
-        <v>-2.751456014021153</v>
+        <v>-2.751456014011439</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-2.647951435709958e-14</v>
+        <v>-1.12489230509892e-13</v>
       </c>
       <c r="AR5" t="n">
-        <v>-13.13151327373335</v>
+        <v>-13.13151327371476</v>
       </c>
       <c r="AS5" t="n">
-        <v>-299.7854009346985</v>
+        <v>-299.7854009346521</v>
       </c>
     </row>
     <row r="6">
@@ -4547,124 +4547,124 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0008788182861810029</v>
+        <v>-0.0008788182861807735</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0001464697143635005</v>
+        <v>-0.0001464697143634622</v>
       </c>
       <c r="H6" t="n">
-        <v>-138.8532892165985</v>
+        <v>-138.8532892165622</v>
       </c>
       <c r="I6" t="n">
-        <v>-29293.9428727001</v>
+        <v>-29293.94287269245</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.008506800363761516</v>
+        <v>-0.008506800363843648</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3200869679146637</v>
+        <v>-0.3200869679146143</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.001454028388444138</v>
+        <v>-0.001454028388443931</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1813005936458008</v>
+        <v>0.1813005936457907</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0008825836814662386</v>
+        <v>0.0008825836814519907</v>
       </c>
       <c r="O6" t="n">
-        <v>-9.285603354946163e-15</v>
+        <v>-3.950848033461115e-14</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.07036120329889795</v>
+        <v>-0.07036120329910434</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.6912454096231312</v>
+        <v>-0.6912454096229569</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.002332846674625141</v>
+        <v>-0.002332846674624704</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0004776631797337471</v>
+        <v>0.0004776631797100466</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.03553489535897476</v>
+        <v>-0.0355348953589887</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.254982535921031e-14</v>
+        <v>-1.010899116652667e-13</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.001454028388444138</v>
+        <v>-0.001454028388443931</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3200869679146637</v>
+        <v>-0.3200869679146143</v>
       </c>
       <c r="X6" t="n">
-        <v>0.008506800363761516</v>
+        <v>0.008506800363843648</v>
       </c>
       <c r="Y6" t="n">
-        <v>-9.285603354946163e-15</v>
+        <v>-3.950848033461115e-14</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0008825836814662386</v>
+        <v>0.0008825836814519907</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.1813005936458008</v>
+        <v>-0.1813005936457907</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.002332846674625141</v>
+        <v>-0.002332846674624704</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.6912454096231312</v>
+        <v>-0.6912454096229569</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.07036120329889795</v>
+        <v>0.07036120329910434</v>
       </c>
       <c r="AE6" t="n">
-        <v>-2.254982535921031e-14</v>
+        <v>-1.010899116652667e-13</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.03553489535897476</v>
+        <v>-0.0355348953589887</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0004776631797337471</v>
+        <v>-0.0004776631797100466</v>
       </c>
       <c r="AH6" t="n">
-        <v>138.8532892165985</v>
+        <v>138.8532892165622</v>
       </c>
       <c r="AI6" t="n">
-        <v>-42.9634944294736</v>
+        <v>-42.9634944294793</v>
       </c>
       <c r="AJ6" t="n">
-        <v>10.38529125068932</v>
+        <v>10.38529125067953</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.775201647367488e-14</v>
+        <v>1.752702276334041e-13</v>
       </c>
       <c r="AL6" t="n">
-        <v>-4.206939262141617</v>
+        <v>-4.206939262112485</v>
       </c>
       <c r="AM6" t="n">
-        <v>-262.6994518333104</v>
+        <v>-262.6994518333376</v>
       </c>
       <c r="AN6" t="n">
-        <v>-138.8532892165985</v>
+        <v>-138.8532892165622</v>
       </c>
       <c r="AO6" t="n">
-        <v>42.9634944294736</v>
+        <v>42.9634944294793</v>
       </c>
       <c r="AP6" t="n">
-        <v>-10.38529125068932</v>
+        <v>-10.38529125067953</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-3.775201647367488e-14</v>
+        <v>-1.752702276334041e-13</v>
       </c>
       <c r="AR6" t="n">
-        <v>-58.10480824199429</v>
+        <v>-58.10480824196471</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.918485256468898</v>
+        <v>4.918485256461651</v>
       </c>
     </row>
     <row r="7">
@@ -4686,124 +4686,124 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.000668775858676608</v>
+        <v>-0.0006687758586765627</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.000111462643112768</v>
+        <v>-0.0001114626431127605</v>
       </c>
       <c r="H7" t="n">
-        <v>-105.6665856709041</v>
+        <v>-105.6665856708969</v>
       </c>
       <c r="I7" t="n">
-        <v>-22292.5286225536</v>
+        <v>-22292.52862255209</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.008506800363690507</v>
+        <v>-0.008506800363530128</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3199836416745839</v>
+        <v>-0.3199836416745343</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.000121566495562611</v>
+        <v>-0.0001215664955624709</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03205627621730149</v>
+        <v>0.0320562762172913</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0008825836814785056</v>
+        <v>0.0008825836815066833</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.295205578831507e-15</v>
+        <v>-3.953174045802473e-14</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.07036120329871685</v>
+        <v>-0.07036120329830216</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.6908036589437132</v>
+        <v>-0.6908036589435386</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.000790342354239219</v>
+        <v>-0.0007903423542390336</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0334916199497208</v>
+        <v>0.03349161994969708</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.03553489535896087</v>
+        <v>-0.03553489535892964</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.253216035953992e-14</v>
+        <v>-1.010500600582059e-13</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.000121566495562611</v>
+        <v>-0.0001215664955624709</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3199836416745839</v>
+        <v>-0.3199836416745343</v>
       </c>
       <c r="X7" t="n">
-        <v>0.008506800363690507</v>
+        <v>0.008506800363530128</v>
       </c>
       <c r="Y7" t="n">
-        <v>-9.295205578831507e-15</v>
+        <v>-3.953174045802473e-14</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008825836814785056</v>
+        <v>0.0008825836815066833</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.03205627621730149</v>
+        <v>-0.0320562762172913</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.000790342354239219</v>
+        <v>-0.0007903423542390336</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.6908036589437132</v>
+        <v>-0.6908036589435386</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.07036120329871685</v>
+        <v>0.07036120329830216</v>
       </c>
       <c r="AE7" t="n">
-        <v>-2.253216035953992e-14</v>
+        <v>-1.010500600582059e-13</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.03553489535896087</v>
+        <v>-0.03553489535892964</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0334916199497208</v>
+        <v>-0.03349161994969708</v>
       </c>
       <c r="AH7" t="n">
-        <v>105.6665856709041</v>
+        <v>105.6665856708969</v>
       </c>
       <c r="AI7" t="n">
-        <v>42.96349442945541</v>
+        <v>42.96349442944967</v>
       </c>
       <c r="AJ7" t="n">
-        <v>10.38529125069712</v>
+        <v>10.38529125071589</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.767440976047779e-14</v>
+        <v>1.750906019389773e-13</v>
       </c>
       <c r="AL7" t="n">
-        <v>-4.206939262166223</v>
+        <v>-4.206939262224786</v>
       </c>
       <c r="AM7" t="n">
-        <v>129.9526376503565</v>
+        <v>129.9526376503293</v>
       </c>
       <c r="AN7" t="n">
-        <v>-105.6665856709041</v>
+        <v>-105.6665856708969</v>
       </c>
       <c r="AO7" t="n">
-        <v>-42.96349442945541</v>
+        <v>-42.96349442944967</v>
       </c>
       <c r="AP7" t="n">
-        <v>-10.38529125069712</v>
+        <v>-10.38529125071589</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-3.767440976047779e-14</v>
+        <v>-1.750906019389773e-13</v>
       </c>
       <c r="AR7" t="n">
-        <v>-58.10480824201649</v>
+        <v>-58.10480824207055</v>
       </c>
       <c r="AS7" t="n">
-        <v>127.8283289263759</v>
+        <v>127.8283289263687</v>
       </c>
     </row>
     <row r="8">
@@ -4825,124 +4825,124 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>0.000878818286180932</v>
+        <v>0.0008788182861808262</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001464697143634887</v>
+        <v>0.000146469714363471</v>
       </c>
       <c r="H8" t="n">
-        <v>138.8532892165873</v>
+        <v>138.8532892165705</v>
       </c>
       <c r="I8" t="n">
-        <v>29293.94287269773</v>
+        <v>29293.94287269421</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.008617658990396852</v>
+        <v>-0.008617658990236473</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3199836416746615</v>
+        <v>-0.319983641674853</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001454028388444068</v>
+        <v>0.001454028388443984</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03205627621731389</v>
+        <v>0.03205627621734609</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.006590736799541642</v>
+        <v>-0.006590736799513456</v>
       </c>
       <c r="O8" t="n">
-        <v>-9.296542609148836e-15</v>
+        <v>-3.95222817975377e-14</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.06987906847877449</v>
+        <v>-0.06987906847835977</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.6908036589438927</v>
+        <v>-0.6908036589443535</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002332846674625</v>
+        <v>0.00233284667462481</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03349161994973283</v>
+        <v>0.03349161994976197</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0002044443358560187</v>
+        <v>0.0002044443358872198</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.255910051777855e-14</v>
+        <v>-1.010917419802469e-13</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001454028388444068</v>
+        <v>0.001454028388443984</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3199836416746615</v>
+        <v>-0.319983641674853</v>
       </c>
       <c r="X8" t="n">
-        <v>0.008617658990396852</v>
+        <v>0.008617658990236473</v>
       </c>
       <c r="Y8" t="n">
-        <v>-9.296542609148836e-15</v>
+        <v>-3.95222817975377e-14</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.006590736799541642</v>
+        <v>-0.006590736799513456</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.03205627621731389</v>
+        <v>-0.03205627621734609</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.002332846674625</v>
+        <v>0.00233284667462481</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.6908036589438927</v>
+        <v>-0.6908036589443535</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.06987906847877449</v>
+        <v>0.06987906847835977</v>
       </c>
       <c r="AE8" t="n">
-        <v>-2.255910051777855e-14</v>
+        <v>-1.010917419802469e-13</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0002044443358560187</v>
+        <v>0.0002044443358872198</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.03349161994973283</v>
+        <v>-0.03349161994976197</v>
       </c>
       <c r="AH8" t="n">
-        <v>-138.8532892165873</v>
+        <v>-138.8532892165705</v>
       </c>
       <c r="AI8" t="n">
-        <v>42.96349442946246</v>
+        <v>42.96349442948349</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-10.38529125067246</v>
+        <v>-10.38529125065367</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.774728020148455e-14</v>
+        <v>1.752361559046339e-13</v>
       </c>
       <c r="AL8" t="n">
-        <v>26.12743971182311</v>
+        <v>26.12743971176449</v>
       </c>
       <c r="AM8" t="n">
-        <v>129.9526376503774</v>
+        <v>129.9526376504382</v>
       </c>
       <c r="AN8" t="n">
-        <v>138.8532892165873</v>
+        <v>138.8532892165705</v>
       </c>
       <c r="AO8" t="n">
-        <v>-42.96349442946246</v>
+        <v>-42.96349442948349</v>
       </c>
       <c r="AP8" t="n">
-        <v>10.38529125067246</v>
+        <v>10.38529125065367</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-3.774728020148455e-14</v>
+        <v>-1.752361559046339e-13</v>
       </c>
       <c r="AR8" t="n">
-        <v>36.18430779221164</v>
+        <v>36.18430779215749</v>
       </c>
       <c r="AS8" t="n">
-        <v>127.8283289263974</v>
+        <v>127.8283289264627</v>
       </c>
     </row>
     <row r="9">
@@ -4964,124 +4964,124 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0006687758586766784</v>
+        <v>0.0006687758586765106</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001114626431127797</v>
+        <v>0.0001114626431127518</v>
       </c>
       <c r="H9" t="n">
-        <v>105.6665856709152</v>
+        <v>105.6665856708887</v>
       </c>
       <c r="I9" t="n">
-        <v>22292.52862255594</v>
+        <v>22292.52862255035</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.008617658990467861</v>
+        <v>-0.008617658990549991</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3200869679147415</v>
+        <v>-0.3200869679149329</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001215664955626805</v>
+        <v>0.0001215664955624186</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1813005936458132</v>
+        <v>0.1813005936458454</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.006590736799553908</v>
+        <v>-0.006590736799568158</v>
       </c>
       <c r="O9" t="n">
-        <v>-9.303613152494448e-15</v>
+        <v>-3.952324315212423e-14</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.06987906847895559</v>
+        <v>-0.06987906847916199</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.6912454096233109</v>
+        <v>-0.6912454096237716</v>
       </c>
       <c r="R9" t="n">
-        <v>0.000790342354239359</v>
+        <v>0.0007903423542389292</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0004776631797457648</v>
+        <v>0.0004776631797749287</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0002044443358421079</v>
+        <v>0.0002044443358281631</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.255697836653975e-14</v>
+        <v>-1.010136040492752e-13</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0001215664955626805</v>
+        <v>0.0001215664955624186</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3200869679147415</v>
+        <v>-0.3200869679149329</v>
       </c>
       <c r="X9" t="n">
-        <v>0.008617658990467861</v>
+        <v>0.008617658990549991</v>
       </c>
       <c r="Y9" t="n">
-        <v>-9.303613152494448e-15</v>
+        <v>-3.952324315212423e-14</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.006590736799553908</v>
+        <v>-0.006590736799568158</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.1813005936458132</v>
+        <v>-0.1813005936458454</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.000790342354239359</v>
+        <v>0.0007903423542389292</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.6912454096233109</v>
+        <v>-0.6912454096237716</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.06987906847895559</v>
+        <v>0.06987906847916199</v>
       </c>
       <c r="AE9" t="n">
-        <v>-2.255697836653975e-14</v>
+        <v>-1.010136040492752e-13</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0002044443358421079</v>
+        <v>0.0002044443358281631</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.0004776631797457648</v>
+        <v>-0.0004776631797749287</v>
       </c>
       <c r="AH9" t="n">
-        <v>-105.6665856709152</v>
+        <v>-105.6665856708887</v>
       </c>
       <c r="AI9" t="n">
-        <v>-42.96349442946655</v>
+        <v>-42.96349442944549</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-10.38529125068024</v>
+        <v>-10.38529125069003</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.772111637843662e-14</v>
+        <v>1.750110271688143e-13</v>
       </c>
       <c r="AL9" t="n">
-        <v>26.12743971184766</v>
+        <v>26.12743971187681</v>
       </c>
       <c r="AM9" t="n">
-        <v>-262.6994518332895</v>
+        <v>-262.6994518332286</v>
       </c>
       <c r="AN9" t="n">
-        <v>105.6665856709152</v>
+        <v>105.6665856708887</v>
       </c>
       <c r="AO9" t="n">
-        <v>42.96349442946655</v>
+        <v>42.96349442944549</v>
       </c>
       <c r="AP9" t="n">
-        <v>10.38529125068024</v>
+        <v>10.38529125069003</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-3.772111637843662e-14</v>
+        <v>-1.750110271688143e-13</v>
       </c>
       <c r="AR9" t="n">
-        <v>36.18430779223377</v>
+        <v>36.18430779226336</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.918485256490328</v>
+        <v>4.918485256555641</v>
       </c>
     </row>
     <row r="10">
@@ -5103,124 +5103,124 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.000699321510061648</v>
+        <v>-0.0006993215100614693</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0001165535850102747</v>
+        <v>-0.0001165535850102449</v>
       </c>
       <c r="H10" t="n">
-        <v>-110.4927985897404</v>
+        <v>-110.4927985897122</v>
       </c>
       <c r="I10" t="n">
-        <v>-23310.71700205493</v>
+        <v>-23310.71700204898</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.07036120329889795</v>
+        <v>-0.07036120329910434</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6912454096231312</v>
+        <v>-0.6912454096229569</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.002332846674625141</v>
+        <v>-0.002332846674624704</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0004776631797337471</v>
+        <v>0.0004776631797100466</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.03553489535897476</v>
+        <v>-0.0355348953589887</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.254982535921031e-14</v>
+        <v>-1.010899116652667e-13</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4537190030253384</v>
+        <v>-0.4537190030256291</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.7504936950267934</v>
+        <v>-0.7504936950263797</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.003032168184686789</v>
+        <v>-0.003032168184686173</v>
       </c>
       <c r="S10" t="n">
-        <v>0.006590736799546265</v>
+        <v>0.006590736799522585</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0290784907041432</v>
+        <v>-0.02907849070414583</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.586128221406856e-14</v>
+        <v>-1.611412101213256e-13</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.002332846674625141</v>
+        <v>-0.002332846674624704</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6912454096231312</v>
+        <v>-0.6912454096229569</v>
       </c>
       <c r="X10" t="n">
-        <v>0.07036120329889795</v>
+        <v>0.07036120329910434</v>
       </c>
       <c r="Y10" t="n">
-        <v>-2.254982535921031e-14</v>
+        <v>-1.010899116652667e-13</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.03553489535897476</v>
+        <v>-0.0355348953589887</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.0004776631797337471</v>
+        <v>-0.0004776631797100466</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.003032168184686789</v>
+        <v>-0.003032168184686173</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.7504936950267934</v>
+        <v>-0.7504936950263797</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.4537190030253384</v>
+        <v>0.4537190030256291</v>
       </c>
       <c r="AE10" t="n">
-        <v>-3.586128221406856e-14</v>
+        <v>-1.611412101213256e-13</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.0290784907041432</v>
+        <v>-0.02907849070414583</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.006590736799546265</v>
+        <v>-0.006590736799522585</v>
       </c>
       <c r="AH10" t="n">
-        <v>110.4927985897404</v>
+        <v>110.4927985897122</v>
       </c>
       <c r="AI10" t="n">
-        <v>9.38396108156951</v>
+        <v>9.383961081545465</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-46.74768491248135</v>
+        <v>-46.7476849124899</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.788645412536577e-14</v>
+        <v>1.709152340672448e-13</v>
       </c>
       <c r="AL10" t="n">
-        <v>135.4653152928687</v>
+        <v>135.4653152928859</v>
       </c>
       <c r="AM10" t="n">
-        <v>32.67555772336971</v>
+        <v>32.6755577232978</v>
       </c>
       <c r="AN10" t="n">
-        <v>-110.4927985897404</v>
+        <v>-110.4927985897122</v>
       </c>
       <c r="AO10" t="n">
-        <v>-9.38396108156951</v>
+        <v>-9.383961081545465</v>
       </c>
       <c r="AP10" t="n">
-        <v>46.74768491248135</v>
+        <v>46.7476849124899</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-3.788645412536577e-14</v>
+        <v>-1.709152340672448e-13</v>
       </c>
       <c r="AR10" t="n">
-        <v>145.0207941820194</v>
+        <v>145.0207941820534</v>
       </c>
       <c r="AS10" t="n">
-        <v>23.62820876604724</v>
+        <v>23.6282087659751</v>
       </c>
     </row>
     <row r="11">
@@ -5242,124 +5242,124 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.000666230946440811</v>
+        <v>-0.0006662309464408056</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0001110384910734685</v>
+        <v>-0.0001110384910734676</v>
       </c>
       <c r="H11" t="n">
-        <v>-105.2644895376481</v>
+        <v>-105.2644895376473</v>
       </c>
       <c r="I11" t="n">
-        <v>-22207.6982146937</v>
+        <v>-22207.69821469352</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.07036120329871685</v>
+        <v>-0.07036120329830216</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6908036589437132</v>
+        <v>-0.6908036589435386</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.000790342354239219</v>
+        <v>-0.0007903423542390336</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0334916199497208</v>
+        <v>0.03349161994969708</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.03553489535896087</v>
+        <v>-0.03553489535892964</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.253216035953992e-14</v>
+        <v>-1.010500600582059e-13</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537190030250376</v>
+        <v>-0.4537190030243844</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.7505876822825513</v>
+        <v>-0.7505876822821378</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.00145657330068003</v>
+        <v>-0.001456573300679839</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0008825836814738829</v>
+        <v>-0.0008825836814975517</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0290784907041274</v>
+        <v>-0.02907849070410424</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.586244829761654e-14</v>
+        <v>-1.611526070967156e-13</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.000790342354239219</v>
+        <v>-0.0007903423542390336</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6908036589437132</v>
+        <v>-0.6908036589435386</v>
       </c>
       <c r="X11" t="n">
-        <v>0.07036120329871685</v>
+        <v>0.07036120329830216</v>
       </c>
       <c r="Y11" t="n">
-        <v>-2.253216035953992e-14</v>
+        <v>-1.010500600582059e-13</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.03553489535896087</v>
+        <v>-0.03553489535892964</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.0334916199497208</v>
+        <v>-0.03349161994969708</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.00145657330068003</v>
+        <v>-0.001456573300679839</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.7505876822825513</v>
+        <v>-0.7505876822821378</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.4537190030250376</v>
+        <v>0.4537190030243844</v>
       </c>
       <c r="AE11" t="n">
-        <v>-3.586244829761654e-14</v>
+        <v>-1.611526070967156e-13</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.0290784907041274</v>
+        <v>-0.02907849070410424</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0008825836814738829</v>
+        <v>0.0008825836814975517</v>
       </c>
       <c r="AH11" t="n">
-        <v>105.2644895376481</v>
+        <v>105.2644895376473</v>
       </c>
       <c r="AI11" t="n">
-        <v>-9.38396108158932</v>
+        <v>-9.383961081613165</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-46.74768491247382</v>
+        <v>-46.74768491245524</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.7940050285295e-14</v>
+        <v>1.710610954172968e-13</v>
       </c>
       <c r="AL11" t="n">
-        <v>135.4653152928447</v>
+        <v>135.4653152927949</v>
       </c>
       <c r="AM11" t="n">
-        <v>-53.58879393185191</v>
+        <v>-53.58879393192353</v>
       </c>
       <c r="AN11" t="n">
-        <v>-105.2644895376481</v>
+        <v>-105.2644895376473</v>
       </c>
       <c r="AO11" t="n">
-        <v>9.38396108158932</v>
+        <v>9.383961081613165</v>
       </c>
       <c r="AP11" t="n">
-        <v>46.74768491247382</v>
+        <v>46.74768491245524</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-3.7940050285295e-14</v>
+        <v>-1.710610954172968e-13</v>
       </c>
       <c r="AR11" t="n">
-        <v>145.0207941819982</v>
+        <v>145.0207941819365</v>
       </c>
       <c r="AS11" t="n">
-        <v>-2.714972557683836</v>
+        <v>-2.714972557755459</v>
       </c>
     </row>
     <row r="12">
@@ -5381,124 +5381,124 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>0.000699321510061586</v>
+        <v>0.000699321510061491</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0001165535850102643</v>
+        <v>0.0001165535850102485</v>
       </c>
       <c r="H12" t="n">
-        <v>110.4927985897306</v>
+        <v>110.4927985897156</v>
       </c>
       <c r="I12" t="n">
-        <v>23310.71700205286</v>
+        <v>23310.7170020497</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.06987906847877449</v>
+        <v>-0.06987906847835977</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6908036589438927</v>
+        <v>-0.6908036589443535</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002332846674625</v>
+        <v>0.00233284667462481</v>
       </c>
       <c r="M12" t="n">
-        <v>0.03349161994973283</v>
+        <v>0.03349161994976197</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0002044443358560187</v>
+        <v>0.0002044443358872198</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.255910051777855e-14</v>
+        <v>-1.010917419802469e-13</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537911944462054</v>
+        <v>-0.4537911944455522</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.7505876822828246</v>
+        <v>-0.7505876822834716</v>
       </c>
       <c r="R12" t="n">
-        <v>0.003032168184686586</v>
+        <v>0.003032168184686301</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0008825836814639399</v>
+        <v>-0.0008825836814504936</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1913477001707182</v>
+        <v>-0.1913477001706949</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.584592144909157e-14</v>
+        <v>-1.611381091097773e-13</v>
       </c>
       <c r="V12" t="n">
-        <v>0.002332846674625</v>
+        <v>0.00233284667462481</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6908036589438927</v>
+        <v>-0.6908036589443535</v>
       </c>
       <c r="X12" t="n">
-        <v>0.06987906847877449</v>
+        <v>0.06987906847835977</v>
       </c>
       <c r="Y12" t="n">
-        <v>-2.255910051777855e-14</v>
+        <v>-1.010917419802469e-13</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0002044443358560187</v>
+        <v>0.0002044443358872198</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.03349161994973283</v>
+        <v>-0.03349161994976197</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.003032168184686586</v>
+        <v>0.003032168184686301</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.7505876822828246</v>
+        <v>-0.7505876822834716</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.4537911944462054</v>
+        <v>0.4537911944455522</v>
       </c>
       <c r="AE12" t="n">
-        <v>-3.584592144909157e-14</v>
+        <v>-1.611381091097773e-13</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.1913477001707182</v>
+        <v>-0.1913477001706949</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0008825836814639399</v>
+        <v>0.0008825836814504936</v>
       </c>
       <c r="AH12" t="n">
-        <v>-110.4927985897306</v>
+        <v>-110.4927985897156</v>
       </c>
       <c r="AI12" t="n">
-        <v>-9.38396108158247</v>
+        <v>-9.383961081568032</v>
       </c>
       <c r="AJ12" t="n">
-        <v>46.74768491249836</v>
+        <v>46.7476849125169</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.7816336496814e-14</v>
+        <v>1.709011987532788e-13</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.505532197369803</v>
+        <v>1.505532197320065</v>
       </c>
       <c r="AM12" t="n">
-        <v>-53.58879393183292</v>
+        <v>-53.58879393180126</v>
       </c>
       <c r="AN12" t="n">
-        <v>110.4927985897306</v>
+        <v>110.4927985897156</v>
       </c>
       <c r="AO12" t="n">
-        <v>9.38396108158247</v>
+        <v>9.383961081568032</v>
       </c>
       <c r="AP12" t="n">
-        <v>-46.74768491249836</v>
+        <v>-46.7476849125169</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-3.7816336496814e-14</v>
+        <v>-1.709011987532788e-13</v>
       </c>
       <c r="AR12" t="n">
-        <v>-281.99164167236</v>
+        <v>-281.9916416724216</v>
       </c>
       <c r="AS12" t="n">
-        <v>-2.714972557661781</v>
+        <v>-2.714972557606814</v>
       </c>
     </row>
     <row r="13">
@@ -5520,124 +5520,124 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0006662309464408723</v>
+        <v>0.0006662309464407836</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0001110384910734787</v>
+        <v>0.0001110384910734639</v>
       </c>
       <c r="H13" t="n">
-        <v>105.2644895376578</v>
+        <v>105.2644895376438</v>
       </c>
       <c r="I13" t="n">
-        <v>22207.69821469574</v>
+        <v>22207.69821469278</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.06987906847895559</v>
+        <v>-0.06987906847916199</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6912454096233109</v>
+        <v>-0.6912454096237716</v>
       </c>
       <c r="L13" t="n">
-        <v>0.000790342354239359</v>
+        <v>0.0007903423542389292</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0004776631797457648</v>
+        <v>0.0004776631797749287</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0002044443358421079</v>
+        <v>0.0002044443358281631</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.255697836653975e-14</v>
+        <v>-1.010136040492752e-13</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.4537911944465061</v>
+        <v>-0.453791194446797</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.7504936950270665</v>
+        <v>-0.7504936950277137</v>
       </c>
       <c r="R13" t="n">
-        <v>0.001456573300680231</v>
+        <v>0.001456573300679713</v>
       </c>
       <c r="S13" t="n">
-        <v>0.006590736799556234</v>
+        <v>0.006590736799569702</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1913477001707339</v>
+        <v>-0.1913477001707365</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.591934838764536e-14</v>
+        <v>-1.612105836505838e-13</v>
       </c>
       <c r="V13" t="n">
-        <v>0.000790342354239359</v>
+        <v>0.0007903423542389292</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.6912454096233109</v>
+        <v>-0.6912454096237716</v>
       </c>
       <c r="X13" t="n">
-        <v>0.06987906847895559</v>
+        <v>0.06987906847916199</v>
       </c>
       <c r="Y13" t="n">
-        <v>-2.255697836653975e-14</v>
+        <v>-1.010136040492752e-13</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0002044443358421079</v>
+        <v>0.0002044443358281631</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.0004776631797457648</v>
+        <v>-0.0004776631797749287</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.001456573300680231</v>
+        <v>0.001456573300679713</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.7504936950270665</v>
+        <v>-0.7504936950277137</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.4537911944465061</v>
+        <v>0.453791194446797</v>
       </c>
       <c r="AE13" t="n">
-        <v>-3.591934838764536e-14</v>
+        <v>-1.612105836505838e-13</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.1913477001707339</v>
+        <v>-0.1913477001707365</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.006590736799556234</v>
+        <v>-0.006590736799569702</v>
       </c>
       <c r="AH13" t="n">
-        <v>-105.2644895376578</v>
+        <v>-105.2644895376438</v>
       </c>
       <c r="AI13" t="n">
-        <v>9.383961081576246</v>
+        <v>9.383961081590712</v>
       </c>
       <c r="AJ13" t="n">
-        <v>46.74768491249078</v>
+        <v>46.74768491248219</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.803136082930058e-14</v>
+        <v>1.713298650191092e-13</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.505532197393904</v>
+        <v>1.505532197411242</v>
       </c>
       <c r="AM13" t="n">
-        <v>32.67555772338847</v>
+        <v>32.6755577234203</v>
       </c>
       <c r="AN13" t="n">
-        <v>105.2644895376578</v>
+        <v>105.2644895376438</v>
       </c>
       <c r="AO13" t="n">
-        <v>-9.383961081576246</v>
+        <v>-9.383961081590712</v>
       </c>
       <c r="AP13" t="n">
-        <v>-46.74768491249078</v>
+        <v>-46.74768491248219</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-3.803136082930058e-14</v>
+        <v>-1.713298650191092e-13</v>
       </c>
       <c r="AR13" t="n">
-        <v>-281.9916416723386</v>
+        <v>-281.9916416723045</v>
       </c>
       <c r="AS13" t="n">
-        <v>23.62820876606884</v>
+        <v>23.62820876612409</v>
       </c>
     </row>
     <row r="14">
@@ -5659,124 +5659,124 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0001075661259880563</v>
+        <v>-0.0001075661259879882</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.792768766467605e-05</v>
+        <v>-1.79276876646647e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>-16.99544790611289</v>
+        <v>-16.99544790610213</v>
       </c>
       <c r="I14" t="n">
-        <v>-3585.537532935209</v>
+        <v>-3585.537532932939</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4537190030253384</v>
+        <v>-0.4537190030256291</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7504936950267934</v>
+        <v>-0.7504936950263797</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.003032168184686789</v>
+        <v>-0.003032168184686173</v>
       </c>
       <c r="M14" t="n">
-        <v>0.006590736799546265</v>
+        <v>0.006590736799522585</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0290784907041432</v>
+        <v>-0.02907849070414583</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.586128221406856e-14</v>
+        <v>-1.611412101213256e-13</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.8457911393550082</v>
+        <v>-0.845791139355267</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.7611520690276043</v>
+        <v>-0.7611520690270692</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.003139734310674845</v>
+        <v>-0.003139734310674162</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0006683120527693941</v>
+        <v>-0.0006683120527781236</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.05000005721100176</v>
+        <v>-0.05000005721099737</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.797347225031697e-14</v>
+        <v>-1.899677898334275e-13</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.003032168184686789</v>
+        <v>-0.003032168184686173</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.7504936950267934</v>
+        <v>-0.7504936950263797</v>
       </c>
       <c r="X14" t="n">
-        <v>0.4537190030253384</v>
+        <v>0.4537190030256291</v>
       </c>
       <c r="Y14" t="n">
-        <v>-3.586128221406856e-14</v>
+        <v>-1.611412101213256e-13</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.0290784907041432</v>
+        <v>-0.02907849070414583</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.006590736799546265</v>
+        <v>-0.006590736799522585</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.003139734310674845</v>
+        <v>-0.003139734310674162</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.7611520690276043</v>
+        <v>-0.7611520690270692</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.8457911393550082</v>
+        <v>0.845791139355267</v>
       </c>
       <c r="AE14" t="n">
-        <v>-4.797347225031697e-14</v>
+        <v>-1.899677898334275e-13</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.05000005721100176</v>
+        <v>-0.05000005721099737</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0006683120527693941</v>
+        <v>0.0006683120527781236</v>
       </c>
       <c r="AH14" t="n">
-        <v>16.99544790611293</v>
+        <v>16.99544790610213</v>
       </c>
       <c r="AI14" t="n">
-        <v>-1.753528725748197</v>
+        <v>-1.753528725754137</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-38.19300150411129</v>
+        <v>-38.19300150410469</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.44731562570147e-14</v>
+        <v>8.204488071905921e-14</v>
       </c>
       <c r="AL14" t="n">
-        <v>130.0609637274092</v>
+        <v>130.0609637273842</v>
       </c>
       <c r="AM14" t="n">
-        <v>-10.63228232795814</v>
+        <v>-10.63228232796507</v>
       </c>
       <c r="AN14" t="n">
-        <v>-16.99544790611293</v>
+        <v>-16.99544790610213</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.753528725748197</v>
+        <v>1.753528725754137</v>
       </c>
       <c r="AP14" t="n">
-        <v>38.19300150411129</v>
+        <v>38.19300150410469</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-3.44731562570147e-14</v>
+        <v>-8.204488071905921e-14</v>
       </c>
       <c r="AR14" t="n">
-        <v>99.09704529725843</v>
+        <v>99.09704529724391</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.111109973468956</v>
+        <v>0.1111099734400796</v>
       </c>
     </row>
     <row r="15">
@@ -5798,124 +5798,124 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0001024763015164266</v>
+        <v>-0.0001024763015164182</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.70793835860711e-05</v>
+        <v>-1.707938358606969e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>-16.19125563959541</v>
+        <v>-16.19125563959407</v>
       </c>
       <c r="I15" t="n">
-        <v>-3415.876717214221</v>
+        <v>-3415.876717213939</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4537190030250376</v>
+        <v>-0.4537190030243844</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7505876822825513</v>
+        <v>-0.7505876822821378</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.00145657330068003</v>
+        <v>-0.001456573300679839</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0008825836814738829</v>
+        <v>-0.0008825836814975517</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0290784907041274</v>
+        <v>-0.02907849070410424</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.586244829761654e-14</v>
+        <v>-1.611526070967156e-13</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.8457911393545802</v>
+        <v>-0.8457911393537922</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.7611372713168385</v>
+        <v>-0.7611372713163034</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.001559049602196457</v>
+        <v>-0.001559049602196257</v>
       </c>
       <c r="S15" t="n">
-        <v>0.00202947994641545</v>
+        <v>0.002029479946406675</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.05000005721099056</v>
+        <v>-0.05000005721098015</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.795316946883113e-14</v>
+        <v>-1.900821841067412e-13</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.00145657330068003</v>
+        <v>-0.001456573300679839</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7505876822825513</v>
+        <v>-0.7505876822821378</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4537190030250376</v>
+        <v>0.4537190030243844</v>
       </c>
       <c r="Y15" t="n">
-        <v>-3.586244829761654e-14</v>
+        <v>-1.611526070967156e-13</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.0290784907041274</v>
+        <v>-0.02907849070410424</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0008825836814738829</v>
+        <v>0.0008825836814975517</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.001559049602196457</v>
+        <v>-0.001559049602196257</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.7611372713168385</v>
+        <v>-0.7611372713163034</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.8457911393545802</v>
+        <v>0.8457911393537922</v>
       </c>
       <c r="AE15" t="n">
-        <v>-4.795316946883113e-14</v>
+        <v>-1.900821841067412e-13</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.05000005721099056</v>
+        <v>-0.05000005721098015</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.00202947994641545</v>
+        <v>-0.002029479946406675</v>
       </c>
       <c r="AH15" t="n">
-        <v>16.19125563959543</v>
+        <v>16.19125563959406</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.753528725734071</v>
+        <v>1.753528725728103</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-38.19300150409987</v>
+        <v>-38.19300150409149</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.441205256422615e-14</v>
+        <v>8.233802687468803e-14</v>
       </c>
       <c r="AL15" t="n">
-        <v>130.0609637273784</v>
+        <v>130.0609637273625</v>
       </c>
       <c r="AM15" t="n">
-        <v>7.415513261840374</v>
+        <v>7.415513261833325</v>
       </c>
       <c r="AN15" t="n">
-        <v>-16.19125563959543</v>
+        <v>-16.19125563959406</v>
       </c>
       <c r="AO15" t="n">
-        <v>-1.753528725734071</v>
+        <v>-1.753528725728103</v>
       </c>
       <c r="AP15" t="n">
-        <v>38.19300150409987</v>
+        <v>38.19300150409149</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-3.441205256422615e-14</v>
+        <v>-8.233802687468803e-14</v>
       </c>
       <c r="AR15" t="n">
-        <v>99.0970452972208</v>
+        <v>99.09704529718621</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.10565909256411</v>
+        <v>3.10565909253512</v>
       </c>
     </row>
     <row r="16">
@@ -5937,124 +5937,124 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0001075661259880263</v>
+        <v>0.0001075661259879821</v>
       </c>
       <c r="G16" t="n">
-        <v>1.792768766467106e-05</v>
+        <v>1.792768766466369e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>16.99544790610816</v>
+        <v>16.99544790610117</v>
       </c>
       <c r="I16" t="n">
-        <v>3585.537532934211</v>
+        <v>3585.537532932737</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4537911944462054</v>
+        <v>-0.4537911944455522</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7505876822828246</v>
+        <v>-0.7505876822834716</v>
       </c>
       <c r="L16" t="n">
-        <v>0.003032168184686586</v>
+        <v>0.003032168184686301</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0008825836814639399</v>
+        <v>-0.0008825836814504936</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1913477001707182</v>
+        <v>-0.1913477001706949</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.584592144909157e-14</v>
+        <v>-1.611381091097773e-13</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.8461134431647414</v>
+        <v>-0.8461134431639535</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.7611372713171778</v>
+        <v>-0.7611372713178689</v>
       </c>
       <c r="R16" t="n">
-        <v>0.003139734310674613</v>
+        <v>0.003139734310674283</v>
       </c>
       <c r="S16" t="n">
-        <v>0.002029479946420887</v>
+        <v>0.00202947994642285</v>
       </c>
       <c r="T16" t="n">
-        <v>0.008961453069770897</v>
+        <v>0.008961453069781296</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.795187645833391e-14</v>
+        <v>-1.900022251312968e-13</v>
       </c>
       <c r="V16" t="n">
-        <v>0.003032168184686586</v>
+        <v>0.003032168184686301</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7505876822828246</v>
+        <v>-0.7505876822834716</v>
       </c>
       <c r="X16" t="n">
-        <v>0.4537911944462054</v>
+        <v>0.4537911944455522</v>
       </c>
       <c r="Y16" t="n">
-        <v>-3.584592144909157e-14</v>
+        <v>-1.611381091097773e-13</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.1913477001707182</v>
+        <v>-0.1913477001706949</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0008825836814639399</v>
+        <v>0.0008825836814504936</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.003139734310674613</v>
+        <v>0.003139734310674283</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.7611372713171778</v>
+        <v>-0.7611372713178689</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.8461134431647414</v>
+        <v>0.8461134431639535</v>
       </c>
       <c r="AE16" t="n">
-        <v>-4.795187645833391e-14</v>
+        <v>-1.900022251312968e-13</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.008961453069770897</v>
+        <v>0.008961453069781296</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.002029479946420887</v>
+        <v>-0.00202947994642285</v>
       </c>
       <c r="AH16" t="n">
-        <v>-16.99544790610815</v>
+        <v>-16.99544790610116</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.75352872573896</v>
+        <v>1.753528725738448</v>
       </c>
       <c r="AJ16" t="n">
-        <v>38.19300150412879</v>
+        <v>38.19300150413709</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.445541041092048e-14</v>
+        <v>8.215171483047837e-14</v>
       </c>
       <c r="AL16" t="n">
-        <v>-262.8077779103483</v>
+        <v>-262.8077779103638</v>
       </c>
       <c r="AM16" t="n">
-        <v>7.415513261851743</v>
+        <v>7.415513261841625</v>
       </c>
       <c r="AN16" t="n">
-        <v>16.99544790610815</v>
+        <v>16.99544790610116</v>
       </c>
       <c r="AO16" t="n">
-        <v>-1.75352872573896</v>
+        <v>-1.753528725738448</v>
       </c>
       <c r="AP16" t="n">
-        <v>-38.19300150412879</v>
+        <v>-38.19300150413709</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-3.445541041092048e-14</v>
+        <v>-8.215171483047837e-14</v>
       </c>
       <c r="AR16" t="n">
-        <v>33.64976888557555</v>
+        <v>33.64976888554114</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.105659092582187</v>
+        <v>3.105659092589121</v>
       </c>
     </row>
     <row r="17">
@@ -6076,124 +6076,124 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>0.000102476301516457</v>
+        <v>0.0001024763015164238</v>
       </c>
       <c r="G17" t="n">
-        <v>1.707938358607617e-05</v>
+        <v>1.707938358607064e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>16.1912556396002</v>
+        <v>16.19125563959496</v>
       </c>
       <c r="I17" t="n">
-        <v>3415.876717215232</v>
+        <v>3415.876717214127</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4537911944465061</v>
+        <v>-0.453791194446797</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7504936950270665</v>
+        <v>-0.7504936950277137</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001456573300680231</v>
+        <v>0.001456573300679713</v>
       </c>
       <c r="M17" t="n">
-        <v>0.006590736799556234</v>
+        <v>0.006590736799569702</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1913477001707339</v>
+        <v>-0.1913477001707365</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.591934838764536e-14</v>
+        <v>-1.612105836505838e-13</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.8461134431651695</v>
+        <v>-0.8461134431654285</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.7611520690279437</v>
+        <v>-0.7611520690286349</v>
       </c>
       <c r="R17" t="n">
-        <v>0.001559049602196688</v>
+        <v>0.001559049602196137</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0006683120527639328</v>
+        <v>-0.0006683120527619788</v>
       </c>
       <c r="T17" t="n">
-        <v>0.008961453069759602</v>
+        <v>0.008961453069764045</v>
       </c>
       <c r="U17" t="n">
-        <v>-4.795728302061472e-14</v>
+        <v>-1.900474795736123e-13</v>
       </c>
       <c r="V17" t="n">
-        <v>0.001456573300680231</v>
+        <v>0.001456573300679713</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.7504936950270665</v>
+        <v>-0.7504936950277137</v>
       </c>
       <c r="X17" t="n">
-        <v>0.4537911944465061</v>
+        <v>0.453791194446797</v>
       </c>
       <c r="Y17" t="n">
-        <v>-3.591934838764536e-14</v>
+        <v>-1.612105836505838e-13</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.1913477001707339</v>
+        <v>-0.1913477001707365</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.006590736799556234</v>
+        <v>-0.006590736799569702</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.001559049602196688</v>
+        <v>0.001559049602196137</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.7611520690279437</v>
+        <v>-0.7611520690286349</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.8461134431651695</v>
+        <v>0.8461134431654285</v>
       </c>
       <c r="AE17" t="n">
-        <v>-4.795728302061472e-14</v>
+        <v>-1.900474795736123e-13</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.008961453069759602</v>
+        <v>0.008961453069764045</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0006683120527639328</v>
+        <v>0.0006683120527619788</v>
       </c>
       <c r="AH17" t="n">
-        <v>-16.1912556396002</v>
+        <v>-16.19125563959497</v>
       </c>
       <c r="AI17" t="n">
-        <v>-1.75352872574328</v>
+        <v>-1.75352872574382</v>
       </c>
       <c r="AJ17" t="n">
-        <v>38.19300150411733</v>
+        <v>38.19300150412386</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.426181395537433e-14</v>
+        <v>8.207424224246545e-14</v>
       </c>
       <c r="AL17" t="n">
-        <v>-262.8077779103172</v>
+        <v>-262.8077779103419</v>
       </c>
       <c r="AM17" t="n">
-        <v>-10.63228232794665</v>
+        <v>-10.63228232795689</v>
       </c>
       <c r="AN17" t="n">
-        <v>16.1912556396002</v>
+        <v>16.19125563959497</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.75352872574328</v>
+        <v>1.75352872574382</v>
       </c>
       <c r="AP17" t="n">
-        <v>-38.19300150411733</v>
+        <v>-38.19300150412386</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-3.426181395537433e-14</v>
+        <v>-8.207424224246545e-14</v>
       </c>
       <c r="AR17" t="n">
-        <v>33.64976888561318</v>
+        <v>33.64976888559887</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.1111099734872596</v>
+        <v>0.1111099734938534</v>
       </c>
     </row>
     <row r="18">
@@ -6215,124 +6215,124 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0001033262400798596</v>
+        <v>0.0001033262400799706</v>
       </c>
       <c r="G18" t="n">
-        <v>1.291578000998245e-05</v>
+        <v>1.291578000999632e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>12.24415944946336</v>
+        <v>12.24415944947652</v>
       </c>
       <c r="I18" t="n">
-        <v>2583.15600199649</v>
+        <v>2583.156001999265</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.008506800363761516</v>
+        <v>-0.008506800363843648</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3200869679146637</v>
+        <v>-0.3200869679146143</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.001454028388444138</v>
+        <v>-0.001454028388443931</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1813005936458008</v>
+        <v>0.1813005936457907</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0008825836814662386</v>
+        <v>0.0008825836814519907</v>
       </c>
       <c r="O18" t="n">
-        <v>-9.285603354946163e-15</v>
+        <v>-3.950848033461115e-14</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.008506800363690507</v>
+        <v>-0.008506800363530128</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.3199836416745839</v>
+        <v>-0.3199836416745343</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.000121566495562611</v>
+        <v>-0.0001215664955624709</v>
       </c>
       <c r="S18" t="n">
-        <v>0.03205627621730149</v>
+        <v>0.0320562762172913</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0008825836814785056</v>
+        <v>0.0008825836815066833</v>
       </c>
       <c r="U18" t="n">
-        <v>-9.295205578831507e-15</v>
+        <v>-3.953174045802473e-14</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3200869679146637</v>
+        <v>-0.3200869679146143</v>
       </c>
       <c r="W18" t="n">
-        <v>0.008506800363761516</v>
+        <v>0.008506800363843648</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.001454028388444138</v>
+        <v>-0.001454028388443931</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.0008825836814662386</v>
+        <v>0.0008825836814519907</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.1813005936458008</v>
+        <v>-0.1813005936457907</v>
       </c>
       <c r="AA18" t="n">
-        <v>-9.285603354946163e-15</v>
+        <v>-3.950848033461115e-14</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.3199836416745839</v>
+        <v>-0.3199836416745343</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.008506800363690507</v>
+        <v>0.008506800363530128</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.000121566495562611</v>
+        <v>-0.0001215664955624709</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.0008825836814785056</v>
+        <v>0.0008825836815066833</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.03205627621730149</v>
+        <v>-0.0320562762172913</v>
       </c>
       <c r="AG18" t="n">
-        <v>-9.295205578831507e-15</v>
+        <v>-3.953174045802473e-14</v>
       </c>
       <c r="AH18" t="n">
-        <v>-12.24415944946668</v>
+        <v>-12.24415944947395</v>
       </c>
       <c r="AI18" t="n">
-        <v>-3.448352714485736e-13</v>
+        <v>-2.747801985947262e-13</v>
       </c>
       <c r="AJ18" t="n">
-        <v>88.67113776478836</v>
+        <v>88.6711377647799</v>
       </c>
       <c r="AK18" t="n">
-        <v>-2.618521718900091e-14</v>
+        <v>-1.167475404545426e-13</v>
       </c>
       <c r="AL18" t="n">
-        <v>-437.5151472319706</v>
+        <v>-437.5151472319367</v>
       </c>
       <c r="AM18" t="n">
-        <v>-1.374012015276094e-12</v>
+        <v>-1.086242207293253e-12</v>
       </c>
       <c r="AN18" t="n">
-        <v>12.24415944946668</v>
+        <v>12.24415944947395</v>
       </c>
       <c r="AO18" t="n">
-        <v>3.448352714485736e-13</v>
+        <v>2.747801985947262e-13</v>
       </c>
       <c r="AP18" t="n">
-        <v>-88.67113776478836</v>
+        <v>-88.6711377647799</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.618521718900091e-14</v>
+        <v>1.167475404545426e-13</v>
       </c>
       <c r="AR18" t="n">
-        <v>-271.8539548863363</v>
+        <v>-271.8539548863024</v>
       </c>
       <c r="AS18" t="n">
-        <v>-1.384670156312495e-12</v>
+        <v>-1.111999381464557e-12</v>
       </c>
     </row>
     <row r="19">
@@ -6366,112 +6366,112 @@
         <v>-2771.465667658624</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.008506800363690507</v>
+        <v>-0.008506800363530128</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3199836416745839</v>
+        <v>-0.3199836416745343</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.000121566495562611</v>
+        <v>-0.0001215664955624709</v>
       </c>
       <c r="M19" t="n">
-        <v>0.03205627621730149</v>
+        <v>0.0320562762172913</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0008825836814785056</v>
+        <v>0.0008825836815066833</v>
       </c>
       <c r="O19" t="n">
-        <v>-9.295205578831507e-15</v>
+        <v>-3.953174045802473e-14</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.008617658990396852</v>
+        <v>-0.008617658990236473</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.3199836416746615</v>
+        <v>-0.319983641674853</v>
       </c>
       <c r="R19" t="n">
-        <v>0.001454028388444068</v>
+        <v>0.001454028388443984</v>
       </c>
       <c r="S19" t="n">
-        <v>0.03205627621731389</v>
+        <v>0.03205627621734609</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.006590736799541642</v>
+        <v>-0.006590736799513456</v>
       </c>
       <c r="U19" t="n">
-        <v>-9.296542609148836e-15</v>
+        <v>-3.95222817975377e-14</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.008506800363690507</v>
+        <v>-0.008506800363530128</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3199836416745839</v>
+        <v>-0.3199836416745343</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.000121566495562611</v>
+        <v>-0.0001215664955624709</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.03205627621730149</v>
+        <v>0.0320562762172913</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.0008825836814785056</v>
+        <v>0.0008825836815066833</v>
       </c>
       <c r="AA19" t="n">
-        <v>-9.295205578831507e-15</v>
+        <v>-3.953174045802473e-14</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.008617658990396852</v>
+        <v>-0.008617658990236473</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.3199836416746615</v>
+        <v>-0.319983641674853</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.001454028388444068</v>
+        <v>0.001454028388443984</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.03205627621731389</v>
+        <v>0.03205627621734609</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.006590736799541642</v>
+        <v>-0.006590736799513456</v>
       </c>
       <c r="AG19" t="n">
-        <v>-9.296542609148836e-15</v>
+        <v>-3.95222817975377e-14</v>
       </c>
       <c r="AH19" t="n">
         <v>13.13674726470185</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.410605131648481e-13</v>
+        <v>2.629008122312371e-13</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.212058392776836</v>
+        <v>2.212058392753398</v>
       </c>
       <c r="AK19" t="n">
-        <v>-2.646494134950217e-14</v>
+        <v>-1.169619956442602e-13</v>
       </c>
       <c r="AL19" t="n">
-        <v>-4.70054070414116</v>
+        <v>-4.700540704047413</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.392663762089796e-12</v>
+        <v>1.023181539494544e-12</v>
       </c>
       <c r="AN19" t="n">
         <v>-13.13674726470185</v>
       </c>
       <c r="AO19" t="n">
-        <v>-3.410605131648481e-13</v>
+        <v>-2.629008122312371e-13</v>
       </c>
       <c r="AP19" t="n">
-        <v>-2.212058392776836</v>
+        <v>-2.212058392753398</v>
       </c>
       <c r="AQ19" t="n">
-        <v>2.646494134950217e-14</v>
+        <v>1.169619956442602e-13</v>
       </c>
       <c r="AR19" t="n">
-        <v>-12.99592643807352</v>
+        <v>-12.99592643797977</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.392663762089796e-12</v>
+        <v>1.051603248924948e-12</v>
       </c>
     </row>
     <row r="20">
@@ -6493,124 +6493,124 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0001033262400799706</v>
+        <v>0.0001033262400798596</v>
       </c>
       <c r="G20" t="n">
-        <v>1.291578000999632e-05</v>
+        <v>1.291578000998245e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>12.24415944947652</v>
+        <v>12.24415944946336</v>
       </c>
       <c r="I20" t="n">
-        <v>2583.156001999265</v>
+        <v>2583.15600199649</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.008617658990396852</v>
+        <v>-0.008617658990236473</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3199836416746615</v>
+        <v>-0.319983641674853</v>
       </c>
       <c r="L20" t="n">
-        <v>0.001454028388444068</v>
+        <v>0.001454028388443984</v>
       </c>
       <c r="M20" t="n">
-        <v>0.03205627621731389</v>
+        <v>0.03205627621734609</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.006590736799541642</v>
+        <v>-0.006590736799513456</v>
       </c>
       <c r="O20" t="n">
-        <v>-9.296542609148836e-15</v>
+        <v>-3.95222817975377e-14</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.008617658990467861</v>
+        <v>-0.008617658990549991</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.3200869679147415</v>
+        <v>-0.3200869679149329</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0001215664955626805</v>
+        <v>0.0001215664955624186</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1813005936458132</v>
+        <v>0.1813005936458454</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.006590736799553908</v>
+        <v>-0.006590736799568158</v>
       </c>
       <c r="U20" t="n">
-        <v>-9.303613152494448e-15</v>
+        <v>-3.952324315212423e-14</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3199836416746615</v>
+        <v>0.319983641674853</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.008617658990396852</v>
+        <v>-0.008617658990236473</v>
       </c>
       <c r="X20" t="n">
-        <v>0.001454028388444068</v>
+        <v>0.001454028388443984</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.006590736799541642</v>
+        <v>0.006590736799513456</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.03205627621731389</v>
+        <v>0.03205627621734609</v>
       </c>
       <c r="AA20" t="n">
-        <v>-9.296542609148836e-15</v>
+        <v>-3.95222817975377e-14</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.3200869679147415</v>
+        <v>0.3200869679149329</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.008617658990467861</v>
+        <v>-0.008617658990549991</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.0001215664955626805</v>
+        <v>0.0001215664955624186</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.006590736799553908</v>
+        <v>0.006590736799568158</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.1813005936458132</v>
+        <v>0.1813005936458454</v>
       </c>
       <c r="AG20" t="n">
-        <v>-9.303613152494448e-15</v>
+        <v>-3.952324315212423e-14</v>
       </c>
       <c r="AH20" t="n">
-        <v>-12.24415944947395</v>
+        <v>-12.24415944946668</v>
       </c>
       <c r="AI20" t="n">
-        <v>-3.529398995283373e-13</v>
+        <v>-2.771116669464391e-13</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-88.67113776479871</v>
+        <v>-88.67113776482549</v>
       </c>
       <c r="AK20" t="n">
-        <v>-2.618391614639393e-14</v>
+        <v>-1.167677066149508e-13</v>
       </c>
       <c r="AL20" t="n">
-        <v>271.8539548863777</v>
+        <v>271.8539548864848</v>
       </c>
       <c r="AM20" t="n">
-        <v>-1.407318706014848e-12</v>
+        <v>-1.108002578575906e-12</v>
       </c>
       <c r="AN20" t="n">
-        <v>12.24415944947395</v>
+        <v>12.24415944946668</v>
       </c>
       <c r="AO20" t="n">
-        <v>3.529398995283373e-13</v>
+        <v>2.771116669464391e-13</v>
       </c>
       <c r="AP20" t="n">
-        <v>88.67113776479871</v>
+        <v>88.67113776482549</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2.618391614639393e-14</v>
+        <v>1.167677066149508e-13</v>
       </c>
       <c r="AR20" t="n">
-        <v>437.515147232012</v>
+        <v>437.515147232119</v>
       </c>
       <c r="AS20" t="n">
-        <v>-1.415756401002e-12</v>
+        <v>-1.109334846205456e-12</v>
       </c>
     </row>
     <row r="21">
@@ -6632,124 +6632,124 @@
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0001108586267063449</v>
+        <v>-0.0001108586267063432</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.385732833829312e-05</v>
+        <v>-1.38573283382929e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>-13.13674726470188</v>
+        <v>-13.13674726470167</v>
       </c>
       <c r="I21" t="n">
-        <v>-2771.465667658624</v>
+        <v>-2771.46566765858</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.008617658990467861</v>
+        <v>-0.008617658990549991</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3200869679147415</v>
+        <v>-0.3200869679149329</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0001215664955626805</v>
+        <v>0.0001215664955624186</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1813005936458132</v>
+        <v>0.1813005936458454</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.006590736799553908</v>
+        <v>-0.006590736799568158</v>
       </c>
       <c r="O21" t="n">
-        <v>-9.303613152494448e-15</v>
+        <v>-3.952324315212423e-14</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.008506800363761516</v>
+        <v>-0.008506800363843648</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.3200869679146637</v>
+        <v>-0.3200869679146143</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.001454028388444138</v>
+        <v>-0.001454028388443931</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1813005936458008</v>
+        <v>0.1813005936457907</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0008825836814662386</v>
+        <v>0.0008825836814519907</v>
       </c>
       <c r="U21" t="n">
-        <v>-9.285603354946163e-15</v>
+        <v>-3.950848033461115e-14</v>
       </c>
       <c r="V21" t="n">
-        <v>0.008617658990467861</v>
+        <v>0.008617658990549991</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3200869679147415</v>
+        <v>-0.3200869679149329</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.0001215664955626805</v>
+        <v>-0.0001215664955624186</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.1813005936458132</v>
+        <v>-0.1813005936458454</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.006590736799553908</v>
+        <v>-0.006590736799568158</v>
       </c>
       <c r="AA21" t="n">
-        <v>9.303613152494448e-15</v>
+        <v>3.952324315212423e-14</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.008506800363761516</v>
+        <v>0.008506800363843648</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.3200869679146637</v>
+        <v>-0.3200869679146143</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.001454028388444138</v>
+        <v>0.001454028388443931</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.1813005936458008</v>
+        <v>-0.1813005936457907</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.0008825836814662386</v>
+        <v>0.0008825836814519907</v>
       </c>
       <c r="AG21" t="n">
-        <v>9.285603354946163e-15</v>
+        <v>3.950848033461115e-14</v>
       </c>
       <c r="AH21" t="n">
-        <v>13.13674726470185</v>
+        <v>13.13674726470174</v>
       </c>
       <c r="AI21" t="n">
-        <v>-3.552713678800501e-13</v>
+        <v>-2.557953848736361e-13</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.212058392787033</v>
+        <v>2.212058392798944</v>
       </c>
       <c r="AK21" t="n">
-        <v>-2.653433028854124e-14</v>
+        <v>-1.168509733417977e-13</v>
       </c>
       <c r="AL21" t="n">
-        <v>-12.99592643811431</v>
+        <v>-12.99592643816196</v>
       </c>
       <c r="AM21" t="n">
-        <v>-1.392663762089796e-12</v>
+        <v>-9.947598300641403e-13</v>
       </c>
       <c r="AN21" t="n">
-        <v>-13.13674726470185</v>
+        <v>-13.13674726470174</v>
       </c>
       <c r="AO21" t="n">
-        <v>3.552713678800501e-13</v>
+        <v>2.557953848736361e-13</v>
       </c>
       <c r="AP21" t="n">
-        <v>-2.212058392787033</v>
+        <v>-2.212058392798944</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2.653433028854124e-14</v>
+        <v>1.168509733417977e-13</v>
       </c>
       <c r="AR21" t="n">
-        <v>-4.70054070418195</v>
+        <v>-4.700540704229594</v>
       </c>
       <c r="AS21" t="n">
-        <v>-1.449507180950604e-12</v>
+        <v>-9.947598300641403e-13</v>
       </c>
     </row>
     <row r="22">
@@ -6771,124 +6771,124 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0004417506794179848</v>
+        <v>0.0004417506794183179</v>
       </c>
       <c r="G22" t="n">
-        <v>5.521883492724811e-05</v>
+        <v>5.521883492728974e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>52.34745551103121</v>
+        <v>52.34745551107067</v>
       </c>
       <c r="I22" t="n">
-        <v>11043.76698544962</v>
+        <v>11043.76698545795</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.07036120329889795</v>
+        <v>-0.07036120329910434</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6912454096231312</v>
+        <v>-0.6912454096229569</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.002332846674625141</v>
+        <v>-0.002332846674624704</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0004776631797337471</v>
+        <v>0.0004776631797100466</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.03553489535897476</v>
+        <v>-0.0355348953589887</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.254982535921031e-14</v>
+        <v>-1.010899116652667e-13</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.07036120329871685</v>
+        <v>-0.07036120329830216</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.6908036589437132</v>
+        <v>-0.6908036589435386</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.000790342354239219</v>
+        <v>-0.0007903423542390336</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0334916199497208</v>
+        <v>0.03349161994969708</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.03553489535896087</v>
+        <v>-0.03553489535892964</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.253216035953992e-14</v>
+        <v>-1.010500600582059e-13</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6912454096231312</v>
+        <v>-0.6912454096229569</v>
       </c>
       <c r="W22" t="n">
-        <v>0.07036120329889795</v>
+        <v>0.07036120329910434</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.002332846674625141</v>
+        <v>-0.002332846674624704</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.03553489535897476</v>
+        <v>-0.0355348953589887</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.0004776631797337471</v>
+        <v>-0.0004776631797100466</v>
       </c>
       <c r="AA22" t="n">
-        <v>-2.254982535921031e-14</v>
+        <v>-1.010899116652667e-13</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.6908036589437132</v>
+        <v>-0.6908036589435386</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.07036120329871685</v>
+        <v>0.07036120329830216</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.000790342354239219</v>
+        <v>-0.0007903423542390336</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.03553489535896087</v>
+        <v>-0.03553489535892964</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.0334916199497208</v>
+        <v>-0.03349161994969708</v>
       </c>
       <c r="AG22" t="n">
-        <v>-2.253216035953992e-14</v>
+        <v>-1.010500600582059e-13</v>
       </c>
       <c r="AH22" t="n">
-        <v>-52.34745551102969</v>
+        <v>-52.34745551107335</v>
       </c>
       <c r="AI22" t="n">
-        <v>7.904787935331115e-14</v>
+        <v>-6.643574579356937e-13</v>
       </c>
       <c r="AJ22" t="n">
-        <v>13.97919724679529</v>
+        <v>13.97919724677558</v>
       </c>
       <c r="AK22" t="n">
-        <v>-2.964295475749168e-14</v>
+        <v>-1.260797022339943e-13</v>
       </c>
       <c r="AL22" t="n">
-        <v>-37.59404297983836</v>
+        <v>-37.59404297975952</v>
       </c>
       <c r="AM22" t="n">
-        <v>3.055333763768431e-13</v>
+        <v>-2.682298827494378e-12</v>
       </c>
       <c r="AN22" t="n">
-        <v>52.34745551102969</v>
+        <v>52.34745551107335</v>
       </c>
       <c r="AO22" t="n">
-        <v>-7.904787935331115e-14</v>
+        <v>6.643574579356937e-13</v>
       </c>
       <c r="AP22" t="n">
-        <v>-13.97919724679529</v>
+        <v>-13.97919724677558</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.964295475749168e-14</v>
+        <v>1.260797022339943e-13</v>
       </c>
       <c r="AR22" t="n">
-        <v>-74.23953499452399</v>
+        <v>-74.23953499444512</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.268496584496461e-13</v>
+        <v>-2.636113549669972e-12</v>
       </c>
     </row>
     <row r="23">
@@ -6910,124 +6910,124 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0004821348199423592</v>
+        <v>0.0004821348199423869</v>
       </c>
       <c r="G23" t="n">
-        <v>6.02668524927949e-05</v>
+        <v>6.026685249279837e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>57.13297616316957</v>
+        <v>57.13297616317285</v>
       </c>
       <c r="I23" t="n">
-        <v>12053.37049855898</v>
+        <v>12053.37049855967</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.07036120329871685</v>
+        <v>-0.07036120329830216</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6908036589437132</v>
+        <v>-0.6908036589435386</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.000790342354239219</v>
+        <v>-0.0007903423542390336</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0334916199497208</v>
+        <v>0.03349161994969708</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.03553489535896087</v>
+        <v>-0.03553489535892964</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.253216035953992e-14</v>
+        <v>-1.010500600582059e-13</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.06987906847877449</v>
+        <v>-0.06987906847835977</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.6908036589438927</v>
+        <v>-0.6908036589443535</v>
       </c>
       <c r="R23" t="n">
-        <v>0.002332846674625</v>
+        <v>0.00233284667462481</v>
       </c>
       <c r="S23" t="n">
-        <v>0.03349161994973283</v>
+        <v>0.03349161994976197</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0002044443358560187</v>
+        <v>0.0002044443358872198</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.255910051777855e-14</v>
+        <v>-1.010917419802469e-13</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.07036120329871685</v>
+        <v>-0.07036120329830216</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6908036589437132</v>
+        <v>-0.6908036589435386</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.000790342354239219</v>
+        <v>-0.0007903423542390336</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.0334916199497208</v>
+        <v>0.03349161994969708</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.03553489535896087</v>
+        <v>-0.03553489535892964</v>
       </c>
       <c r="AA23" t="n">
-        <v>-2.253216035953992e-14</v>
+        <v>-1.010500600582059e-13</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.06987906847877449</v>
+        <v>-0.06987906847835977</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.6908036589438927</v>
+        <v>-0.6908036589443535</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.002332846674625</v>
+        <v>0.00233284667462481</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.03349161994973283</v>
+        <v>0.03349161994976197</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.0002044443358560187</v>
+        <v>0.0002044443358872198</v>
       </c>
       <c r="AG23" t="n">
-        <v>-2.255910051777855e-14</v>
+        <v>-1.010917419802469e-13</v>
       </c>
       <c r="AH23" t="n">
-        <v>-57.13297616316959</v>
+        <v>-57.13297616317323</v>
       </c>
       <c r="AI23" t="n">
-        <v>-8.526512829121202e-14</v>
+        <v>6.679101716144942e-13</v>
       </c>
       <c r="AJ23" t="n">
-        <v>14.38129338005121</v>
+        <v>14.38129338002526</v>
       </c>
       <c r="AK23" t="n">
-        <v>-2.568778523226456e-14</v>
+        <v>-1.385142001097961e-13</v>
       </c>
       <c r="AL23" t="n">
-        <v>-77.36050705082822</v>
+        <v>-77.36050705072442</v>
       </c>
       <c r="AM23" t="n">
-        <v>-3.410605131648481e-13</v>
+        <v>2.728484105318785e-12</v>
       </c>
       <c r="AN23" t="n">
-        <v>57.13297616316959</v>
+        <v>57.13297616317323</v>
       </c>
       <c r="AO23" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>-6.679101716144942e-13</v>
       </c>
       <c r="AP23" t="n">
-        <v>-14.38129338005121</v>
+        <v>-14.38129338002526</v>
       </c>
       <c r="AQ23" t="n">
-        <v>2.568778523226456e-14</v>
+        <v>1.385142001097961e-13</v>
       </c>
       <c r="AR23" t="n">
-        <v>-37.68983998958147</v>
+        <v>-37.68983998947769</v>
       </c>
       <c r="AS23" t="n">
-        <v>-3.410605131648481e-13</v>
+        <v>2.671640686457977e-12</v>
       </c>
     </row>
     <row r="24">
@@ -7049,124 +7049,124 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0004417506794182069</v>
+        <v>0.0004417506794180959</v>
       </c>
       <c r="G24" t="n">
-        <v>5.521883492727586e-05</v>
+        <v>5.521883492726198e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>52.34745551105752</v>
+        <v>52.34745551104436</v>
       </c>
       <c r="I24" t="n">
-        <v>11043.76698545517</v>
+        <v>11043.7669854524</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.06987906847877449</v>
+        <v>-0.06987906847835977</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6908036589438927</v>
+        <v>-0.6908036589443535</v>
       </c>
       <c r="L24" t="n">
-        <v>0.002332846674625</v>
+        <v>0.00233284667462481</v>
       </c>
       <c r="M24" t="n">
-        <v>0.03349161994973283</v>
+        <v>0.03349161994976197</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0002044443358560187</v>
+        <v>0.0002044443358872198</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.255910051777855e-14</v>
+        <v>-1.010917419802469e-13</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.06987906847895559</v>
+        <v>-0.06987906847916199</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.6912454096233109</v>
+        <v>-0.6912454096237716</v>
       </c>
       <c r="R24" t="n">
-        <v>0.000790342354239359</v>
+        <v>0.0007903423542389292</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0004776631797457648</v>
+        <v>0.0004776631797749287</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0002044443358421079</v>
+        <v>0.0002044443358281631</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.255697836653975e-14</v>
+        <v>-1.010136040492752e-13</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6908036589438927</v>
+        <v>0.6908036589443535</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.06987906847877449</v>
+        <v>-0.06987906847835977</v>
       </c>
       <c r="X24" t="n">
-        <v>0.002332846674625</v>
+        <v>0.00233284667462481</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.0002044443358560187</v>
+        <v>-0.0002044443358872198</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.03349161994973283</v>
+        <v>0.03349161994976197</v>
       </c>
       <c r="AA24" t="n">
-        <v>-2.255910051777855e-14</v>
+        <v>-1.010917419802469e-13</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.6912454096233109</v>
+        <v>0.6912454096237716</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.06987906847895559</v>
+        <v>-0.06987906847916199</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.000790342354239359</v>
+        <v>0.0007903423542389292</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.0002044443358421079</v>
+        <v>-0.0002044443358281631</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.0004776631797457648</v>
+        <v>0.0004776631797749287</v>
       </c>
       <c r="AG24" t="n">
-        <v>-2.255697836653975e-14</v>
+        <v>-1.010136040492752e-13</v>
       </c>
       <c r="AH24" t="n">
-        <v>-52.3474555110588</v>
+        <v>-52.34745551104425</v>
       </c>
       <c r="AI24" t="n">
-        <v>6.661338147750939e-14</v>
+        <v>-6.45705711121991e-13</v>
       </c>
       <c r="AJ24" t="n">
-        <v>-13.97919724680534</v>
+        <v>-13.97919724682958</v>
       </c>
       <c r="AK24" t="n">
-        <v>-2.969423752025024e-14</v>
+        <v>-1.260634392014071e-13</v>
       </c>
       <c r="AL24" t="n">
-        <v>74.23953499456417</v>
+        <v>74.23953499466113</v>
       </c>
       <c r="AM24" t="n">
-        <v>2.593480985524366e-13</v>
+        <v>-2.62545540863357e-12</v>
       </c>
       <c r="AN24" t="n">
-        <v>52.3474555110588</v>
+        <v>52.34745551104425</v>
       </c>
       <c r="AO24" t="n">
-        <v>-6.661338147750939e-14</v>
+        <v>6.45705711121991e-13</v>
       </c>
       <c r="AP24" t="n">
-        <v>13.97919724680534</v>
+        <v>13.97919724682958</v>
       </c>
       <c r="AQ24" t="n">
-        <v>2.969423752025024e-14</v>
+        <v>1.260634392014071e-13</v>
       </c>
       <c r="AR24" t="n">
-        <v>37.59404297987852</v>
+        <v>37.5940429799755</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.664535259100376e-13</v>
+        <v>-2.540190280342358e-12</v>
       </c>
     </row>
     <row r="25">
@@ -7188,124 +7188,124 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0004821348199423592</v>
+        <v>0.0004821348199423453</v>
       </c>
       <c r="G25" t="n">
-        <v>6.02668524927949e-05</v>
+        <v>6.026685249279316e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>57.13297616316957</v>
+        <v>57.13297616316792</v>
       </c>
       <c r="I25" t="n">
-        <v>12053.37049855898</v>
+        <v>12053.37049855863</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.06987906847895559</v>
+        <v>-0.06987906847916199</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6912454096233109</v>
+        <v>-0.6912454096237716</v>
       </c>
       <c r="L25" t="n">
-        <v>0.000790342354239359</v>
+        <v>0.0007903423542389292</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0004776631797457648</v>
+        <v>0.0004776631797749287</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0002044443358421079</v>
+        <v>0.0002044443358281631</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.255697836653975e-14</v>
+        <v>-1.010136040492752e-13</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.07036120329889795</v>
+        <v>-0.07036120329910434</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.6912454096231312</v>
+        <v>-0.6912454096229569</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.002332846674625141</v>
+        <v>-0.002332846674624704</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0004776631797337471</v>
+        <v>0.0004776631797100466</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.03553489535897476</v>
+        <v>-0.0355348953589887</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.254982535921031e-14</v>
+        <v>-1.010899116652667e-13</v>
       </c>
       <c r="V25" t="n">
-        <v>0.06987906847895559</v>
+        <v>0.06987906847916199</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.6912454096233109</v>
+        <v>-0.6912454096237716</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.000790342354239359</v>
+        <v>-0.0007903423542389292</v>
       </c>
       <c r="Y25" t="n">
-        <v>-0.0004776631797457648</v>
+        <v>-0.0004776631797749287</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.0002044443358421079</v>
+        <v>0.0002044443358281631</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.255697836653975e-14</v>
+        <v>1.010136040492752e-13</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.07036120329889795</v>
+        <v>0.07036120329910434</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.6912454096231312</v>
+        <v>-0.6912454096229569</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.002332846674625141</v>
+        <v>0.002332846674624704</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.0004776631797337471</v>
+        <v>-0.0004776631797100466</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.03553489535897476</v>
+        <v>-0.0355348953589887</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.254982535921031e-14</v>
+        <v>1.010899116652667e-13</v>
       </c>
       <c r="AH25" t="n">
-        <v>-57.13297616316959</v>
+        <v>-57.13297616316777</v>
       </c>
       <c r="AI25" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>-6.394884621840902e-13</v>
       </c>
       <c r="AJ25" t="n">
-        <v>14.38129338006276</v>
+        <v>14.38129338007445</v>
       </c>
       <c r="AK25" t="n">
-        <v>-2.565309076274502e-14</v>
+        <v>-1.384983707580778e-13</v>
       </c>
       <c r="AL25" t="n">
-        <v>-37.68983998962765</v>
+        <v>-37.68983998967445</v>
       </c>
       <c r="AM25" t="n">
-        <v>2.842170943040401e-13</v>
+        <v>-2.614797267597169e-12</v>
       </c>
       <c r="AN25" t="n">
-        <v>57.13297616316959</v>
+        <v>57.13297616316777</v>
       </c>
       <c r="AO25" t="n">
-        <v>-8.526512829121202e-14</v>
+        <v>6.394884621840902e-13</v>
       </c>
       <c r="AP25" t="n">
-        <v>-14.38129338006276</v>
+        <v>-14.38129338007445</v>
       </c>
       <c r="AQ25" t="n">
-        <v>2.565309076274502e-14</v>
+        <v>1.384983707580778e-13</v>
       </c>
       <c r="AR25" t="n">
-        <v>-77.36050705087436</v>
+        <v>-77.36050705092119</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.842170943040401e-13</v>
+        <v>-2.501110429875553e-12</v>
       </c>
     </row>
     <row r="26">
@@ -7327,124 +7327,124 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-9.398725575793243e-05</v>
+        <v>-9.398725575804345e-05</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.174840696974155e-05</v>
+        <v>-1.174840696975543e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>-11.13748980731499</v>
+        <v>-11.13748980732815</v>
       </c>
       <c r="I26" t="n">
-        <v>-2349.68139394831</v>
+        <v>-2349.681393951086</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4537190030253384</v>
+        <v>-0.4537190030256291</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.7504936950267934</v>
+        <v>-0.7504936950263797</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.003032168184686789</v>
+        <v>-0.003032168184686173</v>
       </c>
       <c r="M26" t="n">
-        <v>0.006590736799546265</v>
+        <v>0.006590736799522585</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.0290784907041432</v>
+        <v>-0.02907849070414583</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.586128221406856e-14</v>
+        <v>-1.611412101213256e-13</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.4537190030250376</v>
+        <v>-0.4537190030243844</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.7505876822825513</v>
+        <v>-0.7505876822821378</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.00145657330068003</v>
+        <v>-0.001456573300679839</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0008825836814738829</v>
+        <v>-0.0008825836814975517</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0290784907041274</v>
+        <v>-0.02907849070410424</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.586244829761654e-14</v>
+        <v>-1.611526070967156e-13</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.7504936950267934</v>
+        <v>-0.7504936950263797</v>
       </c>
       <c r="W26" t="n">
-        <v>0.4537190030253384</v>
+        <v>0.4537190030256291</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.003032168184686789</v>
+        <v>-0.003032168184686173</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.0290784907041432</v>
+        <v>-0.02907849070414583</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.006590736799546265</v>
+        <v>-0.006590736799522585</v>
       </c>
       <c r="AA26" t="n">
-        <v>-3.586128221406856e-14</v>
+        <v>-1.611412101213256e-13</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.7505876822825513</v>
+        <v>-0.7505876822821378</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.4537190030250376</v>
+        <v>0.4537190030243844</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.00145657330068003</v>
+        <v>-0.001456573300679839</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.0290784907041274</v>
+        <v>-0.02907849070410424</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.0008825836814738829</v>
+        <v>0.0008825836814975517</v>
       </c>
       <c r="AG26" t="n">
-        <v>-3.586244829761654e-14</v>
+        <v>-1.611526070967156e-13</v>
       </c>
       <c r="AH26" t="n">
         <v>11.13748980732635</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.435296326235402e-12</v>
+        <v>-4.632738637155853e-12</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.212058392780676</v>
+        <v>2.212058392761011</v>
       </c>
       <c r="AK26" t="n">
-        <v>-3.371608547908522e-14</v>
+        <v>-8.879008639439689e-14</v>
       </c>
       <c r="AL26" t="n">
-        <v>-12.99592643808889</v>
+        <v>-12.99592643801022</v>
       </c>
       <c r="AM26" t="n">
-        <v>5.74118530494161e-12</v>
+        <v>-1.853095454862341e-11</v>
       </c>
       <c r="AN26" t="n">
         <v>-11.13748980732635</v>
       </c>
       <c r="AO26" t="n">
-        <v>-1.435296326235402e-12</v>
+        <v>4.632738637155853e-12</v>
       </c>
       <c r="AP26" t="n">
-        <v>-2.212058392780676</v>
+        <v>-2.212058392761011</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3.371608547908522e-14</v>
+        <v>8.879008639439689e-14</v>
       </c>
       <c r="AR26" t="n">
-        <v>-4.700540704156521</v>
+        <v>-4.700540704077868</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.74118530494161e-12</v>
+        <v>-1.853095454862341e-11</v>
       </c>
     </row>
     <row r="27">
@@ -7478,112 +7478,112 @@
         <v>-1804.785529194164</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4537190030250376</v>
+        <v>-0.4537190030243844</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.7505876822825513</v>
+        <v>-0.7505876822821378</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.00145657330068003</v>
+        <v>-0.001456573300679839</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0008825836814738829</v>
+        <v>-0.0008825836814975517</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.0290784907041274</v>
+        <v>-0.02907849070410424</v>
       </c>
       <c r="O27" t="n">
-        <v>-3.586244829761654e-14</v>
+        <v>-1.611526070967156e-13</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.4537911944462054</v>
+        <v>-0.4537911944455522</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.7505876822828246</v>
+        <v>-0.7505876822834716</v>
       </c>
       <c r="R27" t="n">
-        <v>0.003032168184686586</v>
+        <v>0.003032168184686301</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.0008825836814639399</v>
+        <v>-0.0008825836814504936</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.1913477001707182</v>
+        <v>-0.1913477001706949</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.584592144909157e-14</v>
+        <v>-1.611381091097773e-13</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.4537190030250376</v>
+        <v>-0.4537190030243844</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.7505876822825513</v>
+        <v>-0.7505876822821378</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.00145657330068003</v>
+        <v>-0.001456573300679839</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.0008825836814738829</v>
+        <v>-0.0008825836814975517</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.0290784907041274</v>
+        <v>-0.02907849070410424</v>
       </c>
       <c r="AA27" t="n">
-        <v>-3.586244829761654e-14</v>
+        <v>-1.611526070967156e-13</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.4537911944462054</v>
+        <v>-0.4537911944455522</v>
       </c>
       <c r="AC27" t="n">
-        <v>-0.7505876822828246</v>
+        <v>-0.7505876822834716</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.003032168184686586</v>
+        <v>0.003032168184686301</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.0008825836814639399</v>
+        <v>-0.0008825836814504936</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.1913477001707182</v>
+        <v>-0.1913477001706949</v>
       </c>
       <c r="AG27" t="n">
-        <v>-3.584592144909157e-14</v>
+        <v>-1.611381091097773e-13</v>
       </c>
       <c r="AH27" t="n">
         <v>8.554683408379788</v>
       </c>
       <c r="AI27" t="n">
-        <v>-1.4210854715202e-12</v>
+        <v>4.661160346586257e-12</v>
       </c>
       <c r="AJ27" t="n">
-        <v>91.28529229083352</v>
+        <v>91.28529229081425</v>
       </c>
       <c r="AK27" t="n">
-        <v>-2.122434172857623e-14</v>
+        <v>-1.00450897599913e-13</v>
       </c>
       <c r="AL27" t="n">
-        <v>-275.0817579093762</v>
+        <v>-275.0817579092991</v>
       </c>
       <c r="AM27" t="n">
-        <v>-5.74118530494161e-12</v>
+        <v>1.858779796748422e-11</v>
       </c>
       <c r="AN27" t="n">
         <v>-8.554683408379788</v>
       </c>
       <c r="AO27" t="n">
-        <v>1.4210854715202e-12</v>
+        <v>-4.661160346586257e-12</v>
       </c>
       <c r="AP27" t="n">
-        <v>-91.28529229083352</v>
+        <v>-91.28529229081425</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2.122434172857623e-14</v>
+        <v>1.00450897599913e-13</v>
       </c>
       <c r="AR27" t="n">
-        <v>-455.2005804172919</v>
+        <v>-455.2005804172148</v>
       </c>
       <c r="AS27" t="n">
-        <v>-5.684341886080801e-12</v>
+        <v>1.864464138634503e-11</v>
       </c>
     </row>
     <row r="28">
@@ -7605,124 +7605,124 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>-9.398725575804345e-05</v>
+        <v>-9.398725575793243e-05</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.174840696975543e-05</v>
+        <v>-1.174840696974155e-05</v>
       </c>
       <c r="H28" t="n">
-        <v>-11.13748980732815</v>
+        <v>-11.13748980731499</v>
       </c>
       <c r="I28" t="n">
-        <v>-2349.681393951086</v>
+        <v>-2349.68139394831</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4537911944462054</v>
+        <v>-0.4537911944455522</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.7505876822828246</v>
+        <v>-0.7505876822834716</v>
       </c>
       <c r="L28" t="n">
-        <v>0.003032168184686586</v>
+        <v>0.003032168184686301</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0008825836814639399</v>
+        <v>-0.0008825836814504936</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.1913477001707182</v>
+        <v>-0.1913477001706949</v>
       </c>
       <c r="O28" t="n">
-        <v>-3.584592144909157e-14</v>
+        <v>-1.611381091097773e-13</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.4537911944465061</v>
+        <v>-0.453791194446797</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.7504936950270665</v>
+        <v>-0.7504936950277137</v>
       </c>
       <c r="R28" t="n">
-        <v>0.001456573300680231</v>
+        <v>0.001456573300679713</v>
       </c>
       <c r="S28" t="n">
-        <v>0.006590736799556234</v>
+        <v>0.006590736799569702</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.1913477001707339</v>
+        <v>-0.1913477001707365</v>
       </c>
       <c r="U28" t="n">
-        <v>-3.591934838764536e-14</v>
+        <v>-1.612105836505838e-13</v>
       </c>
       <c r="V28" t="n">
-        <v>0.7505876822828246</v>
+        <v>0.7505876822834716</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.4537911944462054</v>
+        <v>-0.4537911944455522</v>
       </c>
       <c r="X28" t="n">
-        <v>0.003032168184686586</v>
+        <v>0.003032168184686301</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.1913477001707182</v>
+        <v>0.1913477001706949</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.0008825836814639399</v>
+        <v>-0.0008825836814504936</v>
       </c>
       <c r="AA28" t="n">
-        <v>-3.584592144909157e-14</v>
+        <v>-1.611381091097773e-13</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.7504936950270665</v>
+        <v>0.7504936950277137</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.4537911944465061</v>
+        <v>-0.453791194446797</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.001456573300680231</v>
+        <v>0.001456573300679713</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.1913477001707339</v>
+        <v>0.1913477001707365</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.006590736799556234</v>
+        <v>0.006590736799569702</v>
       </c>
       <c r="AG28" t="n">
-        <v>-3.591934838764536e-14</v>
+        <v>-1.612105836505838e-13</v>
       </c>
       <c r="AH28" t="n">
         <v>11.13748980732635</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.4210854715202e-12</v>
+        <v>-4.646949491871055e-12</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-2.212058392789006</v>
+        <v>-2.212058392800185</v>
       </c>
       <c r="AK28" t="n">
-        <v>-3.352873534367973e-14</v>
+        <v>-8.876233081878127e-14</v>
       </c>
       <c r="AL28" t="n">
-        <v>4.700540704189827</v>
+        <v>4.70054070423453</v>
       </c>
       <c r="AM28" t="n">
-        <v>5.712763595511205e-12</v>
+        <v>-1.853095454862341e-11</v>
       </c>
       <c r="AN28" t="n">
         <v>-11.13748980732635</v>
       </c>
       <c r="AO28" t="n">
-        <v>-1.4210854715202e-12</v>
+        <v>4.646949491871055e-12</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.212058392789006</v>
+        <v>2.212058392800185</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.352873534367973e-14</v>
+        <v>8.876233081878127e-14</v>
       </c>
       <c r="AR28" t="n">
-        <v>12.99592643812222</v>
+        <v>12.99592643816695</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.627498467219993e-12</v>
+        <v>-1.861621967691462e-11</v>
       </c>
     </row>
     <row r="29">
@@ -7744,124 +7744,124 @@
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>-7.219142116776656e-05</v>
+        <v>-7.219142116787758e-05</v>
       </c>
       <c r="G29" t="n">
-        <v>-9.02392764597082e-06</v>
+        <v>-9.023927645984697e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>-8.554683408380336</v>
+        <v>-8.554683408393494</v>
       </c>
       <c r="I29" t="n">
-        <v>-1804.785529194164</v>
+        <v>-1804.785529196939</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4537911944465061</v>
+        <v>-0.453791194446797</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.7504936950270665</v>
+        <v>-0.7504936950277137</v>
       </c>
       <c r="L29" t="n">
-        <v>0.001456573300680231</v>
+        <v>0.001456573300679713</v>
       </c>
       <c r="M29" t="n">
-        <v>0.006590736799556234</v>
+        <v>0.006590736799569702</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.1913477001707339</v>
+        <v>-0.1913477001707365</v>
       </c>
       <c r="O29" t="n">
-        <v>-3.591934838764536e-14</v>
+        <v>-1.612105836505838e-13</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.4537190030253384</v>
+        <v>-0.4537190030256291</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.7504936950267934</v>
+        <v>-0.7504936950263797</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.003032168184686789</v>
+        <v>-0.003032168184686173</v>
       </c>
       <c r="S29" t="n">
-        <v>0.006590736799546265</v>
+        <v>0.006590736799522585</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.0290784907041432</v>
+        <v>-0.02907849070414583</v>
       </c>
       <c r="U29" t="n">
-        <v>-3.586128221406856e-14</v>
+        <v>-1.611412101213256e-13</v>
       </c>
       <c r="V29" t="n">
-        <v>0.4537911944465061</v>
+        <v>0.453791194446797</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.7504936950270665</v>
+        <v>-0.7504936950277137</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.001456573300680231</v>
+        <v>-0.001456573300679713</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.006590736799556234</v>
+        <v>-0.006590736799569702</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.1913477001707339</v>
+        <v>-0.1913477001707365</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.591934838764536e-14</v>
+        <v>1.612105836505838e-13</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.4537190030253384</v>
+        <v>0.4537190030256291</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.7504936950267934</v>
+        <v>-0.7504936950263797</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.003032168184686789</v>
+        <v>0.003032168184686173</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.006590736799546265</v>
+        <v>-0.006590736799522585</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.0290784907041432</v>
+        <v>-0.02907849070414583</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.586128221406856e-14</v>
+        <v>1.611412101213256e-13</v>
       </c>
       <c r="AH29" t="n">
-        <v>8.554683408379788</v>
+        <v>8.554683408394339</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.449507180950604e-12</v>
+        <v>-4.632738637155853e-12</v>
       </c>
       <c r="AJ29" t="n">
-        <v>91.2852922908466</v>
+        <v>91.28529229084891</v>
       </c>
       <c r="AK29" t="n">
-        <v>-2.127811815633152e-14</v>
+        <v>-1.005775324136593e-13</v>
       </c>
       <c r="AL29" t="n">
-        <v>-455.2005804173441</v>
+        <v>-455.2005804173534</v>
       </c>
       <c r="AM29" t="n">
-        <v>5.854872142663226e-12</v>
+        <v>-1.84741111297626e-11</v>
       </c>
       <c r="AN29" t="n">
-        <v>-8.554683408379788</v>
+        <v>-8.554683408394339</v>
       </c>
       <c r="AO29" t="n">
-        <v>-1.449507180950604e-12</v>
+        <v>4.632738637155853e-12</v>
       </c>
       <c r="AP29" t="n">
-        <v>-91.2852922908466</v>
+        <v>-91.28529229084891</v>
       </c>
       <c r="AQ29" t="n">
-        <v>2.127811815633152e-14</v>
+        <v>1.005775324136593e-13</v>
       </c>
       <c r="AR29" t="n">
-        <v>-275.0817579094285</v>
+        <v>-275.0817579094377</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.798028723802418e-12</v>
+        <v>-1.858779796748422e-11</v>
       </c>
     </row>
     <row r="30">
@@ -7895,112 +7895,112 @@
         <v>369.9427691461476</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.8457911393550082</v>
+        <v>-0.845791139355267</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.7611520690276043</v>
+        <v>-0.7611520690270692</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.003139734310674845</v>
+        <v>-0.003139734310674162</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0006683120527693941</v>
+        <v>-0.0006683120527781236</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.05000005721100176</v>
+        <v>-0.05000005721099737</v>
       </c>
       <c r="O30" t="n">
-        <v>-4.797347225031697e-14</v>
+        <v>-1.899677898334275e-13</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.8457911393545802</v>
+        <v>-0.8457911393537922</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.7611372713168385</v>
+        <v>-0.7611372713163034</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.001559049602196457</v>
+        <v>-0.001559049602196257</v>
       </c>
       <c r="S30" t="n">
-        <v>0.00202947994641545</v>
+        <v>0.002029479946406675</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.05000005721099056</v>
+        <v>-0.05000005721098015</v>
       </c>
       <c r="U30" t="n">
-        <v>-4.795316946883113e-14</v>
+        <v>-1.900821841067412e-13</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.7611520690276043</v>
+        <v>-0.7611520690270692</v>
       </c>
       <c r="W30" t="n">
-        <v>0.8457911393550082</v>
+        <v>0.845791139355267</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.003139734310674845</v>
+        <v>-0.003139734310674162</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.05000005721100176</v>
+        <v>-0.05000005721099737</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.0006683120527693941</v>
+        <v>0.0006683120527781236</v>
       </c>
       <c r="AA30" t="n">
-        <v>-4.797347225031697e-14</v>
+        <v>-1.899677898334275e-13</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.7611372713168385</v>
+        <v>-0.7611372713163034</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.8457911393545802</v>
+        <v>0.8457911393537922</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.001559049602196457</v>
+        <v>-0.001559049602196257</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.05000005721099056</v>
+        <v>-0.05000005721098015</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.00202947994641545</v>
+        <v>-0.002029479946406675</v>
       </c>
       <c r="AG30" t="n">
-        <v>-4.795316946883113e-14</v>
+        <v>-1.900821841067412e-13</v>
       </c>
       <c r="AH30" t="n">
-        <v>-1.753528725763317</v>
+        <v>-1.753528725748765</v>
       </c>
       <c r="AI30" t="n">
-        <v>4.604316927725449e-12</v>
+        <v>-4.732214620162267e-12</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.4020961332541386</v>
+        <v>0.4020961332469026</v>
       </c>
       <c r="AK30" t="n">
-        <v>-2.389755060505649e-14</v>
+        <v>-3.67622599029005e-14</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0.1111099734689656</v>
+        <v>-0.1111099734400467</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.84172677109018e-11</v>
+        <v>-1.887201506178826e-11</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.753528725763317</v>
+        <v>1.753528725748765</v>
       </c>
       <c r="AO30" t="n">
-        <v>-4.604316927725449e-12</v>
+        <v>4.732214620162267e-12</v>
       </c>
       <c r="AP30" t="n">
-        <v>-0.4020961332541386</v>
+        <v>-0.4020961332469026</v>
       </c>
       <c r="AQ30" t="n">
-        <v>2.389755060505649e-14</v>
+        <v>3.67622599029005e-14</v>
       </c>
       <c r="AR30" t="n">
-        <v>-3.105659092564143</v>
+        <v>-3.105659092535173</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.84172677109018e-11</v>
+        <v>-1.904254531837068e-11</v>
       </c>
     </row>
     <row r="31">
@@ -8022,124 +8022,124 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0003223038101611841</v>
+        <v>-0.0003223038101612952</v>
       </c>
       <c r="G31" t="n">
-        <v>-4.028797627014802e-05</v>
+        <v>-4.02879762701619e-05</v>
       </c>
       <c r="H31" t="n">
-        <v>-38.19300150410032</v>
+        <v>-38.19300150411348</v>
       </c>
       <c r="I31" t="n">
-        <v>-8057.595254029604</v>
+        <v>-8057.595254032378</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8457911393545802</v>
+        <v>-0.8457911393537922</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.7611372713168385</v>
+        <v>-0.7611372713163034</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.001559049602196457</v>
+        <v>-0.001559049602196257</v>
       </c>
       <c r="M31" t="n">
-        <v>0.00202947994641545</v>
+        <v>0.002029479946406675</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.05000005721099056</v>
+        <v>-0.05000005721098015</v>
       </c>
       <c r="O31" t="n">
-        <v>-4.795316946883113e-14</v>
+        <v>-1.900821841067412e-13</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.8461134431647414</v>
+        <v>-0.8461134431639535</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.7611372713171778</v>
+        <v>-0.7611372713178689</v>
       </c>
       <c r="R31" t="n">
-        <v>0.003139734310674613</v>
+        <v>0.003139734310674283</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002029479946420887</v>
+        <v>0.00202947994642285</v>
       </c>
       <c r="T31" t="n">
-        <v>0.008961453069770897</v>
+        <v>0.008961453069781296</v>
       </c>
       <c r="U31" t="n">
-        <v>-4.795187645833391e-14</v>
+        <v>-1.900022251312968e-13</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.8457911393545802</v>
+        <v>-0.8457911393537922</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.7611372713168385</v>
+        <v>-0.7611372713163034</v>
       </c>
       <c r="X31" t="n">
-        <v>-0.001559049602196457</v>
+        <v>-0.001559049602196257</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.00202947994641545</v>
+        <v>0.002029479946406675</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.05000005721099056</v>
+        <v>-0.05000005721098015</v>
       </c>
       <c r="AA31" t="n">
-        <v>-4.795316946883113e-14</v>
+        <v>-1.900821841067412e-13</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.8461134431647414</v>
+        <v>-0.8461134431639535</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.7611372713171778</v>
+        <v>-0.7611372713178689</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.003139734310674613</v>
+        <v>0.003139734310674283</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.002029479946420887</v>
+        <v>0.00202947994642285</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.008961453069770897</v>
+        <v>0.008961453069781296</v>
       </c>
       <c r="AG31" t="n">
-        <v>-4.795187645833391e-14</v>
+        <v>-1.900022251312968e-13</v>
       </c>
       <c r="AH31" t="n">
-        <v>38.19300150409981</v>
+        <v>38.19300150411436</v>
       </c>
       <c r="AI31" t="n">
-        <v>-4.632738637155853e-12</v>
+        <v>4.703792910731863e-12</v>
       </c>
       <c r="AJ31" t="n">
-        <v>16.59335177284954</v>
+        <v>16.59335177284094</v>
       </c>
       <c r="AK31" t="n">
-        <v>-1.160616741602283e-14</v>
+        <v>-3.452880342758036e-14</v>
       </c>
       <c r="AL31" t="n">
-        <v>-99.09704529722077</v>
+        <v>-99.09704529718634</v>
       </c>
       <c r="AM31" t="n">
-        <v>-1.84741111297626e-11</v>
+        <v>1.875832822406664e-11</v>
       </c>
       <c r="AN31" t="n">
-        <v>-38.19300150409981</v>
+        <v>-38.19300150411436</v>
       </c>
       <c r="AO31" t="n">
-        <v>4.632738637155853e-12</v>
+        <v>-4.703792910731863e-12</v>
       </c>
       <c r="AP31" t="n">
-        <v>-16.59335177284954</v>
+        <v>-16.59335177284094</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.160616741602283e-14</v>
+        <v>3.452880342758036e-14</v>
       </c>
       <c r="AR31" t="n">
-        <v>-33.64976888557555</v>
+        <v>-33.64976888554113</v>
       </c>
       <c r="AS31" t="n">
-        <v>-1.84741111297626e-11</v>
+        <v>1.887201506178826e-11</v>
       </c>
     </row>
     <row r="32">
@@ -8173,112 +8173,112 @@
         <v>369.9427691489232</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8461134431647414</v>
+        <v>-0.8461134431639535</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.7611372713171778</v>
+        <v>-0.7611372713178689</v>
       </c>
       <c r="L32" t="n">
-        <v>0.003139734310674613</v>
+        <v>0.003139734310674283</v>
       </c>
       <c r="M32" t="n">
-        <v>0.002029479946420887</v>
+        <v>0.00202947994642285</v>
       </c>
       <c r="N32" t="n">
-        <v>0.008961453069770897</v>
+        <v>0.008961453069781296</v>
       </c>
       <c r="O32" t="n">
-        <v>-4.795187645833391e-14</v>
+        <v>-1.900022251312968e-13</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.8461134431651695</v>
+        <v>-0.8461134431654285</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.7611520690279437</v>
+        <v>-0.7611520690286349</v>
       </c>
       <c r="R32" t="n">
-        <v>0.001559049602196688</v>
+        <v>0.001559049602196137</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.0006683120527639328</v>
+        <v>-0.0006683120527619788</v>
       </c>
       <c r="T32" t="n">
-        <v>0.008961453069759602</v>
+        <v>0.008961453069764045</v>
       </c>
       <c r="U32" t="n">
-        <v>-4.795728302061472e-14</v>
+        <v>-1.900474795736123e-13</v>
       </c>
       <c r="V32" t="n">
-        <v>0.7611372713171778</v>
+        <v>0.7611372713178689</v>
       </c>
       <c r="W32" t="n">
-        <v>-0.8461134431647414</v>
+        <v>-0.8461134431639535</v>
       </c>
       <c r="X32" t="n">
-        <v>0.003139734310674613</v>
+        <v>0.003139734310674283</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.008961453069770897</v>
+        <v>-0.008961453069781296</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.002029479946420887</v>
+        <v>0.00202947994642285</v>
       </c>
       <c r="AA32" t="n">
-        <v>-4.795187645833391e-14</v>
+        <v>-1.900022251312968e-13</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.7611520690279437</v>
+        <v>0.7611520690286349</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.8461134431651695</v>
+        <v>-0.8461134431654285</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.001559049602196688</v>
+        <v>0.001559049602196137</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.008961453069759602</v>
+        <v>-0.008961453069764045</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.0006683120527639328</v>
+        <v>-0.0006683120527619788</v>
       </c>
       <c r="AG32" t="n">
-        <v>-4.795728302061472e-14</v>
+        <v>-1.900474795736123e-13</v>
       </c>
       <c r="AH32" t="n">
         <v>-1.753528725763317</v>
       </c>
       <c r="AI32" t="n">
-        <v>4.604316927725449e-12</v>
+        <v>-4.718003765447065e-12</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-0.4020961332587234</v>
+        <v>-0.4020961332603305</v>
       </c>
       <c r="AK32" t="n">
-        <v>-2.410918686912566e-14</v>
+        <v>-3.682470994803566e-14</v>
       </c>
       <c r="AL32" t="n">
-        <v>3.105659092582468</v>
+        <v>3.105659092588902</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.84741111297626e-11</v>
+        <v>-1.881517164292745e-11</v>
       </c>
       <c r="AN32" t="n">
         <v>1.753528725763317</v>
       </c>
       <c r="AO32" t="n">
-        <v>-4.604316927725449e-12</v>
+        <v>4.718003765447065e-12</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.4020961332587234</v>
+        <v>0.4020961332603305</v>
       </c>
       <c r="AQ32" t="n">
-        <v>2.410918686912566e-14</v>
+        <v>3.682470994803566e-14</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.1111099734873178</v>
+        <v>0.1111099734937417</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.84741111297626e-11</v>
+        <v>-1.887201506178826e-11</v>
       </c>
     </row>
     <row r="33">
@@ -8300,124 +8300,124 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.0003223038101612952</v>
+        <v>-0.0003223038101615172</v>
       </c>
       <c r="G33" t="n">
-        <v>-4.02879762701619e-05</v>
+        <v>-4.028797627018965e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>-38.19300150411348</v>
+        <v>-38.19300150413979</v>
       </c>
       <c r="I33" t="n">
-        <v>-8057.595254032378</v>
+        <v>-8057.595254037929</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.8461134431651695</v>
+        <v>-0.8461134431654285</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.7611520690279437</v>
+        <v>-0.7611520690286349</v>
       </c>
       <c r="L33" t="n">
-        <v>0.001559049602196688</v>
+        <v>0.001559049602196137</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.0006683120527639328</v>
+        <v>-0.0006683120527619788</v>
       </c>
       <c r="N33" t="n">
-        <v>0.008961453069759602</v>
+        <v>0.008961453069764045</v>
       </c>
       <c r="O33" t="n">
-        <v>-4.795728302061472e-14</v>
+        <v>-1.900474795736123e-13</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.8457911393550082</v>
+        <v>-0.845791139355267</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.7611520690276043</v>
+        <v>-0.7611520690270692</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.003139734310674845</v>
+        <v>-0.003139734310674162</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.0006683120527693941</v>
+        <v>-0.0006683120527781236</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.05000005721100176</v>
+        <v>-0.05000005721099737</v>
       </c>
       <c r="U33" t="n">
-        <v>-4.797347225031697e-14</v>
+        <v>-1.899677898334275e-13</v>
       </c>
       <c r="V33" t="n">
-        <v>0.8461134431651695</v>
+        <v>0.8461134431654285</v>
       </c>
       <c r="W33" t="n">
-        <v>-0.7611520690279437</v>
+        <v>-0.7611520690286349</v>
       </c>
       <c r="X33" t="n">
-        <v>-0.001559049602196688</v>
+        <v>-0.001559049602196137</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.0006683120527639328</v>
+        <v>0.0006683120527619788</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.008961453069759602</v>
+        <v>0.008961453069764045</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.795728302061472e-14</v>
+        <v>1.900474795736123e-13</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.8457911393550082</v>
+        <v>0.845791139355267</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.7611520690276043</v>
+        <v>-0.7611520690270692</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.003139734310674845</v>
+        <v>0.003139734310674162</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.0006683120527693941</v>
+        <v>0.0006683120527781236</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.05000005721100176</v>
+        <v>-0.05000005721099737</v>
       </c>
       <c r="AG33" t="n">
-        <v>4.797347225031697e-14</v>
+        <v>1.899677898334275e-13</v>
       </c>
       <c r="AH33" t="n">
-        <v>38.19300150411436</v>
+        <v>38.19300150414347</v>
       </c>
       <c r="AI33" t="n">
-        <v>4.618527782440651e-12</v>
+        <v>-4.746425474877469e-12</v>
       </c>
       <c r="AJ33" t="n">
-        <v>16.59335177285886</v>
+        <v>16.59335177285531</v>
       </c>
       <c r="AK33" t="n">
-        <v>-1.165777543943314e-14</v>
+        <v>-3.446266709505874e-14</v>
       </c>
       <c r="AL33" t="n">
-        <v>-33.64976888561286</v>
+        <v>-33.64976888559865</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.84741111297626e-11</v>
+        <v>-1.892885848064907e-11</v>
       </c>
       <c r="AN33" t="n">
-        <v>-38.19300150411436</v>
+        <v>-38.19300150414347</v>
       </c>
       <c r="AO33" t="n">
-        <v>-4.618527782440651e-12</v>
+        <v>4.746425474877469e-12</v>
       </c>
       <c r="AP33" t="n">
-        <v>-16.59335177285886</v>
+        <v>-16.59335177285531</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.165777543943314e-14</v>
+        <v>3.446266709505874e-14</v>
       </c>
       <c r="AR33" t="n">
-        <v>-99.09704529725796</v>
+        <v>-99.09704529724382</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.84741111297626e-11</v>
+        <v>-1.904254531837068e-11</v>
       </c>
     </row>
   </sheetData>
